--- a/Översikt HOFORS.xlsx
+++ b/Översikt HOFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46064</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>45784</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>46164</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45299</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>46079</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>46163</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>46085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>45316</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1568,7 +1568,7 @@
         <v>46266</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>45163</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1795,7 +1795,7 @@
         <v>44623</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1911,7 +1911,7 @@
         <v>45813</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2024,7 +2024,7 @@
         <v>45860</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2140,7 +2140,7 @@
         <v>46199</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2256,7 +2256,7 @@
         <v>44816</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2366,7 +2366,7 @@
         <v>45895</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>45895</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2588,7 +2588,7 @@
         <v>46154</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2698,7 +2698,7 @@
         <v>45935</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2809,7 +2809,7 @@
         <v>46025</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2919,7 +2919,7 @@
         <v>46043</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3030,7 +3030,7 @@
         <v>46177</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3141,7 +3141,7 @@
         <v>46095</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3247,7 +3247,7 @@
         <v>46199</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3362,7 +3362,7 @@
         <v>45813</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
         <v>45874</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44102</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>44169</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3810,7 +3810,7 @@
         <v>44585</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3921,7 +3921,7 @@
         <v>45317</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4032,7 +4032,7 @@
         <v>45701</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4143,7 +4143,7 @@
         <v>45895</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4254,7 +4254,7 @@
         <v>45895</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
         <v>46142</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>46125</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4587,7 +4587,7 @@
         <v>44649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4692,7 +4692,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4802,7 +4802,7 @@
         <v>44559</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>45477</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5017,7 +5017,7 @@
         <v>44928</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
         <v>45477</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5241,7 +5241,7 @@
         <v>45453</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5351,7 +5351,7 @@
         <v>45488</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5461,7 +5461,7 @@
         <v>45597</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45531</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>44624</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5785,7 +5785,7 @@
         <v>45924</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5899,7 +5899,7 @@
         <v>45917</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6009,7 +6009,7 @@
         <v>45589</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>45007</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>44473</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>45127</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6448,7 +6448,7 @@
         <v>45534</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>46183</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>45924</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6782,7 +6782,7 @@
         <v>46091</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6891,7 +6891,7 @@
         <v>46196</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7001,7 +7001,7 @@
         <v>45531</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7111,7 +7111,7 @@
         <v>46252</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7225,7 +7225,7 @@
         <v>46217</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7335,7 +7335,7 @@
         <v>46217</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7445,7 +7445,7 @@
         <v>46262</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>45813</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45813</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45813</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>45813</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
         <v>45348</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>45860</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8210,7 +8210,7 @@
         <v>45870</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8320,7 +8320,7 @@
         <v>45874</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8430,7 +8430,7 @@
         <v>45881</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>45701</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8650,7 +8650,7 @@
         <v>45727</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8764,7 +8764,7 @@
         <v>45706</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8874,7 +8874,7 @@
         <v>44868</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8952,7 +8952,7 @@
         <v>44582</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9025,7 +9025,7 @@
         <v>44501</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9098,7 +9098,7 @@
         <v>44512</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>44873</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9244,7 +9244,7 @@
         <v>44868</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>44692</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9395,7 +9395,7 @@
         <v>45755</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>45531</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9551,7 +9551,7 @@
         <v>44967</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9624,7 +9624,7 @@
         <v>45523</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9697,7 +9697,7 @@
         <v>45523</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9770,7 +9770,7 @@
         <v>45477</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>45127</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9926,7 +9926,7 @@
         <v>45684</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>45219</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10072,7 +10072,7 @@
         <v>45232</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>44810</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10218,7 +10218,7 @@
         <v>45387</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10291,7 +10291,7 @@
         <v>44487</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10364,7 +10364,7 @@
         <v>45728</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10442,7 +10442,7 @@
         <v>44810</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10515,7 +10515,7 @@
         <v>45475</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10593,7 +10593,7 @@
         <v>44484</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10666,7 +10666,7 @@
         <v>45250</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10739,7 +10739,7 @@
         <v>45173</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10817,7 +10817,7 @@
         <v>45453</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10895,7 +10895,7 @@
         <v>45188</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10968,7 +10968,7 @@
         <v>45007</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11046,7 +11046,7 @@
         <v>44977</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>45488</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>45488</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11275,7 +11275,7 @@
         <v>45587</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11353,7 +11353,7 @@
         <v>45156</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11426,7 +11426,7 @@
         <v>45531</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11504,7 +11504,7 @@
         <v>45887</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11582,7 +11582,7 @@
         <v>45884</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         <v>45490</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11733,7 +11733,7 @@
         <v>45674</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11806,7 +11806,7 @@
         <v>45912</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11884,7 +11884,7 @@
         <v>45453</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11962,7 +11962,7 @@
         <v>45252</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12035,7 +12035,7 @@
         <v>45343</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>45895</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12186,7 +12186,7 @@
         <v>46080</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12264,7 +12264,7 @@
         <v>45463</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>45376</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12415,7 +12415,7 @@
         <v>46105</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>45538</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12566,7 +12566,7 @@
         <v>46092</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>45629</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12717,7 +12717,7 @@
         <v>46085</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12790,7 +12790,7 @@
         <v>46113</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12863,7 +12863,7 @@
         <v>45439</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12941,7 +12941,7 @@
         <v>45439</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13019,7 +13019,7 @@
         <v>44671</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>45917</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         <v>45630</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         <v>45929</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>45069</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13394,7 +13394,7 @@
         <v>45930</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13467,7 +13467,7 @@
         <v>45933</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>45816</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13623,7 +13623,7 @@
         <v>45677</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13696,7 +13696,7 @@
         <v>45933</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13774,7 +13774,7 @@
         <v>45933</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13852,7 +13852,7 @@
         <v>45933</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>45125</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -14003,7 +14003,7 @@
         <v>45935</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14081,7 +14081,7 @@
         <v>45271</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14154,7 +14154,7 @@
         <v>45709</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14227,7 +14227,7 @@
         <v>45587</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>45947</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>44986</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14461,7 +14461,7 @@
         <v>45956</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14534,7 +14534,7 @@
         <v>45967</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14607,7 +14607,7 @@
         <v>45967</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14680,7 +14680,7 @@
         <v>45967</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14753,7 +14753,7 @@
         <v>46042</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14826,7 +14826,7 @@
         <v>45966</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>45969</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14972,7 +14972,7 @@
         <v>45969</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15045,7 +15045,7 @@
         <v>45127</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15123,7 +15123,7 @@
         <v>45792</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15196,7 +15196,7 @@
         <v>46042</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>45980</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15342,7 +15342,7 @@
         <v>45980</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15415,7 +15415,7 @@
         <v>45980</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15488,7 +15488,7 @@
         <v>45980</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>45446</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15634,7 +15634,7 @@
         <v>45986</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>45159</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15780,7 +15780,7 @@
         <v>45986</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15853,7 +15853,7 @@
         <v>46162</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15931,7 +15931,7 @@
         <v>46162</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -16009,7 +16009,7 @@
         <v>46000</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16082,7 +16082,7 @@
         <v>46167</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16160,7 +16160,7 @@
         <v>46002</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16233,7 +16233,7 @@
         <v>44680</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16306,7 +16306,7 @@
         <v>46169</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>46169</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16457,7 +16457,7 @@
         <v>46029</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>46029</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16603,7 +16603,7 @@
         <v>46030</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>46030</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16749,7 +16749,7 @@
         <v>45202</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16822,7 +16822,7 @@
         <v>46037</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16895,7 +16895,7 @@
         <v>46036</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16968,7 +16968,7 @@
         <v>46042</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17041,7 +17041,7 @@
         <v>46050</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>45145</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17187,7 +17187,7 @@
         <v>44812</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17260,7 +17260,7 @@
         <v>45117</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>45117</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17406,7 +17406,7 @@
         <v>46061</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17479,7 +17479,7 @@
         <v>46047</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17552,7 +17552,7 @@
         <v>46183</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17630,7 +17630,7 @@
         <v>46183</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17708,7 +17708,7 @@
         <v>46083</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>45587</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17854,7 +17854,7 @@
         <v>46092</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17932,7 +17932,7 @@
         <v>45506</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>45280</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>44489</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18156,7 +18156,7 @@
         <v>45085</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18234,7 +18234,7 @@
         <v>46196</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>46196</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18390,7 +18390,7 @@
         <v>46107</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18468,7 +18468,7 @@
         <v>46115</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18541,7 +18541,7 @@
         <v>46199</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18619,7 +18619,7 @@
         <v>46064</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18692,7 +18692,7 @@
         <v>45387</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18765,7 +18765,7 @@
         <v>46085</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18838,7 +18838,7 @@
         <v>45476</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18911,7 +18911,7 @@
         <v>46091</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18989,7 +18989,7 @@
         <v>44810</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19062,7 +19062,7 @@
         <v>46133</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19140,7 +19140,7 @@
         <v>44624</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19213,7 +19213,7 @@
         <v>44994</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19291,7 +19291,7 @@
         <v>45531</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>44526</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19442,7 +19442,7 @@
         <v>45343</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19515,7 +19515,7 @@
         <v>46211</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19588,7 +19588,7 @@
         <v>44473</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19666,7 +19666,7 @@
         <v>46259</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19744,7 +19744,7 @@
         <v>45755</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19822,7 +19822,7 @@
         <v>46216</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19900,7 +19900,7 @@
         <v>46216</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19978,7 +19978,7 @@
         <v>46260</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20056,7 +20056,7 @@
         <v>46219</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20129,7 +20129,7 @@
         <v>45117</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20202,7 +20202,7 @@
         <v>45534</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>46268</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>45302</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20426,7 +20426,7 @@
         <v>46272</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20499,7 +20499,7 @@
         <v>45782</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20572,7 +20572,7 @@
         <v>46272</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20645,7 +20645,7 @@
         <v>46274</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20718,7 +20718,7 @@
         <v>46274</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>45334</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20864,7 +20864,7 @@
         <v>46021</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20937,7 +20937,7 @@
         <v>45792</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21010,7 +21010,7 @@
         <v>45523</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>45614</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21156,7 +21156,7 @@
         <v>45805</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21229,7 +21229,7 @@
         <v>45833</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>45835</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45868</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21453,7 +21453,7 @@
         <v>45877</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21531,7 +21531,7 @@
         <v>45700</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>45316</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21687,7 +21687,7 @@
         <v>45319</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21765,7 +21765,7 @@
         <v>45771</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21843,7 +21843,7 @@
         <v>45707</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21921,7 +21921,7 @@
         <v>45895</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21999,7 +21999,7 @@
         <v>46069</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         <v>46089</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>

--- a/Översikt HOFORS.xlsx
+++ b/Översikt HOFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46064</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>45784</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>46164</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45299</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>46079</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>46163</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>46085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>46266</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45316</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45163</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45813</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>44623</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>45860</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>46199</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44816</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>46025</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>46043</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>45895</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45895</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>46095</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>45813</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>46154</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>45935</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>46177</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>45874</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>46199</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44102</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44169</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>44585</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>45317</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45701</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>45895</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45895</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>46142</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>46125</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>44649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>44559</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>45531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>45127</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>44473</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>45488</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>45007</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>45917</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>45924</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>45589</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>46091</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>45453</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>45813</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>45813</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>45813</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>45813</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>45477</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>45534</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>45924</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>45348</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>45860</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>45870</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>46183</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>45874</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>46196</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45531</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>45881</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>45597</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>46252</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>44624</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>46217</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>46217</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>46262</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>45477</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>44928</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>45701</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>45727</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>45706</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>44868</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>44582</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>44501</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>44512</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>44873</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>44868</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>44692</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>45387</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>45531</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>45446</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         <v>45453</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>44810</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>44487</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>45490</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>45271</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>45884</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>46029</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>46030</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>45792</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>45614</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>45523</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>46029</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>45887</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>45173</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>46036</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>45376</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>46037</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>45895</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>46042</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>45488</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>45488</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45387</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>44489</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         <v>46050</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>45343</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>45506</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>46061</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>45917</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>46047</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>45232</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>45930</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>45929</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>46083</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>45534</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>45933</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>45935</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>45933</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>45816</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>45933</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>45933</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>44671</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>46092</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>45587</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45453</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>45947</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>46107</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>44967</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>45956</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>46115</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>45966</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>46064</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>44994</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>46085</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>45967</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>45967</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45967</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>45969</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45969</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>46091</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>45980</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>45980</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>45980</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>46133</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>45980</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>45986</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>45986</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>45728</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>46085</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>44810</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>46080</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>45912</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>46000</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>46002</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>45219</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>46105</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>45463</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>45755</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>44810</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>46113</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>45805</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
         <v>45069</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>45476</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         <v>46092</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>45523</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45523</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>45629</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>45538</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>46042</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>45833</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>46042</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>45792</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         <v>45835</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>44986</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
         <v>46162</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>46162</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>45117</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>46167</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>46169</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>46169</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>44977</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>45475</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>45868</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>45117</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>45007</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>45085</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>46183</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>46183</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>45145</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>45877</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>46196</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>46196</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>46199</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>45159</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>45156</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>46211</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45531</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>45709</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44680</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>46259</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>46216</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>46216</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>46260</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>46219</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18860,7 +18860,7 @@
         <v>45127</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>45755</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>45252</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>45280</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>46268</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>45250</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>46272</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>46272</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>44812</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>46274</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>46274</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>46021</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45202</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>44526</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>46259</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>44473</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>45188</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45587</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>46289</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>44624</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>45117</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>45343</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>44484</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>45587</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>45127</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>45439</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>45439</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>45674</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>45125</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>45630</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>45531</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         <v>45677</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>45684</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>45477</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>45782</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>45302</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>45334</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45700</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>45316</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45319</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>45771</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>45707</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>45895</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>46069</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>46089</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46291</v>
+        <v>46292</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>

--- a/Översikt HOFORS.xlsx
+++ b/Översikt HOFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46064</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>45784</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>46164</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45299</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>46079</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>46163</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>46085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>46266</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45316</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45163</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45813</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>44623</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>45860</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>46199</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44816</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>46025</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>46043</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>45895</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45895</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>46095</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
         <v>45813</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>46154</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>45935</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>46177</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3365,7 +3365,7 @@
         <v>45874</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>46199</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44102</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44169</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>44585</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>45317</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45701</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>45895</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45895</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>46142</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>46125</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>44649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>44559</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>45531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>45127</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>44473</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>45488</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>45007</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>45917</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>45924</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>45589</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5797,7 +5797,7 @@
         <v>46091</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5906,7 +5906,7 @@
         <v>45453</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>45813</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6126,7 +6126,7 @@
         <v>45813</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>45813</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>45813</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>45477</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>45534</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>45924</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>45348</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6899,7 +6899,7 @@
         <v>45860</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7009,7 +7009,7 @@
         <v>45870</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7119,7 +7119,7 @@
         <v>46183</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7229,7 +7229,7 @@
         <v>45874</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7339,7 +7339,7 @@
         <v>46196</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7449,7 +7449,7 @@
         <v>45531</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7559,7 +7559,7 @@
         <v>45881</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7669,7 +7669,7 @@
         <v>45597</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7774,7 +7774,7 @@
         <v>46252</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7888,7 +7888,7 @@
         <v>44624</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7993,7 +7993,7 @@
         <v>46217</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8103,7 +8103,7 @@
         <v>46217</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8213,7 +8213,7 @@
         <v>46262</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8323,7 +8323,7 @@
         <v>45477</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>44928</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8547,7 +8547,7 @@
         <v>45701</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>45727</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>45706</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>44868</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>44582</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>44501</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>44512</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>44873</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>44868</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>44692</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9402,7 +9402,7 @@
         <v>45387</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9475,7 +9475,7 @@
         <v>45531</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9553,7 +9553,7 @@
         <v>45446</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9626,7 +9626,7 @@
         <v>45453</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9704,7 +9704,7 @@
         <v>44810</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9777,7 +9777,7 @@
         <v>44487</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9850,7 +9850,7 @@
         <v>45490</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9928,7 +9928,7 @@
         <v>45271</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>45884</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10074,7 +10074,7 @@
         <v>46029</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10147,7 +10147,7 @@
         <v>46030</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10220,7 +10220,7 @@
         <v>45792</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10293,7 +10293,7 @@
         <v>45614</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>45523</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10439,7 +10439,7 @@
         <v>46029</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>45887</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10590,7 +10590,7 @@
         <v>45173</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>46036</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10741,7 +10741,7 @@
         <v>45376</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>46037</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>45895</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>46042</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>45488</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>45488</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>45387</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>44489</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11340,7 +11340,7 @@
         <v>46050</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11413,7 +11413,7 @@
         <v>45343</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11486,7 +11486,7 @@
         <v>45506</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11564,7 +11564,7 @@
         <v>46061</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>45917</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11715,7 +11715,7 @@
         <v>46047</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>45232</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>45930</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>45929</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -12007,7 +12007,7 @@
         <v>46083</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>45534</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12158,7 +12158,7 @@
         <v>45933</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>45935</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12314,7 +12314,7 @@
         <v>45933</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12392,7 +12392,7 @@
         <v>45816</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>45933</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>45933</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12626,7 +12626,7 @@
         <v>44671</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12699,7 +12699,7 @@
         <v>46092</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12777,7 +12777,7 @@
         <v>45587</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12850,7 +12850,7 @@
         <v>45453</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12928,7 +12928,7 @@
         <v>45947</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -13006,7 +13006,7 @@
         <v>46107</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13084,7 +13084,7 @@
         <v>44967</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13157,7 +13157,7 @@
         <v>45956</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13230,7 +13230,7 @@
         <v>46115</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13303,7 +13303,7 @@
         <v>45966</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>46064</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>44994</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>46085</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13600,7 +13600,7 @@
         <v>45967</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13673,7 +13673,7 @@
         <v>45967</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45967</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13819,7 +13819,7 @@
         <v>45969</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>45969</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13965,7 +13965,7 @@
         <v>46091</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>45980</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>45980</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>45980</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>46133</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>45980</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>45986</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>45986</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14559,7 +14559,7 @@
         <v>45728</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14637,7 +14637,7 @@
         <v>46085</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14710,7 +14710,7 @@
         <v>44810</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14783,7 +14783,7 @@
         <v>46080</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>45912</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>46000</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>46002</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15085,7 +15085,7 @@
         <v>45219</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15158,7 +15158,7 @@
         <v>46105</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>45463</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>45755</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>44810</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>46113</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>45805</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
         <v>45069</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15689,7 +15689,7 @@
         <v>45476</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15762,7 +15762,7 @@
         <v>46092</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15840,7 +15840,7 @@
         <v>45523</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45523</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>45629</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16059,7 +16059,7 @@
         <v>45538</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16132,7 +16132,7 @@
         <v>46042</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16205,7 +16205,7 @@
         <v>45833</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16278,7 +16278,7 @@
         <v>46042</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16351,7 +16351,7 @@
         <v>45792</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16424,7 +16424,7 @@
         <v>45835</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16502,7 +16502,7 @@
         <v>44986</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16580,7 +16580,7 @@
         <v>46162</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>46162</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>45117</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16809,7 +16809,7 @@
         <v>46167</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>46169</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16965,7 +16965,7 @@
         <v>46169</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>44977</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17111,7 +17111,7 @@
         <v>45475</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>45868</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17262,7 +17262,7 @@
         <v>45117</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>45007</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17413,7 +17413,7 @@
         <v>45085</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17491,7 +17491,7 @@
         <v>46183</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17569,7 +17569,7 @@
         <v>46183</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17647,7 +17647,7 @@
         <v>45145</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>45877</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17798,7 +17798,7 @@
         <v>46196</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>46196</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17954,7 +17954,7 @@
         <v>46199</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>45159</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18105,7 +18105,7 @@
         <v>45156</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18178,7 +18178,7 @@
         <v>46211</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45531</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>45709</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18402,7 +18402,7 @@
         <v>44680</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18475,7 +18475,7 @@
         <v>46259</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18553,7 +18553,7 @@
         <v>46216</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18631,7 +18631,7 @@
         <v>46216</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>46260</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>46219</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18860,7 +18860,7 @@
         <v>45127</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18938,7 +18938,7 @@
         <v>45755</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>45252</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19089,7 +19089,7 @@
         <v>45280</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19162,7 +19162,7 @@
         <v>46268</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19235,7 +19235,7 @@
         <v>45250</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19308,7 +19308,7 @@
         <v>46272</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19381,7 +19381,7 @@
         <v>46272</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>44812</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>46274</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19600,7 +19600,7 @@
         <v>46274</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19673,7 +19673,7 @@
         <v>46021</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19746,7 +19746,7 @@
         <v>45202</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>44526</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19892,7 +19892,7 @@
         <v>46259</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>44473</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>45188</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>45587</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20199,7 +20199,7 @@
         <v>46289</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20272,7 +20272,7 @@
         <v>44624</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>45117</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20418,7 +20418,7 @@
         <v>45343</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20491,7 +20491,7 @@
         <v>44484</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20564,7 +20564,7 @@
         <v>45587</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20642,7 +20642,7 @@
         <v>45127</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20720,7 +20720,7 @@
         <v>45439</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>45439</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20876,7 +20876,7 @@
         <v>45674</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20949,7 +20949,7 @@
         <v>45125</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -21022,7 +21022,7 @@
         <v>45630</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21095,7 +21095,7 @@
         <v>45531</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21173,7 +21173,7 @@
         <v>45677</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>45684</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21319,7 +21319,7 @@
         <v>45477</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21397,7 +21397,7 @@
         <v>45782</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21470,7 +21470,7 @@
         <v>45302</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21543,7 +21543,7 @@
         <v>45334</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45700</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>45316</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45319</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>45771</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>45707</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>45895</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>46069</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>46089</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>

--- a/Översikt HOFORS.xlsx
+++ b/Översikt HOFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46064</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>45784</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>46164</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45299</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>46079</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>46163</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>46085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>46266</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45316</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45163</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45813</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>44623</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>45860</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>46199</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44816</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2356,7 +2356,7 @@
     <row r="17" ht="15" customHeight="1">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A 27436-2025</t>
+          <t>A 186-2026</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="D17" s="1" t="n">
-        <v>45813</v>
+        <v>46025</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2385,16 +2385,11 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I17" t="n">
-        <v>5.5</v>
+        <v>6.7</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K17" t="n">
         <v>0</v>
@@ -2403,7 +2398,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -2415,10 +2410,10 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S17" t="n">
         <v>2</v>
@@ -2427,379 +2422,384 @@
         <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Knärot
+Timmerticka</t>
+        </is>
+      </c>
+      <c r="W17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 186-2026 artfynd.xlsx", "A 186-2026")</f>
+        <v/>
+      </c>
+      <c r="X17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 186-2026 karta.png", "A 186-2026")</f>
+        <v/>
+      </c>
+      <c r="Y17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 186-2026 georefererad karta.tif", "A 186-2026")</f>
+        <v/>
+      </c>
+      <c r="Z17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/knärot/A 186-2026 karta knärot.png", "A 186-2026")</f>
+        <v/>
+      </c>
+      <c r="AA17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 186-2026 FSC-klagomål.docx", "A 186-2026")</f>
+        <v/>
+      </c>
+      <c r="AB17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 186-2026 FSC-klagomål mail.docx", "A 186-2026")</f>
+        <v/>
+      </c>
+      <c r="AC17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 186-2026 tillsynsbegäran.docx", "A 186-2026")</f>
+        <v/>
+      </c>
+      <c r="AD17">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 186-2026 tillsynsbegäran mail.docx", "A 186-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>A 27436-2025</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="n">
+        <v>45813</v>
+      </c>
+      <c r="E18" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>GÄVLEBORGS LÄN</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>HOFORS</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="J18" t="n">
+        <v>2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>Mattlummer
 Revlummer</t>
         </is>
       </c>
-      <c r="W17">
+      <c r="W18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 27436-2025 artfynd.xlsx", "A 27436-2025")</f>
         <v/>
       </c>
-      <c r="X17">
+      <c r="X18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 27436-2025 karta.png", "A 27436-2025")</f>
         <v/>
       </c>
-      <c r="Y17">
+      <c r="Y18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 27436-2025 georefererad karta.tif", "A 27436-2025")</f>
         <v/>
       </c>
-      <c r="AA17">
+      <c r="AA18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 27436-2025 FSC-klagomål.docx", "A 27436-2025")</f>
         <v/>
       </c>
-      <c r="AB17">
+      <c r="AB18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 27436-2025 FSC-klagomål mail.docx", "A 27436-2025")</f>
         <v/>
       </c>
-      <c r="AC17">
+      <c r="AC18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 27436-2025 tillsynsbegäran.docx", "A 27436-2025")</f>
         <v/>
       </c>
-      <c r="AD17">
+      <c r="AD18">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 27436-2025 tillsynsbegäran mail.docx", "A 27436-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="18" ht="15" customHeight="1">
-      <c r="A18" t="inlineStr">
+    <row r="19" ht="15" customHeight="1">
+      <c r="A19" t="inlineStr">
         <is>
           <t>A 40393-2025</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D18" s="1" t="n">
+      <c r="D19" s="1" t="n">
         <v>45895</v>
       </c>
-      <c r="E18" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>GÄVLEBORGS LÄN</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>HOFORS</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
+      <c r="E19" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>GÄVLEBORGS LÄN</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>HOFORS</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I18" t="n">
+      <c r="I19" t="n">
         <v>2.9</v>
       </c>
-      <c r="J18" t="n">
-        <v>1</v>
-      </c>
-      <c r="K18" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="n">
+      <c r="J19" t="n">
+        <v>1</v>
+      </c>
+      <c r="K19" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="n">
         <v>2</v>
       </c>
-      <c r="T18" t="n">
+      <c r="T19" t="n">
         <v>2</v>
       </c>
-      <c r="U18" t="n">
+      <c r="U19" t="n">
         <v>2</v>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>Svarta vinbär
 Huggorm</t>
         </is>
       </c>
-      <c r="W18">
+      <c r="W19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 40393-2025 artfynd.xlsx", "A 40393-2025")</f>
         <v/>
       </c>
-      <c r="X18">
+      <c r="X19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 40393-2025 karta.png", "A 40393-2025")</f>
         <v/>
       </c>
-      <c r="Y18">
+      <c r="Y19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 40393-2025 georefererad karta.tif", "A 40393-2025")</f>
         <v/>
       </c>
-      <c r="AA18">
+      <c r="AA19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 40393-2025 FSC-klagomål.docx", "A 40393-2025")</f>
         <v/>
       </c>
-      <c r="AB18">
+      <c r="AB19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 40393-2025 FSC-klagomål mail.docx", "A 40393-2025")</f>
         <v/>
       </c>
-      <c r="AC18">
+      <c r="AC19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 40393-2025 tillsynsbegäran.docx", "A 40393-2025")</f>
         <v/>
       </c>
-      <c r="AD18">
+      <c r="AD19">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 40393-2025 tillsynsbegäran mail.docx", "A 40393-2025")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="15" customHeight="1">
-      <c r="A19" t="inlineStr">
+    <row r="20" ht="15" customHeight="1">
+      <c r="A20" t="inlineStr">
         <is>
           <t>A 40401-2025</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
         <is>
           <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
-      <c r="D19" s="1" t="n">
+      <c r="D20" s="1" t="n">
         <v>45895</v>
       </c>
-      <c r="E19" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>GÄVLEBORGS LÄN</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>HOFORS</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
+      <c r="E20" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>GÄVLEBORGS LÄN</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>HOFORS</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
         <is>
           <t>Sveaskog</t>
         </is>
       </c>
-      <c r="I19" t="n">
+      <c r="I20" t="n">
         <v>12.6</v>
       </c>
-      <c r="J19" t="n">
-        <v>1</v>
-      </c>
-      <c r="K19" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" t="n">
         <v>2</v>
       </c>
-      <c r="T19" t="n">
+      <c r="T20" t="n">
         <v>2</v>
       </c>
-      <c r="U19" t="n">
+      <c r="U20" t="n">
         <v>2</v>
       </c>
-      <c r="V19" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>Svarta vinbär
 Gullviva</t>
         </is>
       </c>
-      <c r="W19">
+      <c r="W20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 40401-2025 artfynd.xlsx", "A 40401-2025")</f>
         <v/>
       </c>
-      <c r="X19">
+      <c r="X20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 40401-2025 karta.png", "A 40401-2025")</f>
         <v/>
       </c>
-      <c r="Y19">
+      <c r="Y20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 40401-2025 georefererad karta.tif", "A 40401-2025")</f>
         <v/>
       </c>
-      <c r="AA19">
+      <c r="AA20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 40401-2025 FSC-klagomål.docx", "A 40401-2025")</f>
         <v/>
       </c>
-      <c r="AB19">
+      <c r="AB20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 40401-2025 FSC-klagomål mail.docx", "A 40401-2025")</f>
         <v/>
       </c>
-      <c r="AC19">
+      <c r="AC20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 40401-2025 tillsynsbegäran.docx", "A 40401-2025")</f>
         <v/>
       </c>
-      <c r="AD19">
+      <c r="AD20">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 40401-2025 tillsynsbegäran mail.docx", "A 40401-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>A 186-2026</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>46025</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>GÄVLEBORGS LÄN</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>HOFORS</t>
-        </is>
-      </c>
-      <c r="I20" t="n">
-        <v>6.7</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1</v>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1</v>
-      </c>
-      <c r="V20" s="2" t="inlineStr">
-        <is>
-          <t>Knärot
-Timmerticka</t>
-        </is>
-      </c>
-      <c r="W20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 186-2026 artfynd.xlsx", "A 186-2026")</f>
-        <v/>
-      </c>
-      <c r="X20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 186-2026 karta.png", "A 186-2026")</f>
-        <v/>
-      </c>
-      <c r="Y20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 186-2026 georefererad karta.tif", "A 186-2026")</f>
-        <v/>
-      </c>
-      <c r="Z20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/knärot/A 186-2026 karta knärot.png", "A 186-2026")</f>
-        <v/>
-      </c>
-      <c r="AA20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 186-2026 FSC-klagomål.docx", "A 186-2026")</f>
-        <v/>
-      </c>
-      <c r="AB20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 186-2026 FSC-klagomål mail.docx", "A 186-2026")</f>
-        <v/>
-      </c>
-      <c r="AC20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 186-2026 tillsynsbegäran.docx", "A 186-2026")</f>
-        <v/>
-      </c>
-      <c r="AD20">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 186-2026 tillsynsbegäran mail.docx", "A 186-2026")</f>
         <v/>
       </c>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A 37011-2025</t>
+          <t>A 3870-2026</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2813,10 +2813,10 @@
         </is>
       </c>
       <c r="D21" s="1" t="n">
-        <v>45874</v>
+        <v>46043</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2834,22 +2834,22 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="J21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O21" t="n">
         <v>0</v>
@@ -2858,7 +2858,7 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="R21" t="n">
         <v>1</v>
@@ -2867,158 +2867,158 @@
         <v>2</v>
       </c>
       <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Skogsalm
+Strutbräken</t>
+        </is>
+      </c>
+      <c r="W21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 3870-2026 artfynd.xlsx", "A 3870-2026")</f>
+        <v/>
+      </c>
+      <c r="X21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 3870-2026 karta.png", "A 3870-2026")</f>
+        <v/>
+      </c>
+      <c r="Y21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 3870-2026 georefererad karta.tif", "A 3870-2026")</f>
+        <v/>
+      </c>
+      <c r="AA21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 3870-2026 FSC-klagomål.docx", "A 3870-2026")</f>
+        <v/>
+      </c>
+      <c r="AB21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 3870-2026 FSC-klagomål mail.docx", "A 3870-2026")</f>
+        <v/>
+      </c>
+      <c r="AC21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 3870-2026 tillsynsbegäran.docx", "A 3870-2026")</f>
+        <v/>
+      </c>
+      <c r="AD21">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 3870-2026 tillsynsbegäran mail.docx", "A 3870-2026")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" ht="15" customHeight="1">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>A 37011-2025</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>avverkningsanmälan</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Föryngringsavverkning</t>
+        </is>
+      </c>
+      <c r="D22" s="1" t="n">
+        <v>45874</v>
+      </c>
+      <c r="E22" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>GÄVLEBORGS LÄN</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>HOFORS</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" t="n">
+        <v>1</v>
+      </c>
+      <c r="K22" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1</v>
+      </c>
+      <c r="M22" t="n">
+        <v>1</v>
+      </c>
+      <c r="N22" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2</v>
+      </c>
+      <c r="R22" t="n">
+        <v>1</v>
+      </c>
+      <c r="S22" t="n">
+        <v>2</v>
+      </c>
+      <c r="T22" t="n">
         <v>5</v>
       </c>
-      <c r="U21" t="n">
+      <c r="U22" t="n">
         <v>4</v>
       </c>
-      <c r="V21" s="2" t="inlineStr">
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>Knärot
 Dropptaggsvamp</t>
         </is>
       </c>
-      <c r="W21">
+      <c r="W22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 37011-2025 artfynd.xlsx", "A 37011-2025")</f>
         <v/>
       </c>
-      <c r="X21">
+      <c r="X22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 37011-2025 karta.png", "A 37011-2025")</f>
         <v/>
       </c>
-      <c r="Y21">
+      <c r="Y22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 37011-2025 georefererad karta.tif", "A 37011-2025")</f>
         <v/>
       </c>
-      <c r="Z21">
+      <c r="Z22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/knärot/A 37011-2025 karta knärot.png", "A 37011-2025")</f>
         <v/>
       </c>
-      <c r="AA21">
+      <c r="AA22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 37011-2025 FSC-klagomål.docx", "A 37011-2025")</f>
         <v/>
       </c>
-      <c r="AB21">
+      <c r="AB22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 37011-2025 FSC-klagomål mail.docx", "A 37011-2025")</f>
         <v/>
       </c>
-      <c r="AC21">
+      <c r="AC22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 37011-2025 tillsynsbegäran.docx", "A 37011-2025")</f>
         <v/>
       </c>
-      <c r="AD21">
+      <c r="AD22">
         <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 37011-2025 tillsynsbegäran mail.docx", "A 37011-2025")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" ht="15" customHeight="1">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>A 3870-2026</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>avverkningsanmälan</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Föryngringsavverkning</t>
-        </is>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>46043</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>46294</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>GÄVLEBORGS LÄN</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>HOFORS</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
-      <c r="I22" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>1</v>
-      </c>
-      <c r="L22" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" t="n">
-        <v>1</v>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
-      <c r="P22" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q22" t="n">
-        <v>1</v>
-      </c>
-      <c r="R22" t="n">
-        <v>1</v>
-      </c>
-      <c r="S22" t="n">
-        <v>2</v>
-      </c>
-      <c r="T22" t="n">
-        <v>2</v>
-      </c>
-      <c r="U22" t="n">
-        <v>1</v>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>Skogsalm
-Strutbräken</t>
-        </is>
-      </c>
-      <c r="W22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 3870-2026 artfynd.xlsx", "A 3870-2026")</f>
-        <v/>
-      </c>
-      <c r="X22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 3870-2026 karta.png", "A 3870-2026")</f>
-        <v/>
-      </c>
-      <c r="Y22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 3870-2026 georefererad karta.tif", "A 3870-2026")</f>
-        <v/>
-      </c>
-      <c r="AA22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 3870-2026 FSC-klagomål.docx", "A 3870-2026")</f>
-        <v/>
-      </c>
-      <c r="AB22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 3870-2026 FSC-klagomål mail.docx", "A 3870-2026")</f>
-        <v/>
-      </c>
-      <c r="AC22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 3870-2026 tillsynsbegäran.docx", "A 3870-2026")</f>
-        <v/>
-      </c>
-      <c r="AD22">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 3870-2026 tillsynsbegäran mail.docx", "A 3870-2026")</f>
         <v/>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
         <v>46095</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>46154</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>45935</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>46177</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>46199</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44102</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44169</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>44585</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>45317</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45701</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>45895</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45895</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>46142</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>46125</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>44649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>44559</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 27431-2025</t>
+          <t>A 35514-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45813</v>
+        <v>45531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>3.4</v>
+        <v>6.5</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -4941,10 +4941,10 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
         <v>0</v>
@@ -4959,55 +4959,59 @@
         <v>1</v>
       </c>
       <c r="R40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U40" t="n">
         <v>0</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Väddnätfjäril</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 27431-2025 artfynd.xlsx", "A 27431-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 35514-2024 artfynd.xlsx", "A 35514-2024")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 27431-2025 karta.png", "A 27431-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 35514-2024 karta.png", "A 35514-2024")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 27431-2025 georefererad karta.tif", "A 27431-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 35514-2024 georefererad karta.tif", "A 35514-2024")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 27431-2025 FSC-klagomål.docx", "A 27431-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 35514-2024 FSC-klagomål.docx", "A 35514-2024")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 27431-2025 FSC-klagomål mail.docx", "A 27431-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 35514-2024 FSC-klagomål mail.docx", "A 35514-2024")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 27431-2025 tillsynsbegäran.docx", "A 27431-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 35514-2024 tillsynsbegäran.docx", "A 35514-2024")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 27431-2025 tillsynsbegäran mail.docx", "A 27431-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 35514-2024 tillsynsbegäran mail.docx", "A 35514-2024")</f>
+        <v/>
+      </c>
+      <c r="AE40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/fåglar/A 35514-2024 prioriterade fågelarter.docx", "A 35514-2024")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 27438-2025</t>
+          <t>A 33298-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5021,10 +5025,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>45813</v>
+        <v>45127</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5042,13 +5046,13 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>0.9</v>
+        <v>5.6</v>
       </c>
       <c r="J41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -5075,49 +5079,49 @@
         <v>1</v>
       </c>
       <c r="T41" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 27438-2025 artfynd.xlsx", "A 27438-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 33298-2023 artfynd.xlsx", "A 33298-2023")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 27438-2025 karta.png", "A 27438-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 33298-2023 karta.png", "A 33298-2023")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 27438-2025 georefererad karta.tif", "A 27438-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 33298-2023 georefererad karta.tif", "A 33298-2023")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 27438-2025 FSC-klagomål.docx", "A 27438-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 33298-2023 FSC-klagomål.docx", "A 33298-2023")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 27438-2025 FSC-klagomål mail.docx", "A 27438-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 33298-2023 FSC-klagomål mail.docx", "A 33298-2023")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 27438-2025 tillsynsbegäran.docx", "A 27438-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 33298-2023 tillsynsbegäran.docx", "A 33298-2023")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 27438-2025 tillsynsbegäran mail.docx", "A 27438-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 33298-2023 tillsynsbegäran mail.docx", "A 33298-2023")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 27432-2025</t>
+          <t>A 54828-2021</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5127,14 +5131,14 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45813</v>
+        <v>44473</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5148,11 +5152,11 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I42" t="n">
-        <v>3.6</v>
+        <v>5.1</v>
       </c>
       <c r="J42" t="n">
         <v>1</v>
@@ -5164,7 +5168,7 @@
         <v>0</v>
       </c>
       <c r="M42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N42" t="n">
         <v>0</v>
@@ -5176,58 +5180,62 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S42" t="n">
         <v>1</v>
       </c>
       <c r="T42" t="n">
-        <v>1</v>
+        <v>64</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>64</v>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 27432-2025 artfynd.xlsx", "A 27432-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 54828-2021 artfynd.xlsx", "A 54828-2021")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 27432-2025 karta.png", "A 27432-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 54828-2021 karta.png", "A 54828-2021")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 27432-2025 georefererad karta.tif", "A 27432-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 54828-2021 georefererad karta.tif", "A 54828-2021")</f>
+        <v/>
+      </c>
+      <c r="Z42">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/knärot/A 54828-2021 karta knärot.png", "A 54828-2021")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 27432-2025 FSC-klagomål.docx", "A 27432-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 54828-2021 FSC-klagomål.docx", "A 54828-2021")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 27432-2025 FSC-klagomål mail.docx", "A 27432-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 54828-2021 FSC-klagomål mail.docx", "A 54828-2021")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 27432-2025 tillsynsbegäran.docx", "A 27432-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 54828-2021 tillsynsbegäran.docx", "A 54828-2021")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 27432-2025 tillsynsbegäran mail.docx", "A 27432-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 54828-2021 tillsynsbegäran mail.docx", "A 54828-2021")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 27441-2025</t>
+          <t>A 30008-2024</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5241,10 +5249,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45813</v>
+        <v>45488</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5262,13 +5270,13 @@
         </is>
       </c>
       <c r="I43" t="n">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="J43" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L43" t="n">
         <v>0</v>
@@ -5298,46 +5306,46 @@
         <v>1</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 27441-2025 artfynd.xlsx", "A 27441-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 30008-2024 artfynd.xlsx", "A 30008-2024")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 27441-2025 karta.png", "A 27441-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 30008-2024 karta.png", "A 30008-2024")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 27441-2025 georefererad karta.tif", "A 27441-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 30008-2024 georefererad karta.tif", "A 30008-2024")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 27441-2025 FSC-klagomål.docx", "A 27441-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 30008-2024 FSC-klagomål.docx", "A 30008-2024")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 27441-2025 FSC-klagomål mail.docx", "A 27441-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 30008-2024 FSC-klagomål mail.docx", "A 30008-2024")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 27441-2025 tillsynsbegäran.docx", "A 27441-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 30008-2024 tillsynsbegäran.docx", "A 30008-2024")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 27441-2025 tillsynsbegäran mail.docx", "A 27441-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 30008-2024 tillsynsbegäran mail.docx", "A 30008-2024")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 28392-2024</t>
+          <t>A 27438-2025</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5351,10 +5359,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45477</v>
+        <v>45813</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5372,7 +5380,7 @@
         </is>
       </c>
       <c r="I44" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J44" t="n">
         <v>1</v>
@@ -5408,7 +5416,7 @@
         <v>2</v>
       </c>
       <c r="U44" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
@@ -5416,38 +5424,38 @@
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 28392-2024 artfynd.xlsx", "A 28392-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 27438-2025 artfynd.xlsx", "A 27438-2025")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 28392-2024 karta.png", "A 28392-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 27438-2025 karta.png", "A 27438-2025")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 28392-2024 georefererad karta.tif", "A 28392-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 27438-2025 georefererad karta.tif", "A 27438-2025")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 28392-2024 FSC-klagomål.docx", "A 28392-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 27438-2025 FSC-klagomål.docx", "A 27438-2025")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 28392-2024 FSC-klagomål mail.docx", "A 28392-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 27438-2025 FSC-klagomål mail.docx", "A 27438-2025")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 28392-2024 tillsynsbegäran.docx", "A 28392-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 27438-2025 tillsynsbegäran.docx", "A 27438-2025")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 28392-2024 tillsynsbegäran mail.docx", "A 28392-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 27438-2025 tillsynsbegäran mail.docx", "A 27438-2025")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 44694-2025</t>
+          <t>A 27432-2025</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5461,10 +5469,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45917</v>
+        <v>45813</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5482,16 +5490,16 @@
         </is>
       </c>
       <c r="I45" t="n">
-        <v>12.1</v>
+        <v>3.6</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5506,7 +5514,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5522,42 +5530,42 @@
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 44694-2025 artfynd.xlsx", "A 44694-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 27432-2025 artfynd.xlsx", "A 27432-2025")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 44694-2025 karta.png", "A 44694-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 27432-2025 karta.png", "A 27432-2025")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 44694-2025 georefererad karta.tif", "A 44694-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 27432-2025 georefererad karta.tif", "A 27432-2025")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 44694-2025 FSC-klagomål.docx", "A 44694-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 27432-2025 FSC-klagomål.docx", "A 27432-2025")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 44694-2025 FSC-klagomål mail.docx", "A 44694-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 27432-2025 FSC-klagomål mail.docx", "A 27432-2025")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 44694-2025 tillsynsbegäran.docx", "A 44694-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 27432-2025 tillsynsbegäran.docx", "A 27432-2025")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 44694-2025 tillsynsbegäran mail.docx", "A 44694-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 27432-2025 tillsynsbegäran mail.docx", "A 27432-2025")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 234-2023</t>
+          <t>A 27441-2025</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5571,10 +5579,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>44928</v>
+        <v>45813</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5592,7 +5600,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>5.1</v>
+        <v>1.2</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
@@ -5604,7 +5612,7 @@
         <v>0</v>
       </c>
       <c r="M46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N46" t="n">
         <v>0</v>
@@ -5616,10 +5624,10 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5628,50 +5636,46 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 234-2023 artfynd.xlsx", "A 234-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 27441-2025 artfynd.xlsx", "A 27441-2025")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 234-2023 karta.png", "A 234-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 27441-2025 karta.png", "A 27441-2025")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 234-2023 georefererad karta.tif", "A 234-2023")</f>
-        <v/>
-      </c>
-      <c r="Z46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/knärot/A 234-2023 karta knärot.png", "A 234-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 27441-2025 georefererad karta.tif", "A 27441-2025")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 234-2023 FSC-klagomål.docx", "A 234-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 27441-2025 FSC-klagomål.docx", "A 27441-2025")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 234-2023 FSC-klagomål mail.docx", "A 234-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 27441-2025 FSC-klagomål mail.docx", "A 27441-2025")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 234-2023 tillsynsbegäran.docx", "A 234-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 27441-2025 tillsynsbegäran.docx", "A 27441-2025")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 234-2023 tillsynsbegäran mail.docx", "A 234-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 27441-2025 tillsynsbegäran mail.docx", "A 27441-2025")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 28397-2024</t>
+          <t>A 27431-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5685,10 +5689,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>45477</v>
+        <v>45813</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5706,7 +5710,7 @@
         </is>
       </c>
       <c r="I47" t="n">
-        <v>5</v>
+        <v>3.4</v>
       </c>
       <c r="J47" t="n">
         <v>1</v>
@@ -5718,7 +5722,7 @@
         <v>0</v>
       </c>
       <c r="M47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N47" t="n">
         <v>0</v>
@@ -5730,58 +5734,58 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 28397-2024 artfynd.xlsx", "A 28397-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 27431-2025 artfynd.xlsx", "A 27431-2025")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 28397-2024 karta.png", "A 28397-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 27431-2025 karta.png", "A 27431-2025")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 28397-2024 georefererad karta.tif", "A 28397-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 27431-2025 georefererad karta.tif", "A 27431-2025")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 28397-2024 FSC-klagomål.docx", "A 28397-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 27431-2025 FSC-klagomål.docx", "A 27431-2025")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 28397-2024 FSC-klagomål mail.docx", "A 28397-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 27431-2025 FSC-klagomål mail.docx", "A 27431-2025")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 28397-2024 tillsynsbegäran.docx", "A 28397-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 27431-2025 tillsynsbegäran.docx", "A 27431-2025")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 28397-2024 tillsynsbegäran mail.docx", "A 28397-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 27431-2025 tillsynsbegäran mail.docx", "A 27431-2025")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 7543-2024</t>
+          <t>A 13745-2023</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5795,10 +5799,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45348</v>
+        <v>45007</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5810,17 +5814,22 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I48" t="n">
-        <v>3.2</v>
+        <v>0.5</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -5835,7 +5844,7 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -5844,49 +5853,49 @@
         <v>1</v>
       </c>
       <c r="T48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U48" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 7543-2024 artfynd.xlsx", "A 7543-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 13745-2023 artfynd.xlsx", "A 13745-2023")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 7543-2024 karta.png", "A 7543-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 13745-2023 karta.png", "A 13745-2023")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 7543-2024 georefererad karta.tif", "A 7543-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 13745-2023 georefererad karta.tif", "A 13745-2023")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 7543-2024 FSC-klagomål.docx", "A 7543-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 13745-2023 FSC-klagomål.docx", "A 13745-2023")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 7543-2024 FSC-klagomål mail.docx", "A 7543-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 13745-2023 FSC-klagomål mail.docx", "A 13745-2023")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 7543-2024 tillsynsbegäran.docx", "A 7543-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 13745-2023 tillsynsbegäran.docx", "A 13745-2023")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 7543-2024 tillsynsbegäran mail.docx", "A 7543-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 13745-2023 tillsynsbegäran mail.docx", "A 13745-2023")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 54828-2021</t>
+          <t>A 44694-2025</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5896,14 +5905,14 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>44473</v>
+        <v>45917</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5917,23 +5926,23 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I49" t="n">
-        <v>5.1</v>
+        <v>12.1</v>
       </c>
       <c r="J49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K49" t="n">
         <v>0</v>
       </c>
       <c r="L49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N49" t="n">
         <v>0</v>
@@ -5948,59 +5957,55 @@
         <v>1</v>
       </c>
       <c r="R49" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
       </c>
       <c r="T49" t="n">
-        <v>64</v>
+        <v>1</v>
       </c>
       <c r="U49" t="n">
-        <v>64</v>
+        <v>0</v>
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 54828-2021 artfynd.xlsx", "A 54828-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 44694-2025 artfynd.xlsx", "A 44694-2025")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 54828-2021 karta.png", "A 54828-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 44694-2025 karta.png", "A 44694-2025")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 54828-2021 georefererad karta.tif", "A 54828-2021")</f>
-        <v/>
-      </c>
-      <c r="Z49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/knärot/A 54828-2021 karta knärot.png", "A 54828-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 44694-2025 georefererad karta.tif", "A 44694-2025")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 54828-2021 FSC-klagomål.docx", "A 54828-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 44694-2025 FSC-klagomål.docx", "A 44694-2025")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 54828-2021 FSC-klagomål mail.docx", "A 54828-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 44694-2025 FSC-klagomål mail.docx", "A 44694-2025")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 54828-2021 tillsynsbegäran.docx", "A 54828-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 44694-2025 tillsynsbegäran.docx", "A 44694-2025")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 54828-2021 tillsynsbegäran mail.docx", "A 54828-2021")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 44694-2025 tillsynsbegäran mail.docx", "A 44694-2025")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 35743-2025</t>
+          <t>A 48063-2024</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6014,10 +6019,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>45860</v>
+        <v>45589</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6029,19 +6034,14 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>1.4</v>
+        <v>3.9</v>
       </c>
       <c r="J50" t="n">
         <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -6075,42 +6075,42 @@
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 35743-2025 artfynd.xlsx", "A 35743-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 48063-2024 artfynd.xlsx", "A 48063-2024")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 35743-2025 karta.png", "A 35743-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 48063-2024 karta.png", "A 48063-2024")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 35743-2025 georefererad karta.tif", "A 35743-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 48063-2024 georefererad karta.tif", "A 48063-2024")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 35743-2025 FSC-klagomål.docx", "A 35743-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 48063-2024 FSC-klagomål.docx", "A 48063-2024")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 35743-2025 FSC-klagomål mail.docx", "A 35743-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 48063-2024 FSC-klagomål mail.docx", "A 48063-2024")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 35743-2025 tillsynsbegäran.docx", "A 35743-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 48063-2024 tillsynsbegäran.docx", "A 48063-2024")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 35743-2025 tillsynsbegäran mail.docx", "A 35743-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 48063-2024 tillsynsbegäran mail.docx", "A 48063-2024")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 36606-2025</t>
+          <t>A 23354-2024</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6124,10 +6124,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45870</v>
+        <v>45453</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6145,16 +6145,16 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>13.3</v>
+        <v>2</v>
       </c>
       <c r="J51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K51" t="n">
         <v>0</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -6169,7 +6169,7 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -6181,46 +6181,46 @@
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 36606-2025 artfynd.xlsx", "A 36606-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 23354-2024 artfynd.xlsx", "A 23354-2024")</f>
         <v/>
       </c>
       <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 36606-2025 karta.png", "A 36606-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 23354-2024 karta.png", "A 23354-2024")</f>
         <v/>
       </c>
       <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 36606-2025 georefererad karta.tif", "A 36606-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 23354-2024 georefererad karta.tif", "A 23354-2024")</f>
         <v/>
       </c>
       <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 36606-2025 FSC-klagomål.docx", "A 36606-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 23354-2024 FSC-klagomål.docx", "A 23354-2024")</f>
         <v/>
       </c>
       <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 36606-2025 FSC-klagomål mail.docx", "A 36606-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 23354-2024 FSC-klagomål mail.docx", "A 23354-2024")</f>
         <v/>
       </c>
       <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 36606-2025 tillsynsbegäran.docx", "A 36606-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 23354-2024 tillsynsbegäran.docx", "A 23354-2024")</f>
         <v/>
       </c>
       <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 36606-2025 tillsynsbegäran mail.docx", "A 36606-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 23354-2024 tillsynsbegäran mail.docx", "A 23354-2024")</f>
         <v/>
       </c>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" t="inlineStr">
         <is>
-          <t>A 23354-2024</t>
+          <t>A 7543-2024</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -6234,10 +6234,10 @@
         </is>
       </c>
       <c r="D52" s="1" t="n">
-        <v>45453</v>
+        <v>45348</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6249,88 +6249,83 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I52" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J52" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" t="n">
+        <v>1</v>
+      </c>
+      <c r="L52" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="P52" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="n">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
         <v>2</v>
       </c>
-      <c r="J52" t="n">
-        <v>1</v>
-      </c>
-      <c r="K52" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" t="n">
-        <v>0</v>
-      </c>
-      <c r="P52" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="n">
-        <v>1</v>
-      </c>
-      <c r="T52" t="n">
-        <v>1</v>
-      </c>
       <c r="U52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V52" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="W52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 23354-2024 artfynd.xlsx", "A 23354-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 7543-2024 artfynd.xlsx", "A 7543-2024")</f>
         <v/>
       </c>
       <c r="X52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 23354-2024 karta.png", "A 23354-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 7543-2024 karta.png", "A 7543-2024")</f>
         <v/>
       </c>
       <c r="Y52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 23354-2024 georefererad karta.tif", "A 23354-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 7543-2024 georefererad karta.tif", "A 7543-2024")</f>
         <v/>
       </c>
       <c r="AA52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 23354-2024 FSC-klagomål.docx", "A 23354-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 7543-2024 FSC-klagomål.docx", "A 7543-2024")</f>
         <v/>
       </c>
       <c r="AB52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 23354-2024 FSC-klagomål mail.docx", "A 23354-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 7543-2024 FSC-klagomål mail.docx", "A 7543-2024")</f>
         <v/>
       </c>
       <c r="AC52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 23354-2024 tillsynsbegäran.docx", "A 23354-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 7543-2024 tillsynsbegäran.docx", "A 7543-2024")</f>
         <v/>
       </c>
       <c r="AD52">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 23354-2024 tillsynsbegäran mail.docx", "A 23354-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 7543-2024 tillsynsbegäran mail.docx", "A 7543-2024")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" t="inlineStr">
         <is>
-          <t>A 37012-2025</t>
+          <t>A 35743-2025</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -6344,10 +6339,10 @@
         </is>
       </c>
       <c r="D53" s="1" t="n">
-        <v>45874</v>
+        <v>45860</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6365,16 +6360,16 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>3.7</v>
+        <v>1.4</v>
       </c>
       <c r="J53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K53" t="n">
         <v>0</v>
       </c>
       <c r="L53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M53" t="n">
         <v>0</v>
@@ -6389,7 +6384,7 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
@@ -6401,46 +6396,46 @@
         <v>1</v>
       </c>
       <c r="U53" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V53" s="2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="W53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 37012-2025 artfynd.xlsx", "A 37012-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 35743-2025 artfynd.xlsx", "A 35743-2025")</f>
         <v/>
       </c>
       <c r="X53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 37012-2025 karta.png", "A 37012-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 35743-2025 karta.png", "A 35743-2025")</f>
         <v/>
       </c>
       <c r="Y53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 37012-2025 georefererad karta.tif", "A 37012-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 35743-2025 georefererad karta.tif", "A 35743-2025")</f>
         <v/>
       </c>
       <c r="AA53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 37012-2025 FSC-klagomål.docx", "A 37012-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 35743-2025 FSC-klagomål.docx", "A 35743-2025")</f>
         <v/>
       </c>
       <c r="AB53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 37012-2025 FSC-klagomål mail.docx", "A 37012-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 35743-2025 FSC-klagomål mail.docx", "A 35743-2025")</f>
         <v/>
       </c>
       <c r="AC53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 37012-2025 tillsynsbegäran.docx", "A 37012-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 35743-2025 tillsynsbegäran.docx", "A 35743-2025")</f>
         <v/>
       </c>
       <c r="AD53">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 37012-2025 tillsynsbegäran mail.docx", "A 37012-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 35743-2025 tillsynsbegäran mail.docx", "A 35743-2025")</f>
         <v/>
       </c>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 37988-2025</t>
+          <t>A 36606-2025</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6454,10 +6449,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45881</v>
+        <v>45870</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6475,7 +6470,7 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.7</v>
+        <v>13.3</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
@@ -6511,46 +6506,46 @@
         <v>1</v>
       </c>
       <c r="U54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>Backruta</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="W54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 37988-2025 artfynd.xlsx", "A 37988-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 36606-2025 artfynd.xlsx", "A 36606-2025")</f>
         <v/>
       </c>
       <c r="X54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 37988-2025 karta.png", "A 37988-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 36606-2025 karta.png", "A 36606-2025")</f>
         <v/>
       </c>
       <c r="Y54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 37988-2025 georefererad karta.tif", "A 37988-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 36606-2025 georefererad karta.tif", "A 36606-2025")</f>
         <v/>
       </c>
       <c r="AA54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 37988-2025 FSC-klagomål.docx", "A 37988-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 36606-2025 FSC-klagomål.docx", "A 36606-2025")</f>
         <v/>
       </c>
       <c r="AB54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 37988-2025 FSC-klagomål mail.docx", "A 37988-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 36606-2025 FSC-klagomål mail.docx", "A 36606-2025")</f>
         <v/>
       </c>
       <c r="AC54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 37988-2025 tillsynsbegäran.docx", "A 37988-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 36606-2025 tillsynsbegäran.docx", "A 36606-2025")</f>
         <v/>
       </c>
       <c r="AD54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 37988-2025 tillsynsbegäran mail.docx", "A 37988-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 36606-2025 tillsynsbegäran mail.docx", "A 36606-2025")</f>
         <v/>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" t="inlineStr">
         <is>
-          <t>A 30008-2024</t>
+          <t>A 37012-2025</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -6564,10 +6559,10 @@
         </is>
       </c>
       <c r="D55" s="1" t="n">
-        <v>45488</v>
+        <v>45874</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6585,16 +6580,16 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.8</v>
+        <v>3.7</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M55" t="n">
         <v>0</v>
@@ -6609,7 +6604,7 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
@@ -6625,42 +6620,42 @@
       </c>
       <c r="V55" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="W55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 30008-2024 artfynd.xlsx", "A 30008-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 37012-2025 artfynd.xlsx", "A 37012-2025")</f>
         <v/>
       </c>
       <c r="X55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 30008-2024 karta.png", "A 30008-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 37012-2025 karta.png", "A 37012-2025")</f>
         <v/>
       </c>
       <c r="Y55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 30008-2024 georefererad karta.tif", "A 30008-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 37012-2025 georefererad karta.tif", "A 37012-2025")</f>
         <v/>
       </c>
       <c r="AA55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 30008-2024 FSC-klagomål.docx", "A 30008-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 37012-2025 FSC-klagomål.docx", "A 37012-2025")</f>
         <v/>
       </c>
       <c r="AB55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 30008-2024 FSC-klagomål mail.docx", "A 30008-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 37012-2025 FSC-klagomål mail.docx", "A 37012-2025")</f>
         <v/>
       </c>
       <c r="AC55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 30008-2024 tillsynsbegäran.docx", "A 30008-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 37012-2025 tillsynsbegäran.docx", "A 37012-2025")</f>
         <v/>
       </c>
       <c r="AD55">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 30008-2024 tillsynsbegäran mail.docx", "A 30008-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 37012-2025 tillsynsbegäran mail.docx", "A 37012-2025")</f>
         <v/>
       </c>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 49815-2024</t>
+          <t>A 37988-2025</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6674,10 +6669,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>45597</v>
+        <v>45881</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6689,8 +6684,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I56" t="n">
-        <v>0.9</v>
+        <v>5.7</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
@@ -6726,46 +6726,46 @@
         <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Backruta</t>
         </is>
       </c>
       <c r="W56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 49815-2024 artfynd.xlsx", "A 49815-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 37988-2025 artfynd.xlsx", "A 37988-2025")</f>
         <v/>
       </c>
       <c r="X56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 49815-2024 karta.png", "A 49815-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 37988-2025 karta.png", "A 37988-2025")</f>
         <v/>
       </c>
       <c r="Y56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 49815-2024 georefererad karta.tif", "A 49815-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 37988-2025 georefererad karta.tif", "A 37988-2025")</f>
         <v/>
       </c>
       <c r="AA56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 49815-2024 FSC-klagomål.docx", "A 49815-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 37988-2025 FSC-klagomål.docx", "A 37988-2025")</f>
         <v/>
       </c>
       <c r="AB56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 49815-2024 FSC-klagomål mail.docx", "A 49815-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 37988-2025 FSC-klagomål mail.docx", "A 37988-2025")</f>
         <v/>
       </c>
       <c r="AC56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 49815-2024 tillsynsbegäran.docx", "A 49815-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 37988-2025 tillsynsbegäran.docx", "A 37988-2025")</f>
         <v/>
       </c>
       <c r="AD56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 49815-2024 tillsynsbegäran mail.docx", "A 49815-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 37988-2025 tillsynsbegäran mail.docx", "A 37988-2025")</f>
         <v/>
       </c>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" t="inlineStr">
         <is>
-          <t>A 35514-2024</t>
+          <t>A 46058-2025</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -6779,10 +6779,10 @@
         </is>
       </c>
       <c r="D57" s="1" t="n">
-        <v>45531</v>
+        <v>45924</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6796,14 +6796,14 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I57" t="n">
-        <v>6.5</v>
+        <v>1.6</v>
       </c>
       <c r="J57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K57" t="n">
         <v>0</v>
@@ -6833,53 +6833,49 @@
         <v>1</v>
       </c>
       <c r="T57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U57" t="n">
         <v>0</v>
       </c>
       <c r="V57" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="W57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 35514-2024 artfynd.xlsx", "A 35514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 46058-2025 artfynd.xlsx", "A 46058-2025")</f>
         <v/>
       </c>
       <c r="X57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 35514-2024 karta.png", "A 35514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 46058-2025 karta.png", "A 46058-2025")</f>
         <v/>
       </c>
       <c r="Y57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 35514-2024 georefererad karta.tif", "A 35514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 46058-2025 georefererad karta.tif", "A 46058-2025")</f>
         <v/>
       </c>
       <c r="AA57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 35514-2024 FSC-klagomål.docx", "A 35514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 46058-2025 FSC-klagomål.docx", "A 46058-2025")</f>
         <v/>
       </c>
       <c r="AB57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 35514-2024 FSC-klagomål mail.docx", "A 35514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 46058-2025 FSC-klagomål mail.docx", "A 46058-2025")</f>
         <v/>
       </c>
       <c r="AC57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 35514-2024 tillsynsbegäran.docx", "A 35514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 46058-2025 tillsynsbegäran.docx", "A 46058-2025")</f>
         <v/>
       </c>
       <c r="AD57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 35514-2024 tillsynsbegäran mail.docx", "A 35514-2024")</f>
-        <v/>
-      </c>
-      <c r="AE57">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/fåglar/A 35514-2024 prioriterade fågelarter.docx", "A 35514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 46058-2025 tillsynsbegäran mail.docx", "A 46058-2025")</f>
         <v/>
       </c>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 46058-2025</t>
+          <t>A 28397-2024</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6893,10 +6889,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45924</v>
+        <v>45477</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6910,20 +6906,20 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="J58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K58" t="n">
         <v>0</v>
       </c>
       <c r="L58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M58" t="n">
         <v>0</v>
@@ -6938,7 +6934,7 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
@@ -6947,49 +6943,49 @@
         <v>1</v>
       </c>
       <c r="T58" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 46058-2025 artfynd.xlsx", "A 46058-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 28397-2024 artfynd.xlsx", "A 28397-2024")</f>
         <v/>
       </c>
       <c r="X58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 46058-2025 karta.png", "A 46058-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 28397-2024 karta.png", "A 28397-2024")</f>
         <v/>
       </c>
       <c r="Y58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 46058-2025 georefererad karta.tif", "A 46058-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 28397-2024 georefererad karta.tif", "A 28397-2024")</f>
         <v/>
       </c>
       <c r="AA58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 46058-2025 FSC-klagomål.docx", "A 46058-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 28397-2024 FSC-klagomål.docx", "A 28397-2024")</f>
         <v/>
       </c>
       <c r="AB58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 46058-2025 FSC-klagomål mail.docx", "A 46058-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 28397-2024 FSC-klagomål mail.docx", "A 28397-2024")</f>
         <v/>
       </c>
       <c r="AC58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 46058-2025 tillsynsbegäran.docx", "A 46058-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 28397-2024 tillsynsbegäran.docx", "A 28397-2024")</f>
         <v/>
       </c>
       <c r="AD58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 46058-2025 tillsynsbegäran mail.docx", "A 46058-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 28397-2024 tillsynsbegäran mail.docx", "A 28397-2024")</f>
         <v/>
       </c>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" t="inlineStr">
         <is>
-          <t>A 10587-2022</t>
+          <t>A 36278-2024</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -7003,10 +6999,10 @@
         </is>
       </c>
       <c r="D59" s="1" t="n">
-        <v>44624</v>
+        <v>45534</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7018,8 +7014,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I59" t="n">
-        <v>5</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="J59" t="n">
         <v>1</v>
@@ -7052,42 +7053,46 @@
         <v>1</v>
       </c>
       <c r="T59" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V59" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="W59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 10587-2022 artfynd.xlsx", "A 10587-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 36278-2024 artfynd.xlsx", "A 36278-2024")</f>
         <v/>
       </c>
       <c r="X59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 10587-2022 karta.png", "A 10587-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 36278-2024 karta.png", "A 36278-2024")</f>
         <v/>
       </c>
       <c r="Y59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 10587-2022 georefererad karta.tif", "A 10587-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 36278-2024 georefererad karta.tif", "A 36278-2024")</f>
         <v/>
       </c>
       <c r="AA59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 10587-2022 FSC-klagomål.docx", "A 10587-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 36278-2024 FSC-klagomål.docx", "A 36278-2024")</f>
         <v/>
       </c>
       <c r="AB59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 10587-2022 FSC-klagomål mail.docx", "A 10587-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 36278-2024 FSC-klagomål mail.docx", "A 36278-2024")</f>
         <v/>
       </c>
       <c r="AC59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 10587-2022 tillsynsbegäran.docx", "A 10587-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 36278-2024 tillsynsbegäran.docx", "A 36278-2024")</f>
         <v/>
       </c>
       <c r="AD59">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 10587-2022 tillsynsbegäran mail.docx", "A 10587-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 36278-2024 tillsynsbegäran mail.docx", "A 36278-2024")</f>
+        <v/>
+      </c>
+      <c r="AE59">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/fåglar/A 36278-2024 prioriterade fågelarter.docx", "A 36278-2024")</f>
         <v/>
       </c>
     </row>
@@ -7111,7 +7116,7 @@
         <v>46091</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7220,7 +7225,7 @@
         <v>45924</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7317,7 +7322,7 @@
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 48063-2024</t>
+          <t>A 35521-2024</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7331,10 +7336,10 @@
         </is>
       </c>
       <c r="D62" s="1" t="n">
-        <v>45589</v>
+        <v>45531</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7346,14 +7351,19 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I62" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="J62" t="n">
         <v>1</v>
       </c>
       <c r="K62" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L62" t="n">
         <v>0</v>
@@ -7387,42 +7397,42 @@
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 48063-2024 artfynd.xlsx", "A 48063-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 35521-2024 artfynd.xlsx", "A 35521-2024")</f>
         <v/>
       </c>
       <c r="X62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 48063-2024 karta.png", "A 48063-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 35521-2024 karta.png", "A 35521-2024")</f>
         <v/>
       </c>
       <c r="Y62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 48063-2024 georefererad karta.tif", "A 48063-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 35521-2024 georefererad karta.tif", "A 35521-2024")</f>
         <v/>
       </c>
       <c r="AA62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 48063-2024 FSC-klagomål.docx", "A 48063-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 35521-2024 FSC-klagomål.docx", "A 35521-2024")</f>
         <v/>
       </c>
       <c r="AB62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 48063-2024 FSC-klagomål mail.docx", "A 48063-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 35521-2024 FSC-klagomål mail.docx", "A 35521-2024")</f>
         <v/>
       </c>
       <c r="AC62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 48063-2024 tillsynsbegäran.docx", "A 48063-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 35521-2024 tillsynsbegäran.docx", "A 35521-2024")</f>
         <v/>
       </c>
       <c r="AD62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 48063-2024 tillsynsbegäran mail.docx", "A 48063-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 35521-2024 tillsynsbegäran mail.docx", "A 35521-2024")</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 13745-2023</t>
+          <t>A 49815-2024</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7436,10 +7446,10 @@
         </is>
       </c>
       <c r="D63" s="1" t="n">
-        <v>45007</v>
+        <v>45597</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7451,13 +7461,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I63" t="n">
-        <v>0.5</v>
+        <v>0.9</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -7493,46 +7498,46 @@
         <v>1</v>
       </c>
       <c r="U63" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="W63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 13745-2023 artfynd.xlsx", "A 13745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 49815-2024 artfynd.xlsx", "A 49815-2024")</f>
         <v/>
       </c>
       <c r="X63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 13745-2023 karta.png", "A 13745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 49815-2024 karta.png", "A 49815-2024")</f>
         <v/>
       </c>
       <c r="Y63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 13745-2023 georefererad karta.tif", "A 13745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 49815-2024 georefererad karta.tif", "A 49815-2024")</f>
         <v/>
       </c>
       <c r="AA63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 13745-2023 FSC-klagomål.docx", "A 13745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 49815-2024 FSC-klagomål.docx", "A 49815-2024")</f>
         <v/>
       </c>
       <c r="AB63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 13745-2023 FSC-klagomål mail.docx", "A 13745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 49815-2024 FSC-klagomål mail.docx", "A 49815-2024")</f>
         <v/>
       </c>
       <c r="AC63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 13745-2023 tillsynsbegäran.docx", "A 13745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 49815-2024 tillsynsbegäran.docx", "A 49815-2024")</f>
         <v/>
       </c>
       <c r="AD63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 13745-2023 tillsynsbegäran mail.docx", "A 13745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 49815-2024 tillsynsbegäran mail.docx", "A 49815-2024")</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 33298-2023</t>
+          <t>A 10587-2022</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7546,10 +7551,10 @@
         </is>
       </c>
       <c r="D64" s="1" t="n">
-        <v>45127</v>
+        <v>44624</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7561,19 +7566,14 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I64" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="J64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K64" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" t="n">
         <v>0</v>
@@ -7600,49 +7600,49 @@
         <v>1</v>
       </c>
       <c r="T64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U64" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 33298-2023 artfynd.xlsx", "A 33298-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 10587-2022 artfynd.xlsx", "A 10587-2022")</f>
         <v/>
       </c>
       <c r="X64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 33298-2023 karta.png", "A 33298-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 10587-2022 karta.png", "A 10587-2022")</f>
         <v/>
       </c>
       <c r="Y64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 33298-2023 georefererad karta.tif", "A 33298-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 10587-2022 georefererad karta.tif", "A 10587-2022")</f>
         <v/>
       </c>
       <c r="AA64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 33298-2023 FSC-klagomål.docx", "A 33298-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 10587-2022 FSC-klagomål.docx", "A 10587-2022")</f>
         <v/>
       </c>
       <c r="AB64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 33298-2023 FSC-klagomål mail.docx", "A 33298-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 10587-2022 FSC-klagomål mail.docx", "A 10587-2022")</f>
         <v/>
       </c>
       <c r="AC64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 33298-2023 tillsynsbegäran.docx", "A 33298-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 10587-2022 tillsynsbegäran.docx", "A 10587-2022")</f>
         <v/>
       </c>
       <c r="AD64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 33298-2023 tillsynsbegäran mail.docx", "A 33298-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 10587-2022 tillsynsbegäran mail.docx", "A 10587-2022")</f>
         <v/>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" t="inlineStr">
         <is>
-          <t>A 36278-2024</t>
+          <t>A 28392-2024</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -7656,10 +7656,10 @@
         </is>
       </c>
       <c r="D65" s="1" t="n">
-        <v>45534</v>
+        <v>45477</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7677,7 +7677,7 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>8.699999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="J65" t="n">
         <v>1</v>
@@ -7710,46 +7710,42 @@
         <v>1</v>
       </c>
       <c r="T65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V65" s="2" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 36278-2024 artfynd.xlsx", "A 36278-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 28392-2024 artfynd.xlsx", "A 28392-2024")</f>
         <v/>
       </c>
       <c r="X65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 36278-2024 karta.png", "A 36278-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 28392-2024 karta.png", "A 28392-2024")</f>
         <v/>
       </c>
       <c r="Y65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 36278-2024 georefererad karta.tif", "A 36278-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 28392-2024 georefererad karta.tif", "A 28392-2024")</f>
         <v/>
       </c>
       <c r="AA65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 36278-2024 FSC-klagomål.docx", "A 36278-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 28392-2024 FSC-klagomål.docx", "A 28392-2024")</f>
         <v/>
       </c>
       <c r="AB65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 36278-2024 FSC-klagomål mail.docx", "A 36278-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 28392-2024 FSC-klagomål mail.docx", "A 28392-2024")</f>
         <v/>
       </c>
       <c r="AC65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 36278-2024 tillsynsbegäran.docx", "A 36278-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 28392-2024 tillsynsbegäran.docx", "A 28392-2024")</f>
         <v/>
       </c>
       <c r="AD65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 36278-2024 tillsynsbegäran mail.docx", "A 36278-2024")</f>
-        <v/>
-      </c>
-      <c r="AE65">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/fåglar/A 36278-2024 prioriterade fågelarter.docx", "A 36278-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 28392-2024 tillsynsbegäran mail.docx", "A 28392-2024")</f>
         <v/>
       </c>
     </row>
@@ -7773,7 +7769,7 @@
         <v>46183</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7883,7 +7879,7 @@
         <v>46196</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7976,7 +7972,7 @@
     <row r="68" ht="15" customHeight="1">
       <c r="A68" t="inlineStr">
         <is>
-          <t>A 33997-2026</t>
+          <t>A 234-2023</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -7990,10 +7986,10 @@
         </is>
       </c>
       <c r="D68" s="1" t="n">
-        <v>46252</v>
+        <v>44928</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8011,7 +8007,7 @@
         </is>
       </c>
       <c r="I68" t="n">
-        <v>10.3</v>
+        <v>5.1</v>
       </c>
       <c r="J68" t="n">
         <v>1</v>
@@ -8047,7 +8043,7 @@
         <v>1</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V68" s="2" t="inlineStr">
         <is>
@@ -8055,42 +8051,42 @@
         </is>
       </c>
       <c r="W68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 33997-2026 artfynd.xlsx", "A 33997-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 234-2023 artfynd.xlsx", "A 234-2023")</f>
         <v/>
       </c>
       <c r="X68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 33997-2026 karta.png", "A 33997-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 234-2023 karta.png", "A 234-2023")</f>
         <v/>
       </c>
       <c r="Y68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 33997-2026 georefererad karta.tif", "A 33997-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 234-2023 georefererad karta.tif", "A 234-2023")</f>
         <v/>
       </c>
       <c r="Z68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/knärot/A 33997-2026 karta knärot.png", "A 33997-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/knärot/A 234-2023 karta knärot.png", "A 234-2023")</f>
         <v/>
       </c>
       <c r="AA68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 33997-2026 FSC-klagomål.docx", "A 33997-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 234-2023 FSC-klagomål.docx", "A 234-2023")</f>
         <v/>
       </c>
       <c r="AB68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 33997-2026 FSC-klagomål mail.docx", "A 33997-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 234-2023 FSC-klagomål mail.docx", "A 234-2023")</f>
         <v/>
       </c>
       <c r="AC68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 33997-2026 tillsynsbegäran.docx", "A 33997-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 234-2023 tillsynsbegäran.docx", "A 234-2023")</f>
         <v/>
       </c>
       <c r="AD68">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 33997-2026 tillsynsbegäran mail.docx", "A 33997-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 234-2023 tillsynsbegäran mail.docx", "A 234-2023")</f>
         <v/>
       </c>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" t="inlineStr">
         <is>
-          <t>A 35521-2024</t>
+          <t>A 31184-2026</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -8104,10 +8100,10 @@
         </is>
       </c>
       <c r="D69" s="1" t="n">
-        <v>45531</v>
+        <v>46217</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8125,7 +8121,7 @@
         </is>
       </c>
       <c r="I69" t="n">
-        <v>1.3</v>
+        <v>7</v>
       </c>
       <c r="J69" t="n">
         <v>1</v>
@@ -8165,35 +8161,35 @@
       </c>
       <c r="V69" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 35521-2024 artfynd.xlsx", "A 35521-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 31184-2026 artfynd.xlsx", "A 31184-2026")</f>
         <v/>
       </c>
       <c r="X69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 35521-2024 karta.png", "A 35521-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 31184-2026 karta.png", "A 31184-2026")</f>
         <v/>
       </c>
       <c r="Y69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 35521-2024 georefererad karta.tif", "A 35521-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 31184-2026 georefererad karta.tif", "A 31184-2026")</f>
         <v/>
       </c>
       <c r="AA69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 35521-2024 FSC-klagomål.docx", "A 35521-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 31184-2026 FSC-klagomål.docx", "A 31184-2026")</f>
         <v/>
       </c>
       <c r="AB69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 35521-2024 FSC-klagomål mail.docx", "A 35521-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 31184-2026 FSC-klagomål mail.docx", "A 31184-2026")</f>
         <v/>
       </c>
       <c r="AC69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 35521-2024 tillsynsbegäran.docx", "A 35521-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 31184-2026 tillsynsbegäran.docx", "A 31184-2026")</f>
         <v/>
       </c>
       <c r="AD69">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 35521-2024 tillsynsbegäran mail.docx", "A 35521-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 31184-2026 tillsynsbegäran mail.docx", "A 31184-2026")</f>
         <v/>
       </c>
     </row>
@@ -8217,7 +8213,7 @@
         <v>46217</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8310,7 +8306,7 @@
     <row r="71" ht="15" customHeight="1">
       <c r="A71" t="inlineStr">
         <is>
-          <t>A 31184-2026</t>
+          <t>A 35482-2026</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -8324,10 +8320,10 @@
         </is>
       </c>
       <c r="D71" s="1" t="n">
-        <v>46217</v>
+        <v>46262</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8345,7 +8341,7 @@
         </is>
       </c>
       <c r="I71" t="n">
-        <v>7</v>
+        <v>3.1</v>
       </c>
       <c r="J71" t="n">
         <v>1</v>
@@ -8378,49 +8374,49 @@
         <v>1</v>
       </c>
       <c r="T71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U71" t="n">
         <v>0</v>
       </c>
       <c r="V71" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="W71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 31184-2026 artfynd.xlsx", "A 31184-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 35482-2026 artfynd.xlsx", "A 35482-2026")</f>
         <v/>
       </c>
       <c r="X71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 31184-2026 karta.png", "A 31184-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 35482-2026 karta.png", "A 35482-2026")</f>
         <v/>
       </c>
       <c r="Y71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 31184-2026 georefererad karta.tif", "A 31184-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 35482-2026 georefererad karta.tif", "A 35482-2026")</f>
         <v/>
       </c>
       <c r="AA71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 31184-2026 FSC-klagomål.docx", "A 31184-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 35482-2026 FSC-klagomål.docx", "A 35482-2026")</f>
         <v/>
       </c>
       <c r="AB71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 31184-2026 FSC-klagomål mail.docx", "A 31184-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 35482-2026 FSC-klagomål mail.docx", "A 35482-2026")</f>
         <v/>
       </c>
       <c r="AC71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 31184-2026 tillsynsbegäran.docx", "A 31184-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 35482-2026 tillsynsbegäran.docx", "A 35482-2026")</f>
         <v/>
       </c>
       <c r="AD71">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 31184-2026 tillsynsbegäran mail.docx", "A 31184-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 35482-2026 tillsynsbegäran mail.docx", "A 35482-2026")</f>
         <v/>
       </c>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" t="inlineStr">
         <is>
-          <t>A 35482-2026</t>
+          <t>A 33997-2026</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -8434,10 +8430,10 @@
         </is>
       </c>
       <c r="D72" s="1" t="n">
-        <v>46262</v>
+        <v>46252</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8455,7 +8451,7 @@
         </is>
       </c>
       <c r="I72" t="n">
-        <v>3.1</v>
+        <v>10.3</v>
       </c>
       <c r="J72" t="n">
         <v>1</v>
@@ -8467,7 +8463,7 @@
         <v>0</v>
       </c>
       <c r="M72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N72" t="n">
         <v>0</v>
@@ -8479,51 +8475,55 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S72" t="n">
         <v>1</v>
       </c>
       <c r="T72" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U72" t="n">
         <v>0</v>
       </c>
       <c r="V72" s="2" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 35482-2026 artfynd.xlsx", "A 35482-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 33997-2026 artfynd.xlsx", "A 33997-2026")</f>
         <v/>
       </c>
       <c r="X72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 35482-2026 karta.png", "A 35482-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 33997-2026 karta.png", "A 33997-2026")</f>
         <v/>
       </c>
       <c r="Y72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 35482-2026 georefererad karta.tif", "A 35482-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 33997-2026 georefererad karta.tif", "A 33997-2026")</f>
+        <v/>
+      </c>
+      <c r="Z72">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/knärot/A 33997-2026 karta knärot.png", "A 33997-2026")</f>
         <v/>
       </c>
       <c r="AA72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 35482-2026 FSC-klagomål.docx", "A 35482-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 33997-2026 FSC-klagomål.docx", "A 33997-2026")</f>
         <v/>
       </c>
       <c r="AB72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 35482-2026 FSC-klagomål mail.docx", "A 35482-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 33997-2026 FSC-klagomål mail.docx", "A 33997-2026")</f>
         <v/>
       </c>
       <c r="AC72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 35482-2026 tillsynsbegäran.docx", "A 35482-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 33997-2026 tillsynsbegäran.docx", "A 33997-2026")</f>
         <v/>
       </c>
       <c r="AD72">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 35482-2026 tillsynsbegäran mail.docx", "A 35482-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 33997-2026 tillsynsbegäran mail.docx", "A 33997-2026")</f>
         <v/>
       </c>
     </row>
@@ -8547,7 +8547,7 @@
         <v>45701</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>45727</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8771,7 +8771,7 @@
         <v>45706</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8881,7 +8881,7 @@
         <v>44868</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8959,7 +8959,7 @@
         <v>44582</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -9032,7 +9032,7 @@
         <v>44501</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>44512</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9178,7 +9178,7 @@
         <v>44873</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9251,7 +9251,7 @@
         <v>44692</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9324,7 +9324,7 @@
         <v>44868</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9385,7 +9385,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 17179-2025</t>
+          <t>A 13473-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9399,10 +9399,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45755</v>
+        <v>45387</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9414,13 +9414,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I83" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -9463,7 +9458,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 35498-2024</t>
+          <t>A 35505-2024</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9480,7 +9475,7 @@
         <v>45531</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9498,7 +9493,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -9541,7 +9536,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 6929-2023</t>
+          <t>A 22226-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9555,10 +9550,10 @@
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>44967</v>
+        <v>45446</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9571,7 +9566,7 @@
         </is>
       </c>
       <c r="I85" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -9614,7 +9609,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 33978-2024</t>
+          <t>A 23376-2024</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9628,10 +9623,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45523</v>
+        <v>45453</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9643,8 +9638,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I86" t="n">
-        <v>0.6</v>
+        <v>10.8</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9687,7 +9687,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 33984-2024</t>
+          <t>A 37744-2022</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9701,10 +9701,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45523</v>
+        <v>44810</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9717,7 +9717,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9760,7 +9760,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 11813-2024</t>
+          <t>A 58240-2021</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9774,10 +9774,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45376</v>
+        <v>44487</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9790,7 +9790,7 @@
         </is>
       </c>
       <c r="I88" t="n">
-        <v>2.3</v>
+        <v>1.1</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9833,7 +9833,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 61642-2025</t>
+          <t>A 30229-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9847,10 +9847,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>46002</v>
+        <v>45490</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9862,8 +9862,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9906,7 +9911,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 38741-2025</t>
+          <t>A 38486-2025</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9920,10 +9925,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>45887</v>
+        <v>45884</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9935,13 +9940,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I90" t="n">
-        <v>2.5</v>
+        <v>1.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9984,7 +9984,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 38486-2025</t>
+          <t>A 62596-2023</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9998,10 +9998,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>45884</v>
+        <v>45271</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         </is>
       </c>
       <c r="I91" t="n">
-        <v>1.9</v>
+        <v>3.6</v>
       </c>
       <c r="J91" t="n">
         <v>0</v>
@@ -10074,7 +10074,7 @@
         <v>45792</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10130,7 +10130,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 28391-2024</t>
+          <t>A 53517-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10144,10 +10144,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45477</v>
+        <v>45614</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10159,13 +10159,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H93" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I93" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -10208,7 +10203,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 4032-2025</t>
+          <t>A 692-2026</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10218,14 +10213,14 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>45684</v>
+        <v>46029</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10238,7 +10233,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>2.7</v>
+        <v>0.5</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -10281,7 +10276,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 33296-2023</t>
+          <t>A 38741-2025</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10295,10 +10290,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45127</v>
+        <v>45887</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10316,7 +10311,7 @@
         </is>
       </c>
       <c r="I95" t="n">
-        <v>6.4</v>
+        <v>2.5</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -10359,7 +10354,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 33981-2024</t>
+          <t>A 892-2026</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10373,10 +10368,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45523</v>
+        <v>46030</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10389,7 +10384,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -10432,7 +10427,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 40407-2025</t>
+          <t>A 33981-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10442,14 +10437,14 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45895</v>
+        <v>45523</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10461,13 +10456,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I97" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -10510,7 +10500,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 53517-2024</t>
+          <t>A 11813-2024</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10524,10 +10514,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45614</v>
+        <v>45376</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10540,7 +10530,7 @@
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1</v>
+        <v>2.3</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -10583,7 +10573,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 51337-2023</t>
+          <t>A 41020-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10597,10 +10587,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45219</v>
+        <v>45173</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10612,8 +10602,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -10656,7 +10651,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 54149-2023</t>
+          <t>A 40407-2025</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10666,14 +10661,14 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45232</v>
+        <v>45895</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10685,8 +10680,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I100" t="n">
-        <v>4.6</v>
+        <v>2.2</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10729,7 +10729,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 37743-2022</t>
+          <t>A 659-2026</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10743,10 +10743,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44810</v>
+        <v>46029</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10759,7 +10759,7 @@
         </is>
       </c>
       <c r="I101" t="n">
-        <v>1.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10802,7 +10802,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 44692-2025</t>
+          <t>A 30007-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10816,10 +10816,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45917</v>
+        <v>45488</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10837,7 +10837,7 @@
         </is>
       </c>
       <c r="I102" t="n">
-        <v>5.4</v>
+        <v>11.5</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10880,7 +10880,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 58240-2021</t>
+          <t>A 30009-2024</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10894,10 +10894,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>44487</v>
+        <v>45488</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10909,8 +10909,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I103" t="n">
-        <v>1.1</v>
+        <v>0.6</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10953,7 +10958,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 26302-2025</t>
+          <t>A 13471-2024</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10963,14 +10968,14 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45805</v>
+        <v>45387</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10983,7 +10988,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>5.3</v>
+        <v>2.9</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -11026,7 +11031,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 13471-2024</t>
+          <t>A 58787-2021</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -11040,10 +11045,10 @@
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45387</v>
+        <v>44489</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11056,7 +11061,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.9</v>
+        <v>1.1</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -11099,7 +11104,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 47091-2025</t>
+          <t>A 2220-2026</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -11113,10 +11118,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45929</v>
+        <v>46036</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11129,7 +11134,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>3.7</v>
+        <v>0.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -11172,7 +11177,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 47249-2025</t>
+          <t>A 2546-2026</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -11186,10 +11191,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45930</v>
+        <v>46037</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11202,7 +11207,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>1.6</v>
+        <v>5</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -11245,7 +11250,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 31471-2025</t>
+          <t>A 6963-2024</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -11259,10 +11264,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45833</v>
+        <v>45343</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11275,7 +11280,7 @@
         </is>
       </c>
       <c r="I108" t="n">
-        <v>1.6</v>
+        <v>2.4</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -11318,7 +11323,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 48232-2025</t>
+          <t>A 31645-2024</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -11332,10 +11337,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45933</v>
+        <v>45506</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11353,7 +11358,7 @@
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>11.1</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -11396,7 +11401,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 27959-2025</t>
+          <t>A 26302-2025</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -11406,14 +11411,14 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45816</v>
+        <v>45805</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11425,13 +11430,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>45.6</v>
+        <v>5.3</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -11474,7 +11474,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 48240-2025</t>
+          <t>A 44692-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -11488,10 +11488,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>45933</v>
+        <v>45917</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11509,7 +11509,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>1.3</v>
+        <v>5.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -11552,7 +11552,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 48241-2025</t>
+          <t>A 31471-2025</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -11566,10 +11566,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45933</v>
+        <v>45833</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11581,13 +11581,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I112" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -11630,7 +11625,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 48231-2025</t>
+          <t>A 3615-2026</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11644,10 +11639,10 @@
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45933</v>
+        <v>46042</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11659,13 +11654,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>2.7</v>
+        <v>2.4</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11708,7 +11698,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 32299-2025</t>
+          <t>A 54149-2023</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11722,10 +11712,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45835</v>
+        <v>45232</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11737,13 +11727,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H114" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I114" t="n">
-        <v>12.8</v>
+        <v>4.6</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11786,7 +11771,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 48612-2025</t>
+          <t>A 32299-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11800,10 +11785,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45935</v>
+        <v>45835</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11821,7 +11806,7 @@
         </is>
       </c>
       <c r="I115" t="n">
-        <v>5.3</v>
+        <v>12.8</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11864,7 +11849,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 11953-2025</t>
+          <t>A 47249-2025</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11878,10 +11863,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45728</v>
+        <v>45930</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11893,13 +11878,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I116" t="n">
-        <v>34.8</v>
+        <v>1.6</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11942,7 +11922,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 27738-2024</t>
+          <t>A 47091-2025</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11956,10 +11936,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45475</v>
+        <v>45929</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11971,13 +11951,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I117" t="n">
-        <v>2.6</v>
+        <v>3.7</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -12020,7 +11995,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 37680-2022</t>
+          <t>A 36283-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -12034,10 +12009,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>44810</v>
+        <v>45534</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12049,8 +12024,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I118" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -12093,7 +12073,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 51225-2025</t>
+          <t>A 48232-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -12107,10 +12087,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>45947</v>
+        <v>45933</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12128,7 +12108,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2.1</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -12171,7 +12151,7 @@
     <row r="120" ht="15" customHeight="1">
       <c r="A120" t="inlineStr">
         <is>
-          <t>A 57632-2021</t>
+          <t>A 48612-2025</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -12185,10 +12165,10 @@
         </is>
       </c>
       <c r="D120" s="1" t="n">
-        <v>44484</v>
+        <v>45935</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12200,8 +12180,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I120" t="n">
-        <v>4.1</v>
+        <v>5.3</v>
       </c>
       <c r="J120" t="n">
         <v>0</v>
@@ -12244,7 +12229,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 58373-2023</t>
+          <t>A 48231-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -12258,10 +12243,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>45250</v>
+        <v>45933</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12273,8 +12258,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -12317,7 +12307,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 41020-2023</t>
+          <t>A 27959-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -12331,10 +12321,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>45173</v>
+        <v>45816</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12348,11 +12338,11 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I122" t="n">
-        <v>1.5</v>
+        <v>45.6</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -12395,7 +12385,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 659-2026</t>
+          <t>A 48240-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -12409,10 +12399,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>46029</v>
+        <v>45933</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12424,8 +12414,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>9.199999999999999</v>
+        <v>1.3</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -12468,7 +12463,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 692-2026</t>
+          <t>A 48241-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -12482,10 +12477,10 @@
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>46029</v>
+        <v>45933</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12497,8 +12492,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I124" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -12541,7 +12541,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 52693-2025</t>
+          <t>A 16371-2022</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -12555,10 +12555,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45956</v>
+        <v>44671</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12571,7 +12571,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>1.4</v>
+        <v>0.8</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -12614,7 +12614,7 @@
     <row r="126" ht="15" customHeight="1">
       <c r="A126" t="inlineStr">
         <is>
-          <t>A 892-2026</t>
+          <t>A 47359-2024</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -12628,10 +12628,10 @@
         </is>
       </c>
       <c r="D126" s="1" t="n">
-        <v>46030</v>
+        <v>45587</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         </is>
       </c>
       <c r="I126" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J126" t="n">
         <v>0</v>
@@ -12687,7 +12687,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 36349-2025</t>
+          <t>A 23355-2024</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12701,10 +12701,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45868</v>
+        <v>45453</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12716,8 +12716,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>2.7</v>
+        <v>1.2</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12760,7 +12765,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 44356-2023</t>
+          <t>A 36349-2025</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12774,10 +12779,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45188</v>
+        <v>45868</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12790,7 +12795,7 @@
         </is>
       </c>
       <c r="I128" t="n">
-        <v>2.1</v>
+        <v>2.7</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12833,7 +12838,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 23355-2024</t>
+          <t>A 5549-2026</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12847,10 +12852,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45453</v>
+        <v>46050</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12862,13 +12867,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>1.2</v>
+        <v>2.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12911,7 +12911,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 13744-2023</t>
+          <t>A 51225-2025</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12925,10 +12925,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>45007</v>
+        <v>45947</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12942,11 +12942,11 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I130" t="n">
-        <v>1</v>
+        <v>2.1</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12989,7 +12989,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 37444-2025</t>
+          <t>A 6929-2023</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -13003,10 +13003,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45877</v>
+        <v>44967</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13018,13 +13018,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I131" t="n">
-        <v>4.8</v>
+        <v>0.9</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -13067,7 +13062,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 54876-2025</t>
+          <t>A 37444-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -13081,10 +13076,10 @@
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45967</v>
+        <v>45877</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13096,8 +13091,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I132" t="n">
-        <v>0.6</v>
+        <v>4.8</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -13140,7 +13140,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 54877-2025</t>
+          <t>A 52693-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -13154,10 +13154,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45967</v>
+        <v>45956</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13170,7 +13170,7 @@
         </is>
       </c>
       <c r="I133" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -13213,7 +13213,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 54874-2025</t>
+          <t>A 7580-2026</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -13227,10 +13227,10 @@
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45967</v>
+        <v>46061</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13243,7 +13243,7 @@
         </is>
       </c>
       <c r="I134" t="n">
-        <v>5.3</v>
+        <v>1.5</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -13303,7 +13303,7 @@
         <v>45966</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13359,7 +13359,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 55288-2025</t>
+          <t>A 54874-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -13373,10 +13373,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45969</v>
+        <v>45967</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13389,7 +13389,7 @@
         </is>
       </c>
       <c r="I136" t="n">
-        <v>2.6</v>
+        <v>5.3</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -13432,7 +13432,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 55287-2025</t>
+          <t>A 11607-2023</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -13446,10 +13446,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45969</v>
+        <v>44994</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13461,8 +13461,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I137" t="n">
-        <v>2.7</v>
+        <v>1.1</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -13505,7 +13510,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 8510-2023</t>
+          <t>A 54876-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -13519,10 +13524,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>44977</v>
+        <v>45967</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13535,7 +13540,7 @@
         </is>
       </c>
       <c r="I138" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="J138" t="n">
         <v>0</v>
@@ -13578,7 +13583,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 2546-2026</t>
+          <t>A 54877-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -13592,10 +13597,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>46037</v>
+        <v>45967</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13608,7 +13613,7 @@
         </is>
       </c>
       <c r="I139" t="n">
-        <v>5</v>
+        <v>0.9</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -13651,7 +13656,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 2220-2026</t>
+          <t>A 55287-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -13665,10 +13670,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46036</v>
+        <v>45969</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13681,7 +13686,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -13724,7 +13729,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 3615-2026</t>
+          <t>A 55288-2025</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -13738,10 +13743,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>46042</v>
+        <v>45969</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13754,7 +13759,7 @@
         </is>
       </c>
       <c r="I141" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -13797,7 +13802,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 57596-2025</t>
+          <t>A 4566-2026</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -13811,10 +13816,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45980</v>
+        <v>46047</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13827,7 +13832,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>1.9</v>
+        <v>1.1</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -13887,7 +13892,7 @@
         <v>45980</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13960,7 +13965,7 @@
         <v>45980</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14016,7 +14021,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 57594-2025</t>
+          <t>A 57596-2025</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -14033,7 +14038,7 @@
         <v>45980</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14046,7 +14051,7 @@
         </is>
       </c>
       <c r="I145" t="n">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -14089,7 +14094,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 58633-2025</t>
+          <t>A 57594-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -14103,10 +14108,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45986</v>
+        <v>45980</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14119,7 +14124,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.3</v>
+        <v>0.9</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -14162,7 +14167,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 58805-2025</t>
+          <t>A 58633-2025</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -14179,7 +14184,7 @@
         <v>45986</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14235,7 +14240,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 5549-2026</t>
+          <t>A 58805-2025</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -14249,10 +14254,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>46050</v>
+        <v>45986</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14265,7 +14270,7 @@
         </is>
       </c>
       <c r="I148" t="n">
-        <v>2.4</v>
+        <v>1.3</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -14308,7 +14313,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 47495-2024</t>
+          <t>A 11953-2025</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -14322,10 +14327,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45587</v>
+        <v>45728</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14343,7 +14348,7 @@
         </is>
       </c>
       <c r="I149" t="n">
-        <v>5.2</v>
+        <v>34.8</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -14386,7 +14391,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 30007-2024</t>
+          <t>A 37743-2022</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -14400,10 +14405,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45488</v>
+        <v>44810</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14415,13 +14420,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I150" t="n">
-        <v>11.5</v>
+        <v>1.6</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -14464,7 +14464,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 30009-2024</t>
+          <t>A 11462-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -14478,10 +14478,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45488</v>
+        <v>46083</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14493,13 +14493,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I151" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -14542,7 +14537,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 37763-2023</t>
+          <t>A 61186-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -14556,10 +14551,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>45156</v>
+        <v>46000</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14572,7 +14567,7 @@
         </is>
       </c>
       <c r="I152" t="n">
-        <v>2.9</v>
+        <v>4.2</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -14615,7 +14610,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 35505-2024</t>
+          <t>A 51337-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -14629,10 +14624,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>45531</v>
+        <v>45219</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14642,11 +14637,6 @@
       <c r="G153" t="inlineStr">
         <is>
           <t>HOFORS</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I153" t="n">
@@ -14693,7 +14683,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 61186-2025</t>
+          <t>A 61642-2025</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -14707,10 +14697,10 @@
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14723,7 +14713,7 @@
         </is>
       </c>
       <c r="I154" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -14766,7 +14756,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 30229-2024</t>
+          <t>A 17185-2025</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -14780,10 +14770,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45490</v>
+        <v>45755</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14797,11 +14787,11 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I155" t="n">
-        <v>3.3</v>
+        <v>10.3</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -14844,7 +14834,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 2612-2025</t>
+          <t>A 12803-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -14854,14 +14844,14 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45674</v>
+        <v>46092</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14873,8 +14863,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I156" t="n">
-        <v>3.8</v>
+        <v>7.4</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -14917,7 +14912,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 7580-2026</t>
+          <t>A 37680-2022</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -14931,10 +14926,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46061</v>
+        <v>44810</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14947,7 +14942,7 @@
         </is>
       </c>
       <c r="I157" t="n">
-        <v>1.5</v>
+        <v>6.6</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -14990,7 +14985,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 23376-2024</t>
+          <t>A 15810-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -15004,10 +14999,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45453</v>
+        <v>46107</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15025,7 +15020,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>10.8</v>
+        <v>0.7</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -15068,7 +15063,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 4566-2026</t>
+          <t>A 28133-2024</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -15082,10 +15077,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46047</v>
+        <v>45476</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15098,7 +15093,7 @@
         </is>
       </c>
       <c r="I159" t="n">
-        <v>1.1</v>
+        <v>3.8</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -15141,7 +15136,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 58955-2023</t>
+          <t>A 33978-2024</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -15155,10 +15150,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45252</v>
+        <v>45523</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15171,7 +15166,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -15214,7 +15209,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 6963-2024</t>
+          <t>A 33984-2024</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -15228,10 +15223,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45343</v>
+        <v>45523</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15244,7 +15239,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>2.4</v>
+        <v>0.5</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -15287,7 +15282,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 11462-2026</t>
+          <t>A 17170-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -15301,10 +15296,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>46083</v>
+        <v>46115</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15317,7 +15312,7 @@
         </is>
       </c>
       <c r="I162" t="n">
-        <v>0.8</v>
+        <v>2.7</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -15377,7 +15372,7 @@
         <v>45538</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15433,7 +15428,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 12803-2026</t>
+          <t>A 8321-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -15447,10 +15442,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46092</v>
+        <v>46064</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15462,13 +15457,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I164" t="n">
-        <v>7.4</v>
+        <v>0.9</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -15511,7 +15501,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 21027-2024</t>
+          <t>A 11873-2026</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -15525,10 +15515,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>45439</v>
+        <v>46085</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15540,13 +15530,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I165" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -15589,7 +15574,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 21028-2024</t>
+          <t>A 12705-2026</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -15603,10 +15588,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45439</v>
+        <v>46091</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15620,11 +15605,11 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I166" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -15667,7 +15652,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 16371-2022</t>
+          <t>A 10161-2023</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -15681,10 +15666,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>44671</v>
+        <v>44986</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15696,8 +15681,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I167" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -15740,7 +15730,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 57751-2024</t>
+          <t>A 19401-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -15754,10 +15744,10 @@
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>45630</v>
+        <v>46133</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15769,8 +15759,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -15813,7 +15808,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 15810-2026</t>
+          <t>A 31611-2023</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -15823,14 +15818,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46107</v>
+        <v>45117</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15842,13 +15837,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I169" t="n">
-        <v>0.7</v>
+        <v>4.4</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -15891,7 +15881,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 2915-2025</t>
+          <t>A 11871-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -15905,10 +15895,10 @@
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>45677</v>
+        <v>46085</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15921,7 +15911,7 @@
         </is>
       </c>
       <c r="I170" t="n">
-        <v>1.9</v>
+        <v>1.3</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -15964,7 +15954,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 32980-2023</t>
+          <t>A 11277-2026</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15978,10 +15968,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>45125</v>
+        <v>46080</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15993,8 +15983,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>0.7</v>
+        <v>2.1</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -16037,7 +16032,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 62596-2023</t>
+          <t>A 43885-2025</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -16051,10 +16046,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>45271</v>
+        <v>45912</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16066,8 +16061,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I172" t="n">
-        <v>3.6</v>
+        <v>1.6</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -16110,7 +16110,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 17170-2026</t>
+          <t>A 15217-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -16124,10 +16124,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46115</v>
+        <v>46105</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16139,8 +16139,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -16183,7 +16188,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 8448-2025</t>
+          <t>A 25474-2024</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -16197,10 +16202,10 @@
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>45709</v>
+        <v>45463</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16212,8 +16217,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>1.7</v>
+        <v>0.9</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -16256,7 +16266,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 47493-2024</t>
+          <t>A 8510-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -16270,10 +16280,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>45587</v>
+        <v>44977</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16285,13 +16295,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H175" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I175" t="n">
-        <v>3.9</v>
+        <v>0.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -16334,7 +16339,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 8321-2026</t>
+          <t>A 27738-2024</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -16348,10 +16353,10 @@
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46064</v>
+        <v>45475</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16363,8 +16368,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I176" t="n">
-        <v>0.9</v>
+        <v>2.6</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -16407,7 +16417,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 11873-2026</t>
+          <t>A 16888-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -16421,10 +16431,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46085</v>
+        <v>46113</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16437,7 +16447,7 @@
         </is>
       </c>
       <c r="I177" t="n">
-        <v>0.5</v>
+        <v>2</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -16480,7 +16490,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 12705-2026</t>
+          <t>A 31607-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -16490,14 +16500,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46091</v>
+        <v>45117</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16509,13 +16519,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>1.3</v>
+        <v>3.8</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -16558,7 +16563,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 10161-2023</t>
+          <t>A 13744-2023</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -16572,10 +16577,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>44986</v>
+        <v>45007</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16593,7 +16598,7 @@
         </is>
       </c>
       <c r="I179" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -16636,7 +16641,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 19401-2026</t>
+          <t>A 24988-2023</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -16650,10 +16655,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46133</v>
+        <v>45085</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16667,11 +16672,11 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I180" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -16714,7 +16719,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 34232-2023</t>
+          <t>A 35136-2023</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -16728,10 +16733,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45127</v>
+        <v>45145</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16743,13 +16748,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I181" t="n">
-        <v>5.8</v>
+        <v>2</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -16792,7 +16792,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 43885-2025</t>
+          <t>A 22129-2023</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -16802,14 +16802,14 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>45912</v>
+        <v>45069</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16827,7 +16827,7 @@
         </is>
       </c>
       <c r="I182" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -16870,7 +16870,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 11277-2026</t>
+          <t>A 12922-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -16884,10 +16884,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46080</v>
+        <v>46092</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -16948,7 +16948,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 25474-2024</t>
+          <t>A 57400-2024</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -16962,10 +16962,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>45463</v>
+        <v>45629</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16977,13 +16977,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>0.9</v>
+        <v>2.7</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -17026,7 +17021,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 22226-2024</t>
+          <t>A 37693-2023</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -17040,10 +17035,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45446</v>
+        <v>45159</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17099,7 +17094,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 15217-2026</t>
+          <t>A 37763-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -17113,10 +17108,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>46105</v>
+        <v>45156</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17128,13 +17123,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I186" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -17177,7 +17167,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 12922-2026</t>
+          <t>A 3614-2026</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -17191,10 +17181,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46092</v>
+        <v>46042</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17206,13 +17196,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -17255,7 +17240,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 57400-2024</t>
+          <t>A 3391-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -17269,10 +17254,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>45629</v>
+        <v>46042</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17285,7 +17270,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -17328,7 +17313,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 37693-2023</t>
+          <t>A 23545-2025</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -17338,14 +17323,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45159</v>
+        <v>45792</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17358,7 +17343,7 @@
         </is>
       </c>
       <c r="I189" t="n">
-        <v>0.6</v>
+        <v>3.5</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -17401,7 +17386,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 11871-2026</t>
+          <t>A 23326-2026</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -17415,10 +17400,10 @@
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>46085</v>
+        <v>46162</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17430,8 +17415,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -17474,7 +17464,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 16888-2026</t>
+          <t>A 23334-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -17488,10 +17478,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46113</v>
+        <v>46162</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17503,8 +17493,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I191" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -17547,7 +17542,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 22129-2023</t>
+          <t>A 35498-2024</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -17557,14 +17552,14 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>45069</v>
+        <v>45531</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17582,7 +17577,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -17625,7 +17620,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 17762-2022</t>
+          <t>A 23833-2026</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -17635,14 +17630,14 @@
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>44680</v>
+        <v>46167</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17652,6 +17647,11 @@
       <c r="G193" t="inlineStr">
         <is>
           <t>HOFORS</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I193" t="n">
@@ -17698,7 +17698,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 3391-2026</t>
+          <t>A 8448-2025</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -17712,10 +17712,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>46042</v>
+        <v>45709</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17728,7 +17728,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>0.7</v>
+        <v>1.7</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -17771,7 +17771,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 23545-2025</t>
+          <t>A 17762-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -17781,14 +17781,14 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45792</v>
+        <v>44680</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17801,7 +17801,7 @@
         </is>
       </c>
       <c r="I195" t="n">
-        <v>3.5</v>
+        <v>1</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -17844,7 +17844,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 3614-2026</t>
+          <t>A 24342-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -17854,14 +17854,14 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>46042</v>
+        <v>46169</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17873,8 +17873,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -17917,7 +17922,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 23334-2026</t>
+          <t>A 24258-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -17931,10 +17936,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17946,13 +17951,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H197" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I197" t="n">
-        <v>0.5</v>
+        <v>2.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -17995,7 +17995,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 23326-2026</t>
+          <t>A 33296-2023</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -18009,10 +18009,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>46162</v>
+        <v>45127</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18030,7 +18030,7 @@
         </is>
       </c>
       <c r="I198" t="n">
-        <v>1.4</v>
+        <v>6.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -18073,7 +18073,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 23833-2026</t>
+          <t>A 17179-2025</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -18087,10 +18087,10 @@
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46167</v>
+        <v>45755</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18104,11 +18104,11 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I199" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -18151,7 +18151,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 47459-2023</t>
+          <t>A 58955-2023</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -18165,10 +18165,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>45202</v>
+        <v>45252</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18181,7 +18181,7 @@
         </is>
       </c>
       <c r="I200" t="n">
-        <v>6</v>
+        <v>1.4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -18224,7 +18224,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 24258-2026</t>
+          <t>A 64359-2023</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -18238,10 +18238,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46169</v>
+        <v>45280</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>2.9</v>
+        <v>4.7</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -18297,7 +18297,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 24342-2026</t>
+          <t>A 58373-2023</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -18307,14 +18307,14 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46169</v>
+        <v>45250</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18326,13 +18326,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I202" t="n">
-        <v>1.5</v>
+        <v>0.6</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -18375,7 +18370,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 35136-2023</t>
+          <t>A 26516-2026</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -18385,14 +18380,14 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45145</v>
+        <v>46183</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18404,8 +18399,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -18448,7 +18448,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 38251-2022</t>
+          <t>A 26515-2026</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -18458,14 +18458,14 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>44812</v>
+        <v>46183</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18477,8 +18477,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>3.5</v>
+        <v>1.4</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -18521,7 +18526,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 31607-2023</t>
+          <t>A 38251-2022</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -18531,14 +18536,14 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>45117</v>
+        <v>44812</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18551,7 +18556,7 @@
         </is>
       </c>
       <c r="I205" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -18594,7 +18599,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 31611-2023</t>
+          <t>A 28330-2026</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -18604,14 +18609,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45117</v>
+        <v>46196</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18623,8 +18628,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I206" t="n">
-        <v>4.4</v>
+        <v>1.1</v>
       </c>
       <c r="J206" t="n">
         <v>0</v>
@@ -18667,7 +18677,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 26515-2026</t>
+          <t>A 28329-2026</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -18677,14 +18687,14 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46183</v>
+        <v>46196</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18702,7 +18712,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>1.4</v>
+        <v>3.1</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -18745,7 +18755,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 26516-2026</t>
+          <t>A 47459-2023</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -18755,14 +18765,14 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>46183</v>
+        <v>45202</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18774,13 +18784,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H208" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I208" t="n">
-        <v>1.8</v>
+        <v>6</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -18823,7 +18828,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 47359-2024</t>
+          <t>A 68079-2021</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -18837,10 +18842,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>45587</v>
+        <v>44526</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18853,7 +18858,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>1.2</v>
+        <v>2.3</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -18896,7 +18901,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 31645-2024</t>
+          <t>A 29060-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -18910,10 +18915,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>45506</v>
+        <v>46199</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18931,7 +18936,7 @@
         </is>
       </c>
       <c r="I210" t="n">
-        <v>11.1</v>
+        <v>3.1</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -18974,7 +18979,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 64359-2023</t>
+          <t>A 54826-2021</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -18988,10 +18993,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45280</v>
+        <v>44473</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19003,8 +19008,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I211" t="n">
-        <v>4.7</v>
+        <v>6</v>
       </c>
       <c r="J211" t="n">
         <v>0</v>
@@ -19047,7 +19057,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 58787-2021</t>
+          <t>A 44356-2023</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -19061,10 +19071,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44489</v>
+        <v>45188</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19077,7 +19087,7 @@
         </is>
       </c>
       <c r="I212" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -19120,7 +19130,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 24988-2023</t>
+          <t>A 47495-2024</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -19134,10 +19144,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45085</v>
+        <v>45587</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19155,7 +19165,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>1.9</v>
+        <v>5.2</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -19198,7 +19208,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 28330-2026</t>
+          <t>A 30638-2026</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -19212,10 +19222,10 @@
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46196</v>
+        <v>46211</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19227,13 +19237,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I214" t="n">
-        <v>1.1</v>
+        <v>8</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -19276,7 +19281,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 28329-2026</t>
+          <t>A 10602-2022</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -19290,10 +19295,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>46196</v>
+        <v>44624</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19305,13 +19310,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I215" t="n">
-        <v>3.1</v>
+        <v>7</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -19354,7 +19354,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 29060-2026</t>
+          <t>A 34993-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -19368,10 +19368,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46199</v>
+        <v>46259</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19389,7 +19389,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>3.1</v>
+        <v>6.7</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -19432,7 +19432,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 13473-2024</t>
+          <t>A 31088-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -19446,10 +19446,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>45387</v>
+        <v>46216</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19461,8 +19461,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I217" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -19505,7 +19510,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 28133-2024</t>
+          <t>A 35219-2026</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -19519,10 +19524,10 @@
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45476</v>
+        <v>46260</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19534,8 +19539,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I218" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -19578,7 +19588,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 37744-2022</t>
+          <t>A 31613-2023</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -19588,14 +19598,14 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>44810</v>
+        <v>45117</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19608,7 +19618,7 @@
         </is>
       </c>
       <c r="I219" t="n">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -19651,7 +19661,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 10602-2022</t>
+          <t>A 31315-2026</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -19665,10 +19675,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>44624</v>
+        <v>46219</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19681,7 +19691,7 @@
         </is>
       </c>
       <c r="I220" t="n">
-        <v>7</v>
+        <v>0.9</v>
       </c>
       <c r="J220" t="n">
         <v>0</v>
@@ -19724,7 +19734,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 30638-2026</t>
+          <t>A 6958-2024</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -19738,10 +19748,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>46211</v>
+        <v>45343</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19754,7 +19764,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>8</v>
+        <v>3.4</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -19797,7 +19807,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 34993-2026</t>
+          <t>A 57632-2021</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -19811,10 +19821,10 @@
         </is>
       </c>
       <c r="D222" s="1" t="n">
-        <v>46259</v>
+        <v>44484</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19826,13 +19836,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I222" t="n">
-        <v>6.7</v>
+        <v>4.1</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -19875,7 +19880,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 31087-2026</t>
+          <t>A 47493-2024</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -19889,10 +19894,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46216</v>
+        <v>45587</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19906,11 +19911,11 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I223" t="n">
-        <v>1.5</v>
+        <v>3.9</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -19953,7 +19958,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 31088-2026</t>
+          <t>A 34232-2023</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -19967,10 +19972,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46216</v>
+        <v>45127</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19984,11 +19989,11 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Kommuner</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I224" t="n">
-        <v>1.3</v>
+        <v>5.8</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -20031,7 +20036,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 11607-2023</t>
+          <t>A 36278-2026</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -20045,10 +20050,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>44994</v>
+        <v>46268</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20060,13 +20065,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>1.1</v>
+        <v>2.8</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -20109,7 +20109,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 35504-2024</t>
+          <t>A 36707-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -20123,10 +20123,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45531</v>
+        <v>46272</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20138,13 +20138,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I226" t="n">
-        <v>1.8</v>
+        <v>3.3</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -20187,7 +20182,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 68079-2021</t>
+          <t>A 36808-2026</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -20201,10 +20196,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>44526</v>
+        <v>46272</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20217,7 +20212,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>2.3</v>
+        <v>3.1</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -20260,7 +20255,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 35219-2026</t>
+          <t>A 21027-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -20274,10 +20269,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>46260</v>
+        <v>45439</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20295,7 +20290,7 @@
         </is>
       </c>
       <c r="I228" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J228" t="n">
         <v>0</v>
@@ -20338,7 +20333,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 31315-2026</t>
+          <t>A 21028-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -20352,10 +20347,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46219</v>
+        <v>45439</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20367,8 +20362,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H229" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I229" t="n">
-        <v>0.9</v>
+        <v>1.6</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -20411,7 +20411,7 @@
     <row r="230" ht="15" customHeight="1">
       <c r="A230" t="inlineStr">
         <is>
-          <t>A 6958-2024</t>
+          <t>A 2612-2025</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -20421,14 +20421,14 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D230" s="1" t="n">
-        <v>45343</v>
+        <v>45674</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         </is>
       </c>
       <c r="I230" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="J230" t="n">
         <v>0</v>
@@ -20484,7 +20484,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 54826-2021</t>
+          <t>A 37148-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -20498,10 +20498,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>44473</v>
+        <v>46274</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20513,13 +20513,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I231" t="n">
-        <v>6</v>
+        <v>0.4</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -20562,7 +20557,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 36278-2026</t>
+          <t>A 32980-2023</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -20576,10 +20571,10 @@
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>46268</v>
+        <v>45125</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20592,7 +20587,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>2.8</v>
+        <v>0.7</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -20635,7 +20630,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 17185-2025</t>
+          <t>A 37182-2026</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -20649,10 +20644,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>45755</v>
+        <v>46274</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20664,13 +20659,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H233" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I233" t="n">
-        <v>10.3</v>
+        <v>4</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -20713,7 +20703,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 36707-2026</t>
+          <t>A 57751-2024</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -20727,10 +20717,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>46272</v>
+        <v>45630</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20743,7 +20733,7 @@
         </is>
       </c>
       <c r="I234" t="n">
-        <v>3.3</v>
+        <v>1.8</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -20786,7 +20776,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 36808-2026</t>
+          <t>A 35504-2024</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -20800,10 +20790,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>46272</v>
+        <v>45531</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20815,8 +20805,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H235" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I235" t="n">
-        <v>3.1</v>
+        <v>1.8</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -20859,7 +20854,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 37148-2026</t>
+          <t>A 34980-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -20873,10 +20868,10 @@
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>46274</v>
+        <v>46259</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20888,8 +20883,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H236" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I236" t="n">
-        <v>0.4</v>
+        <v>1.7</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -20932,7 +20932,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 37182-2026</t>
+          <t>A 2915-2025</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -20946,10 +20946,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>46274</v>
+        <v>45677</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         </is>
       </c>
       <c r="I237" t="n">
-        <v>4</v>
+        <v>1.9</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -21005,7 +21005,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 31613-2023</t>
+          <t>A 4032-2025</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -21015,14 +21015,14 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45117</v>
+        <v>45684</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.2</v>
+        <v>2.7</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -21078,7 +21078,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 36283-2024</t>
+          <t>A 28391-2024</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -21092,10 +21092,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45534</v>
+        <v>45477</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         </is>
       </c>
       <c r="I239" t="n">
-        <v>6.9</v>
+        <v>2.7</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -21156,7 +21156,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 64036-2025</t>
+          <t>A 21340-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -21170,10 +21170,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>46021</v>
+        <v>45782</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21186,7 +21186,7 @@
         </is>
       </c>
       <c r="I240" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -21229,7 +21229,7 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 1144-2024</t>
+          <t>A 39529-2026</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -21243,10 +21243,10 @@
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45302</v>
+        <v>46289</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>0.9</v>
+        <v>3.3</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -21302,7 +21302,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>A 21340-2025</t>
+          <t>A 1144-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -21316,10 +21316,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45782</v>
+        <v>45302</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21332,7 +21332,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -21392,7 +21392,7 @@
         <v>45334</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21448,7 +21448,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A 34980-2026</t>
+          <t>A 64036-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -21462,10 +21462,10 @@
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>46259</v>
+        <v>46021</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21477,13 +21477,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H244" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I244" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -21526,7 +21521,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>A 39529-2026</t>
+          <t>A 31087-2026</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -21540,10 +21535,10 @@
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>46289</v>
+        <v>46216</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21555,8 +21550,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H245" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I245" t="n">
-        <v>3.3</v>
+        <v>1.5</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -21616,7 +21616,7 @@
         <v>45700</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21694,7 +21694,7 @@
         <v>45316</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21772,7 +21772,7 @@
         <v>45319</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21850,7 +21850,7 @@
         <v>45771</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21928,7 +21928,7 @@
         <v>45707</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -22006,7 +22006,7 @@
         <v>45895</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>
@@ -22084,7 +22084,7 @@
         <v>46069</v>
       </c>
       <c r="E252" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F252" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>46089</v>
       </c>
       <c r="E253" s="1" t="n">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="F253" t="inlineStr">
         <is>

--- a/Översikt HOFORS.xlsx
+++ b/Översikt HOFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46064</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>45784</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>46164</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45299</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>46079</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>46163</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>46085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>46266</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45316</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45163</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45813</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>44623</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>45860</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>46199</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44816</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>46025</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>46043</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>45895</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45895</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>45813</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>46095</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>46154</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>45874</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>45935</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>46177</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>46199</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44102</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44169</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>44585</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>45317</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45701</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>45895</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45895</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>46142</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>46125</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>44649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>44559</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>45477</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45917</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44928</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>45477</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>45453</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>45924</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>45813</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>45813</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>45813</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>45813</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>46091</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>45488</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>45597</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>45531</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>44624</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>45348</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>45860</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>45870</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>45874</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>45881</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>46183</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>45589</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>46196</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>45007</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>45127</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>46217</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>46217</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>46262</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>45534</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>45531</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>46252</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>44473</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>45701</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>45727</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>45706</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>44868</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>44582</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>44501</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         <v>44512</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>44873</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>44868</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44692</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>45755</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>45531</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>44967</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>45523</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         <v>45523</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>45376</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>46002</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>45477</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>45887</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9965,7 +9965,7 @@
         <v>45884</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>45684</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>45127</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>45219</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>45895</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>45232</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>46029</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>46029</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>44810</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         <v>46030</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>46037</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>46036</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>45792</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>46042</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         <v>44487</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>45523</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>45917</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>45614</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>46050</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>45387</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>45929</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>45930</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>45728</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>45933</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>46061</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>45816</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>45933</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>45933</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>45933</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45475</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>45935</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>44810</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>46047</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>44484</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>45250</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12575,7 +12575,7 @@
         <v>45173</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>45947</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>45188</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>45453</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>46083</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>45007</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>45956</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>46092</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>44977</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>45966</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>45969</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>45969</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>45980</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>45980</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>45980</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>46107</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>45980</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>45587</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>45488</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>45488</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>45986</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>45986</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14226,7 +14226,7 @@
         <v>46115</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>45156</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14372,7 +14372,7 @@
         <v>45531</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>45805</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>45490</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>46085</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>45674</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>46091</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>46000</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>46133</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>45453</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>45252</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>45833</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>45343</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>45835</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>45538</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>45912</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>45439</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>45439</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>44671</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>45630</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>46080</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>45463</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>46105</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>46092</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>45677</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>45629</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>45125</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>46085</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>45271</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>45709</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>46113</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>45587</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>45868</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>45069</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>44986</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>46042</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>45792</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17080,7 +17080,7 @@
         <v>46042</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>45127</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>46162</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
         <v>45877</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>46162</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>46167</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>46169</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>46169</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>45446</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>45159</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>46183</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>46183</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>44680</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>46196</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>46196</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>46199</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45202</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>46211</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>46259</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>46216</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>45145</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>46260</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>44812</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>46219</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>45117</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>45117</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>46268</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>46272</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>46272</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>46274</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>46274</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         <v>45587</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>45506</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>45280</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>44489</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>45085</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>46259</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>46289</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>45387</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
         <v>45476</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>44810</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>44624</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>46021</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>46216</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20382,7 +20382,7 @@
         <v>44994</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>45967</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>46064</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20606,7 +20606,7 @@
         <v>45967</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>45967</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>45531</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>44526</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20903,7 +20903,7 @@
         <v>45343</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>44473</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21054,7 +21054,7 @@
         <v>45755</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21132,7 +21132,7 @@
         <v>45117</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>45302</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>45782</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>45334</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>45700</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>45316</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>45319</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>45771</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>45707</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>45895</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>46069</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>46089</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46298</v>
+        <v>46299</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>

--- a/Översikt HOFORS.xlsx
+++ b/Översikt HOFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46064</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>45784</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>46164</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45299</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>46079</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>46163</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>46085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>46266</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45316</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45163</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45813</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>44623</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>45860</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>46199</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44816</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>46025</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2483,7 +2483,7 @@
         <v>46043</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2594,7 +2594,7 @@
         <v>45895</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45895</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>45813</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>46095</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3033,7 +3033,7 @@
         <v>46154</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3143,7 +3143,7 @@
         <v>45874</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>45935</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>46177</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>46199</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44102</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44169</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>44585</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>45317</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45701</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>45895</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45895</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>46142</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>46125</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>44649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>44559</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>45477</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>45917</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5134,7 +5134,7 @@
         <v>44928</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>45477</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>45453</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>45924</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>45813</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5688,7 +5688,7 @@
         <v>45813</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5798,7 +5798,7 @@
         <v>45813</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5908,7 +5908,7 @@
         <v>45813</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6018,7 +6018,7 @@
         <v>46091</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6127,7 +6127,7 @@
         <v>45488</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6237,7 +6237,7 @@
         <v>45597</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6342,7 +6342,7 @@
         <v>45531</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>44624</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>45348</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>45860</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>45870</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>45874</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>45881</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7106,7 +7106,7 @@
         <v>46183</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7216,7 +7216,7 @@
         <v>45589</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7321,7 +7321,7 @@
         <v>46196</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>45007</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>45127</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>46217</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>46217</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>46262</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>45534</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>45531</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>46252</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>44473</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8433,7 +8433,7 @@
         <v>45701</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8543,7 +8543,7 @@
         <v>45727</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8657,7 +8657,7 @@
         <v>45706</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8767,7 +8767,7 @@
         <v>44868</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8845,7 +8845,7 @@
         <v>44582</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>44501</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8991,7 +8991,7 @@
         <v>44512</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -9064,7 +9064,7 @@
         <v>44873</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9137,7 +9137,7 @@
         <v>44868</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44692</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9288,7 +9288,7 @@
         <v>45755</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9366,7 +9366,7 @@
         <v>45531</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>44967</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>45523</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9590,7 +9590,7 @@
         <v>45523</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9663,7 +9663,7 @@
         <v>45376</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9736,7 +9736,7 @@
         <v>46002</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9809,7 +9809,7 @@
         <v>45477</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9887,7 +9887,7 @@
         <v>45887</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9965,7 +9965,7 @@
         <v>45884</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -10038,7 +10038,7 @@
         <v>45684</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10111,7 +10111,7 @@
         <v>45127</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10189,7 +10189,7 @@
         <v>45219</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10262,7 +10262,7 @@
         <v>45895</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10340,7 +10340,7 @@
         <v>45232</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10413,7 +10413,7 @@
         <v>46029</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
         <v>46029</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>44810</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10632,7 +10632,7 @@
         <v>46030</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>46037</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>46036</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10851,7 +10851,7 @@
         <v>45792</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10924,7 +10924,7 @@
         <v>46042</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         <v>44487</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11070,7 +11070,7 @@
         <v>45523</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11143,7 +11143,7 @@
         <v>45917</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11221,7 +11221,7 @@
         <v>45614</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11294,7 +11294,7 @@
         <v>46050</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11367,7 +11367,7 @@
         <v>45387</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11440,7 +11440,7 @@
         <v>45929</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>45930</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11586,7 +11586,7 @@
         <v>45728</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11664,7 +11664,7 @@
         <v>45933</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11742,7 +11742,7 @@
         <v>46061</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11815,7 +11815,7 @@
         <v>45816</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11893,7 +11893,7 @@
         <v>45933</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>45933</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12049,7 +12049,7 @@
         <v>45933</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12127,7 +12127,7 @@
         <v>45475</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12205,7 +12205,7 @@
         <v>45935</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12283,7 +12283,7 @@
         <v>44810</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>46047</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12429,7 +12429,7 @@
         <v>44484</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>45250</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12575,7 +12575,7 @@
         <v>45173</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12653,7 +12653,7 @@
         <v>45947</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12731,7 +12731,7 @@
         <v>45188</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12804,7 +12804,7 @@
         <v>45453</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>46083</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12955,7 +12955,7 @@
         <v>45007</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -13033,7 +13033,7 @@
         <v>45956</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13106,7 +13106,7 @@
         <v>46092</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>44977</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13257,7 +13257,7 @@
         <v>45966</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>45969</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13403,7 +13403,7 @@
         <v>45969</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13476,7 +13476,7 @@
         <v>45980</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13549,7 +13549,7 @@
         <v>45980</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13622,7 +13622,7 @@
         <v>45980</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>46107</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>45980</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13846,7 +13846,7 @@
         <v>45587</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>45488</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -14002,7 +14002,7 @@
         <v>45488</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14080,7 +14080,7 @@
         <v>45986</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>45986</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14226,7 +14226,7 @@
         <v>46115</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14299,7 +14299,7 @@
         <v>45156</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14372,7 +14372,7 @@
         <v>45531</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14450,7 +14450,7 @@
         <v>45805</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14523,7 +14523,7 @@
         <v>45490</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14601,7 +14601,7 @@
         <v>46085</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14674,7 +14674,7 @@
         <v>45674</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14747,7 +14747,7 @@
         <v>46091</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14825,7 +14825,7 @@
         <v>46000</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14898,7 +14898,7 @@
         <v>46133</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>45453</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15054,7 +15054,7 @@
         <v>45252</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15127,7 +15127,7 @@
         <v>45833</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15200,7 +15200,7 @@
         <v>45343</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15273,7 +15273,7 @@
         <v>45835</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>45538</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15424,7 +15424,7 @@
         <v>45912</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>45439</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15580,7 +15580,7 @@
         <v>45439</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15658,7 +15658,7 @@
         <v>44671</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15731,7 +15731,7 @@
         <v>45630</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15804,7 +15804,7 @@
         <v>46080</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15882,7 +15882,7 @@
         <v>45463</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>46105</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -16038,7 +16038,7 @@
         <v>46092</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16116,7 +16116,7 @@
         <v>45677</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16189,7 +16189,7 @@
         <v>45629</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16262,7 +16262,7 @@
         <v>45125</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16335,7 +16335,7 @@
         <v>46085</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16408,7 +16408,7 @@
         <v>45271</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16481,7 +16481,7 @@
         <v>45709</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16554,7 +16554,7 @@
         <v>46113</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16627,7 +16627,7 @@
         <v>45587</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16705,7 +16705,7 @@
         <v>45868</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16778,7 +16778,7 @@
         <v>45069</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>44986</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16934,7 +16934,7 @@
         <v>46042</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -17007,7 +17007,7 @@
         <v>45792</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17080,7 +17080,7 @@
         <v>46042</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>45127</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17231,7 +17231,7 @@
         <v>46162</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17309,7 +17309,7 @@
         <v>45877</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17387,7 +17387,7 @@
         <v>46162</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17465,7 +17465,7 @@
         <v>46167</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>46169</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17616,7 +17616,7 @@
         <v>46169</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17694,7 +17694,7 @@
         <v>45446</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17767,7 +17767,7 @@
         <v>45159</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17840,7 +17840,7 @@
         <v>46183</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>46183</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17996,7 +17996,7 @@
         <v>44680</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>46196</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>46196</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>46199</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>45202</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18376,7 +18376,7 @@
         <v>46211</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18449,7 +18449,7 @@
         <v>46259</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18527,7 +18527,7 @@
         <v>46216</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18605,7 +18605,7 @@
         <v>45145</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18678,7 +18678,7 @@
         <v>46260</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18756,7 +18756,7 @@
         <v>44812</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18829,7 +18829,7 @@
         <v>46219</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>45117</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18975,7 +18975,7 @@
         <v>45117</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -19048,7 +19048,7 @@
         <v>46268</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>46272</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19194,7 +19194,7 @@
         <v>46272</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19267,7 +19267,7 @@
         <v>46274</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>46274</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         <v>45587</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>45506</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19564,7 +19564,7 @@
         <v>45280</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19637,7 +19637,7 @@
         <v>44489</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19710,7 +19710,7 @@
         <v>45085</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19788,7 +19788,7 @@
         <v>46259</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>46289</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19939,7 +19939,7 @@
         <v>45387</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -20012,7 +20012,7 @@
         <v>45476</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20085,7 +20085,7 @@
         <v>44810</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20158,7 +20158,7 @@
         <v>44624</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>46021</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20304,7 +20304,7 @@
         <v>46216</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20382,7 +20382,7 @@
         <v>44994</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20460,7 +20460,7 @@
         <v>45967</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20533,7 +20533,7 @@
         <v>46064</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20606,7 +20606,7 @@
         <v>45967</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20679,7 +20679,7 @@
         <v>45967</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20752,7 +20752,7 @@
         <v>45531</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20830,7 +20830,7 @@
         <v>44526</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20903,7 +20903,7 @@
         <v>45343</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20976,7 +20976,7 @@
         <v>44473</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -21054,7 +21054,7 @@
         <v>45755</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21132,7 +21132,7 @@
         <v>45117</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>45302</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21278,7 +21278,7 @@
         <v>45782</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21351,7 +21351,7 @@
         <v>45334</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21424,7 +21424,7 @@
         <v>45700</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>45316</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21580,7 +21580,7 @@
         <v>45319</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21658,7 +21658,7 @@
         <v>45771</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21736,7 +21736,7 @@
         <v>45707</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21814,7 +21814,7 @@
         <v>45895</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21892,7 +21892,7 @@
         <v>46069</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>
@@ -21970,7 +21970,7 @@
         <v>46089</v>
       </c>
       <c r="E251" s="1" t="n">
-        <v>46299</v>
+        <v>46300</v>
       </c>
       <c r="F251" t="inlineStr">
         <is>

--- a/Översikt HOFORS.xlsx
+++ b/Översikt HOFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46064</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>45784</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>46164</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45299</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>46079</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>46163</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>46266</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>46085</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45316</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45163</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45813</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>44623</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>45860</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>46199</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44816</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45895</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>45895</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>45813</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>45874</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>46025</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>46043</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>46154</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>46095</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>45935</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>46177</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>46199</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44102</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44169</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>44585</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>45317</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45701</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>45895</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45895</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>46142</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>46125</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>44559</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>44649</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>45531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>45127</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45488</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>45917</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>45007</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>45531</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>45589</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>45597</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>45453</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>45813</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>45813</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>45813</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>45813</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>44624</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>45477</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>45348</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>45860</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>45477</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>45870</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>45874</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>45881</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>44928</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>45924</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>46091</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>46183</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>46196</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>46217</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>46217</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>46252</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>46262</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>45701</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>45727</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45706</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44868</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44582</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>44501</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>44512</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>44873</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44692</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>45531</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>44868</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>45538</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>45587</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>45127</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45453</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>45446</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>45387</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>45439</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>45439</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>45674</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>44986</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>45125</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>44810</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>45117</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>44487</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>45490</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>45884</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>45271</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>45887</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>45630</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>45376</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>45531</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>45895</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>45677</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10867,7 +10867,7 @@
         <v>45173</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>45684</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>44977</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>45475</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>45117</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>45477</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>45007</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>45488</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45488</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45085</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>45387</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>45782</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>44489</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>45302</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>45145</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>45343</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>45917</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>45506</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>45334</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>45930</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>45232</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45929</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         <v>45792</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>45614</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>45523</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>45933</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>45935</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>45933</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>44671</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>45816</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>45159</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>45156</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>45933</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>45587</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>45933</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>45453</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>44967</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>45531</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>45947</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>45709</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>45805</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>44680</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>44994</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>45956</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>45833</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>45127</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>45835</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>45966</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>45969</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>45969</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45755</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>45252</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>45728</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>45280</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>44810</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>45250</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>45219</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>45868</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>44812</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>45755</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>44810</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>45980</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>45980</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>45980</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>45877</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>45980</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>45202</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>45986</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>46107</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>44526</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>45476</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>45986</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>45523</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>45523</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16399,7 +16399,7 @@
         <v>46115</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>46085</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>46000</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>46002</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>46091</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>45188</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>45587</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>46085</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>44624</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>46080</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>45912</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>46029</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>46030</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>46105</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>46029</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>45463</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17597,7 +17597,7 @@
         <v>46036</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>46037</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17743,7 +17743,7 @@
         <v>46113</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>45117</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>46042</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>45343</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>44484</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>45069</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>46050</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>46092</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>46061</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
         <v>45629</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>46047</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>46042</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>46042</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>46083</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>45792</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>46092</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         <v>46162</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>46162</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>46167</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>46169</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>46183</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>46183</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>46196</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>46196</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>46199</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>46211</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>46216</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>46219</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>46268</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>46272</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>46272</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>46274</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20144,7 +20144,7 @@
         <v>46274</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>46289</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>46021</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>46216</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>46064</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>46300</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>46133</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>46300</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>45967</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45967</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>45967</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>46259</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>46259</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>46260</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
         <v>46169</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>45700</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>45316</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21420,7 +21420,7 @@
         <v>45319</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>45771</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>45707</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>45895</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>46069</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>46089</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46305</v>
+        <v>46306</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>

--- a/Översikt HOFORS.xlsx
+++ b/Översikt HOFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46064</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>45784</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>46164</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45299</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>46079</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>46163</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>46266</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1457,7 +1457,7 @@
         <v>46085</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45316</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45163</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45813</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>44623</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>45860</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>46199</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44816</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45895</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>45895</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>45813</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>45874</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2821,7 +2821,7 @@
         <v>46025</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2931,7 +2931,7 @@
         <v>46043</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3042,7 +3042,7 @@
         <v>46154</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3152,7 +3152,7 @@
         <v>46095</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3258,7 +3258,7 @@
         <v>45935</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>46177</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>46199</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44102</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44169</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>44585</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>45317</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45701</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>45895</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45895</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>46142</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>46125</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>44559</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>44649</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>45531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>45127</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45488</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>45917</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>45007</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>45531</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>45589</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5683,7 +5683,7 @@
         <v>45597</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5788,7 +5788,7 @@
         <v>45453</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>45813</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>45813</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6118,7 +6118,7 @@
         <v>45813</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6228,7 +6228,7 @@
         <v>45813</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>44624</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6443,7 +6443,7 @@
         <v>45477</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>45348</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>45860</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6768,7 +6768,7 @@
         <v>45477</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6878,7 +6878,7 @@
         <v>45870</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6988,7 +6988,7 @@
         <v>45874</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7098,7 +7098,7 @@
         <v>45881</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>44928</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7322,7 +7322,7 @@
         <v>45924</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7432,7 +7432,7 @@
         <v>46091</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7541,7 +7541,7 @@
         <v>46183</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>46196</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7761,7 +7761,7 @@
         <v>46217</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7871,7 +7871,7 @@
         <v>46217</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7981,7 +7981,7 @@
         <v>46252</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>46262</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>45701</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>45727</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45706</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44868</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44582</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>44501</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>44512</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>44873</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44692</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>45531</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>44868</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>45538</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>45587</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>45127</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>45453</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>45446</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>45387</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9591,7 +9591,7 @@
         <v>45439</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9669,7 +9669,7 @@
         <v>45439</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9747,7 +9747,7 @@
         <v>45674</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>44986</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9898,7 +9898,7 @@
         <v>45125</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>44810</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10044,7 +10044,7 @@
         <v>45117</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10117,7 +10117,7 @@
         <v>44487</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>45490</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10268,7 +10268,7 @@
         <v>45884</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>45271</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>45887</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10492,7 +10492,7 @@
         <v>45630</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10565,7 +10565,7 @@
         <v>45376</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>45531</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>45895</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10794,7 +10794,7 @@
         <v>45677</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10867,7 +10867,7 @@
         <v>45173</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>45684</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11018,7 +11018,7 @@
         <v>44977</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>45475</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>45117</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11242,7 +11242,7 @@
         <v>45477</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>45007</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11398,7 +11398,7 @@
         <v>45488</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>45488</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45085</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>45387</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11705,7 +11705,7 @@
         <v>45782</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11778,7 +11778,7 @@
         <v>44489</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11851,7 +11851,7 @@
         <v>45302</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11924,7 +11924,7 @@
         <v>45145</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>45343</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12070,7 +12070,7 @@
         <v>45917</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12148,7 +12148,7 @@
         <v>45506</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12226,7 +12226,7 @@
         <v>45334</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>45930</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12372,7 +12372,7 @@
         <v>45232</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12445,7 +12445,7 @@
         <v>45929</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12518,7 +12518,7 @@
         <v>45792</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12591,7 +12591,7 @@
         <v>45614</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12664,7 +12664,7 @@
         <v>45523</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>45933</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12815,7 +12815,7 @@
         <v>45935</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>45933</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12971,7 +12971,7 @@
         <v>44671</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13044,7 +13044,7 @@
         <v>45816</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13122,7 +13122,7 @@
         <v>45159</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13195,7 +13195,7 @@
         <v>45156</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>45933</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>45587</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13419,7 +13419,7 @@
         <v>45933</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13497,7 +13497,7 @@
         <v>45453</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>44967</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13648,7 +13648,7 @@
         <v>45531</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13726,7 +13726,7 @@
         <v>45947</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13804,7 +13804,7 @@
         <v>45709</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13877,7 +13877,7 @@
         <v>45805</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13950,7 +13950,7 @@
         <v>44680</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14023,7 +14023,7 @@
         <v>44994</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>45956</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>45833</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>45127</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14325,7 +14325,7 @@
         <v>45835</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14403,7 +14403,7 @@
         <v>45966</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>45969</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14549,7 +14549,7 @@
         <v>45969</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14622,7 +14622,7 @@
         <v>45755</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>45252</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14773,7 +14773,7 @@
         <v>45728</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>45280</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14924,7 +14924,7 @@
         <v>44810</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14997,7 +14997,7 @@
         <v>45250</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>45219</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15143,7 +15143,7 @@
         <v>45868</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15216,7 +15216,7 @@
         <v>44812</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>45755</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15367,7 +15367,7 @@
         <v>44810</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15440,7 +15440,7 @@
         <v>45980</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>45980</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15586,7 +15586,7 @@
         <v>45980</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15659,7 +15659,7 @@
         <v>45877</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>45980</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>45202</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>45986</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15956,7 +15956,7 @@
         <v>46107</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16034,7 +16034,7 @@
         <v>44526</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>45476</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>45986</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>45523</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>45523</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16399,7 +16399,7 @@
         <v>46115</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16472,7 +16472,7 @@
         <v>46085</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>46000</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16618,7 +16618,7 @@
         <v>46002</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>46091</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16769,7 +16769,7 @@
         <v>45188</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>45587</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16920,7 +16920,7 @@
         <v>46085</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16993,7 +16993,7 @@
         <v>44624</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>46080</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17144,7 +17144,7 @@
         <v>45912</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17222,7 +17222,7 @@
         <v>46029</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17295,7 +17295,7 @@
         <v>46030</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>46105</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>46029</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17519,7 +17519,7 @@
         <v>45463</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17597,7 +17597,7 @@
         <v>46036</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17670,7 +17670,7 @@
         <v>46037</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17743,7 +17743,7 @@
         <v>46113</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>45117</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>46042</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17962,7 +17962,7 @@
         <v>45343</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18035,7 +18035,7 @@
         <v>44484</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18108,7 +18108,7 @@
         <v>45069</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18186,7 +18186,7 @@
         <v>46050</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18259,7 +18259,7 @@
         <v>46092</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>46061</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18410,7 +18410,7 @@
         <v>45629</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>46047</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>46042</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>46042</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>46083</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18775,7 +18775,7 @@
         <v>45792</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18848,7 +18848,7 @@
         <v>46092</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18926,7 +18926,7 @@
         <v>46162</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19004,7 +19004,7 @@
         <v>46162</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19082,7 +19082,7 @@
         <v>46167</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19160,7 +19160,7 @@
         <v>46169</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19238,7 +19238,7 @@
         <v>46183</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19316,7 +19316,7 @@
         <v>46183</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19394,7 +19394,7 @@
         <v>46196</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>46196</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19550,7 +19550,7 @@
         <v>46199</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>46211</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>46216</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>46219</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>46268</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19925,7 +19925,7 @@
         <v>46272</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>46272</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>46274</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20144,7 +20144,7 @@
         <v>46274</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>46289</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>46021</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>46216</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>46064</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20514,7 +20514,7 @@
         <v>46300</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>46133</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20665,7 +20665,7 @@
         <v>46300</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>45967</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20811,7 +20811,7 @@
         <v>45967</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20884,7 +20884,7 @@
         <v>45967</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20957,7 +20957,7 @@
         <v>46259</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21035,7 +21035,7 @@
         <v>46259</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>46260</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
         <v>46169</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>45700</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21342,7 +21342,7 @@
         <v>45316</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21420,7 +21420,7 @@
         <v>45319</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21498,7 +21498,7 @@
         <v>45771</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21576,7 +21576,7 @@
         <v>45707</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21654,7 +21654,7 @@
         <v>45895</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21732,7 +21732,7 @@
         <v>46069</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>
@@ -21810,7 +21810,7 @@
         <v>46089</v>
       </c>
       <c r="E250" s="1" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F250" t="inlineStr">
         <is>

--- a/Översikt HOFORS.xlsx
+++ b/Översikt HOFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46064</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>45784</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>46164</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45299</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>46079</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>46163</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>46085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>46266</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45316</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45163</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>44623</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>45813</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>45860</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>46199</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44816</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45895</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>45895</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46154</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45935</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>46025</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>46177</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>46043</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>46095</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>46199</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>45813</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>45874</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44102</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44169</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>44585</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>45317</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45701</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>45895</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45895</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>46142</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>46125</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>44649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>44559</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>45477</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>44928</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45477</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>45453</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>45488</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>45597</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v>45531</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>44624</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>45917</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>45589</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>46183</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45007</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>45924</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>46091</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>45127</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>46196</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>46217</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>46217</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>45531</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>46252</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>46262</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>45813</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>45813</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>45813</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>45813</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45348</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>45860</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>45870</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>45874</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>45881</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>45701</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>45727</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45706</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44868</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44582</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>44501</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>44512</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>44873</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44868</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>44692</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>45755</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>45531</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>44967</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>45523</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>45523</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>45684</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>45477</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45127</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45219</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>45232</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>44810</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>44487</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>45387</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>45728</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>44810</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>45475</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>45250</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>45173</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>45453</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>45188</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         <v>45007</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>44977</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>45587</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>45488</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10867,7 +10867,7 @@
         <v>45488</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>45887</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>45884</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>45156</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>45912</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>45531</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>45490</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>46080</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>45674</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45895</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>45463</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>45453</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>45376</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>45252</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>46105</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>46092</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>45629</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>46085</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>46113</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>45343</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>45069</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>45917</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>45538</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45929</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>45439</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>45439</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>44671</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>45930</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>45933</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>45816</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>45933</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>45933</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>45933</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>45935</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>45630</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45947</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>46042</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>45677</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>45125</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>45792</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>46042</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>45271</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>45956</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>45709</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>45587</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>45966</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>45969</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>45969</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>46162</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>44986</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>45980</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>45980</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>45980</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>46162</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>45980</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>46167</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
         <v>45986</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15163,7 +15163,7 @@
         <v>45986</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>45127</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>46169</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>46000</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>46002</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>45446</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
         <v>45159</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>46029</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>46029</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>46030</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>46037</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>46036</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>46042</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>44680</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>46050</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>46183</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>46061</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>46183</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>46047</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>46083</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>45202</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
         <v>46092</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>46196</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>46196</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45145</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>44812</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>46107</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>46115</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>45117</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45117</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>46199</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>46085</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>46091</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>45587</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>45506</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>45280</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44489</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>45085</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>46211</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>46216</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>46219</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>46272</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45387</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>46272</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>46274</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>45476</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>46274</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>44810</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>44624</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>44994</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>45531</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>44526</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>45343</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>46289</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>45755</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>46021</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>46216</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>45117</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>45967</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>46064</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>45967</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>45967</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>46300</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>46300</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>46133</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>45302</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>45782</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20144,7 +20144,7 @@
         <v>45334</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>46259</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20295,7 +20295,7 @@
         <v>46260</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>46259</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>45792</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>46169</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>45523</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>45614</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>45805</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>46268</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>45833</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>45835</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>45868</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>45877</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
         <v>45700</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>45316</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>45319</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>45771</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45707</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>45895</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>46069</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>46089</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46312</v>
+        <v>46313</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>

--- a/Översikt HOFORS.xlsx
+++ b/Översikt HOFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46064</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>45784</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>46164</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45299</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>46079</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>46163</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>46085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>46266</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45316</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45163</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>44623</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>45813</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>45860</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>46199</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44816</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45895</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>45895</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46154</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45935</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>46025</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>46177</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>46043</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>46095</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>46199</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>45813</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>45874</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44102</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44169</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>44585</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>45317</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45701</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>45895</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45895</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>46142</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>46125</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>44649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>44559</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>45477</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5024,7 +5024,7 @@
         <v>44928</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5138,7 +5138,7 @@
         <v>45477</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5248,7 +5248,7 @@
         <v>45453</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5358,7 +5358,7 @@
         <v>45488</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5468,7 +5468,7 @@
         <v>45597</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5573,7 +5573,7 @@
         <v>45531</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5687,7 +5687,7 @@
         <v>44624</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5792,7 +5792,7 @@
         <v>45917</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>45589</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6007,7 +6007,7 @@
         <v>46183</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6117,7 +6117,7 @@
         <v>45007</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6227,7 +6227,7 @@
         <v>45924</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6337,7 +6337,7 @@
         <v>46091</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6446,7 +6446,7 @@
         <v>45127</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6556,7 +6556,7 @@
         <v>46196</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6666,7 +6666,7 @@
         <v>46217</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6776,7 +6776,7 @@
         <v>46217</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6886,7 +6886,7 @@
         <v>45531</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6996,7 +6996,7 @@
         <v>46252</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>46262</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7220,7 +7220,7 @@
         <v>45813</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7330,7 +7330,7 @@
         <v>45813</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7440,7 +7440,7 @@
         <v>45813</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7550,7 +7550,7 @@
         <v>45813</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7660,7 +7660,7 @@
         <v>45348</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>45860</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>45870</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>45874</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>45881</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>45701</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>45727</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45706</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44868</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44582</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>44501</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>44512</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>44873</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44868</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>44692</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>45755</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>45531</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>44967</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>45523</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>45523</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>45684</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9508,7 +9508,7 @@
         <v>45477</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45127</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>45219</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>45232</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9810,7 +9810,7 @@
         <v>44810</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9883,7 +9883,7 @@
         <v>44487</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>45387</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10029,7 +10029,7 @@
         <v>45728</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10107,7 +10107,7 @@
         <v>44810</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10180,7 +10180,7 @@
         <v>45475</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10258,7 +10258,7 @@
         <v>45250</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10331,7 +10331,7 @@
         <v>45173</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10409,7 +10409,7 @@
         <v>45453</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10487,7 +10487,7 @@
         <v>45188</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10560,7 +10560,7 @@
         <v>45007</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>44977</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10711,7 +10711,7 @@
         <v>45587</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10789,7 +10789,7 @@
         <v>45488</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10867,7 +10867,7 @@
         <v>45488</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10945,7 +10945,7 @@
         <v>45887</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11023,7 +11023,7 @@
         <v>45884</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11096,7 +11096,7 @@
         <v>45156</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11169,7 +11169,7 @@
         <v>45912</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11247,7 +11247,7 @@
         <v>45531</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11325,7 +11325,7 @@
         <v>45490</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11403,7 +11403,7 @@
         <v>46080</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11481,7 +11481,7 @@
         <v>45674</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11554,7 +11554,7 @@
         <v>45895</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>45463</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11710,7 +11710,7 @@
         <v>45453</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         <v>45376</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11861,7 +11861,7 @@
         <v>45252</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11934,7 +11934,7 @@
         <v>46105</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12012,7 +12012,7 @@
         <v>46092</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>45629</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12163,7 +12163,7 @@
         <v>46085</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12236,7 +12236,7 @@
         <v>46113</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12309,7 +12309,7 @@
         <v>45343</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>45069</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>45917</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12538,7 +12538,7 @@
         <v>45538</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12611,7 +12611,7 @@
         <v>45929</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12684,7 +12684,7 @@
         <v>45439</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12762,7 +12762,7 @@
         <v>45439</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>44671</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12913,7 +12913,7 @@
         <v>45930</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12986,7 +12986,7 @@
         <v>45933</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13064,7 +13064,7 @@
         <v>45816</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>45933</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13220,7 +13220,7 @@
         <v>45933</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>45933</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13376,7 +13376,7 @@
         <v>45935</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>45630</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>45947</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13605,7 +13605,7 @@
         <v>46042</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13678,7 +13678,7 @@
         <v>45677</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13751,7 +13751,7 @@
         <v>45125</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13824,7 +13824,7 @@
         <v>45792</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13897,7 +13897,7 @@
         <v>46042</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13970,7 +13970,7 @@
         <v>45271</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>45956</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14116,7 +14116,7 @@
         <v>45709</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14189,7 +14189,7 @@
         <v>45587</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14267,7 +14267,7 @@
         <v>45966</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>45969</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14413,7 +14413,7 @@
         <v>45969</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14486,7 +14486,7 @@
         <v>46162</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14564,7 +14564,7 @@
         <v>44986</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14642,7 +14642,7 @@
         <v>45980</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14715,7 +14715,7 @@
         <v>45980</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14788,7 +14788,7 @@
         <v>45980</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14861,7 +14861,7 @@
         <v>46162</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14939,7 +14939,7 @@
         <v>45980</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -15012,7 +15012,7 @@
         <v>46167</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
         <v>45986</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15163,7 +15163,7 @@
         <v>45986</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15236,7 +15236,7 @@
         <v>45127</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15314,7 +15314,7 @@
         <v>46169</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15392,7 +15392,7 @@
         <v>46000</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15465,7 +15465,7 @@
         <v>46002</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15538,7 +15538,7 @@
         <v>45446</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15611,7 +15611,7 @@
         <v>45159</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>46029</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15757,7 +15757,7 @@
         <v>46029</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15830,7 +15830,7 @@
         <v>46030</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15903,7 +15903,7 @@
         <v>46037</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15976,7 +15976,7 @@
         <v>46036</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16049,7 +16049,7 @@
         <v>46042</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16122,7 +16122,7 @@
         <v>44680</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16195,7 +16195,7 @@
         <v>46050</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>46183</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>46061</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16419,7 +16419,7 @@
         <v>46183</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16497,7 +16497,7 @@
         <v>46047</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16570,7 +16570,7 @@
         <v>46083</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16643,7 +16643,7 @@
         <v>45202</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
         <v>46092</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16794,7 +16794,7 @@
         <v>46196</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16872,7 +16872,7 @@
         <v>46196</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16950,7 +16950,7 @@
         <v>45145</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17023,7 +17023,7 @@
         <v>44812</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>46107</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17174,7 +17174,7 @@
         <v>46115</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17247,7 +17247,7 @@
         <v>45117</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17320,7 +17320,7 @@
         <v>45117</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>46199</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>46085</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17544,7 +17544,7 @@
         <v>46091</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>45587</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>45506</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17773,7 +17773,7 @@
         <v>45280</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17846,7 +17846,7 @@
         <v>44489</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>45085</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17997,7 +17997,7 @@
         <v>46211</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>46216</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18148,7 +18148,7 @@
         <v>46219</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18221,7 +18221,7 @@
         <v>46272</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45387</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18367,7 +18367,7 @@
         <v>46272</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>46274</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>45476</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>46274</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>44810</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>44624</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>44994</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18883,7 +18883,7 @@
         <v>45531</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>44526</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>45343</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>46289</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>45755</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>46021</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>46216</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19409,7 +19409,7 @@
         <v>45117</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19482,7 +19482,7 @@
         <v>45967</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>46064</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>45967</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>45967</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>46300</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19847,7 +19847,7 @@
         <v>46300</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19920,7 +19920,7 @@
         <v>46133</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>45302</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20071,7 +20071,7 @@
         <v>45782</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20144,7 +20144,7 @@
         <v>45334</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20217,7 +20217,7 @@
         <v>46259</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20295,7 +20295,7 @@
         <v>46260</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20373,7 +20373,7 @@
         <v>46259</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>45792</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>46169</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20597,7 +20597,7 @@
         <v>45523</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20670,7 +20670,7 @@
         <v>45614</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20743,7 +20743,7 @@
         <v>45805</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>46268</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20889,7 +20889,7 @@
         <v>45833</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20962,7 +20962,7 @@
         <v>45835</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21040,7 +21040,7 @@
         <v>45868</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>45877</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21191,7 +21191,7 @@
         <v>45700</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21269,7 +21269,7 @@
         <v>45316</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21347,7 +21347,7 @@
         <v>45319</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21425,7 +21425,7 @@
         <v>45771</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21503,7 +21503,7 @@
         <v>45707</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21581,7 +21581,7 @@
         <v>45895</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21659,7 +21659,7 @@
         <v>46069</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21737,7 +21737,7 @@
         <v>46089</v>
       </c>
       <c r="E249" s="1" t="n">
-        <v>46313</v>
+        <v>46314</v>
       </c>
       <c r="F249" t="inlineStr">
         <is>

--- a/Översikt HOFORS.xlsx
+++ b/Översikt HOFORS.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE249"/>
+  <dimension ref="A1:AE248"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="0" ht="15" customHeight="1"/>
@@ -601,7 +601,7 @@
         <v>46064</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>45784</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>46164</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45299</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>46079</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>46163</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>46085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>46266</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45316</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45163</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>44623</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1918,7 +1918,7 @@
         <v>45813</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>45860</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>46199</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44816</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45895</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>45895</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>46154</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2705,7 +2705,7 @@
         <v>45935</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>46025</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2926,7 +2926,7 @@
         <v>46177</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3037,7 +3037,7 @@
         <v>46043</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3148,7 +3148,7 @@
         <v>46095</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3254,7 +3254,7 @@
         <v>46199</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3369,7 +3369,7 @@
         <v>45813</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3480,7 +3480,7 @@
         <v>45874</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44102</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44169</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>44585</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>45317</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45701</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>45895</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45895</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>46142</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>46125</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>44649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>44559</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4897,7 +4897,7 @@
     <row r="40" ht="15" customHeight="1">
       <c r="A40" t="inlineStr">
         <is>
-          <t>A 28392-2024</t>
+          <t>A 35514-2024</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4911,10 +4911,10 @@
         </is>
       </c>
       <c r="D40" s="1" t="n">
-        <v>45477</v>
+        <v>45531</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="I40" t="n">
-        <v>0.5</v>
+        <v>6.5</v>
       </c>
       <c r="J40" t="n">
         <v>1</v>
@@ -4941,7 +4941,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M40" t="n">
         <v>0</v>
@@ -4956,7 +4956,7 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R40" t="n">
         <v>0</v>
@@ -4965,49 +4965,53 @@
         <v>1</v>
       </c>
       <c r="T40" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U40" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="W40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 28392-2024 artfynd.xlsx", "A 28392-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 35514-2024 artfynd.xlsx", "A 35514-2024")</f>
         <v/>
       </c>
       <c r="X40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 28392-2024 karta.png", "A 28392-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 35514-2024 karta.png", "A 35514-2024")</f>
         <v/>
       </c>
       <c r="Y40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 28392-2024 georefererad karta.tif", "A 28392-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 35514-2024 georefererad karta.tif", "A 35514-2024")</f>
         <v/>
       </c>
       <c r="AA40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 28392-2024 FSC-klagomål.docx", "A 28392-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 35514-2024 FSC-klagomål.docx", "A 35514-2024")</f>
         <v/>
       </c>
       <c r="AB40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 28392-2024 FSC-klagomål mail.docx", "A 28392-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 35514-2024 FSC-klagomål mail.docx", "A 35514-2024")</f>
         <v/>
       </c>
       <c r="AC40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 28392-2024 tillsynsbegäran.docx", "A 28392-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 35514-2024 tillsynsbegäran.docx", "A 35514-2024")</f>
         <v/>
       </c>
       <c r="AD40">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 28392-2024 tillsynsbegäran mail.docx", "A 28392-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 35514-2024 tillsynsbegäran mail.docx", "A 35514-2024")</f>
+        <v/>
+      </c>
+      <c r="AE40">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/fåglar/A 35514-2024 prioriterade fågelarter.docx", "A 35514-2024")</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" t="inlineStr">
         <is>
-          <t>A 234-2023</t>
+          <t>A 33298-2023</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -5021,10 +5025,10 @@
         </is>
       </c>
       <c r="D41" s="1" t="n">
-        <v>44928</v>
+        <v>45127</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5042,19 +5046,19 @@
         </is>
       </c>
       <c r="I41" t="n">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="J41" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" t="n">
         <v>1</v>
       </c>
-      <c r="K41" t="n">
-        <v>0</v>
-      </c>
       <c r="L41" t="n">
         <v>0</v>
       </c>
       <c r="M41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N41" t="n">
         <v>0</v>
@@ -5066,10 +5070,10 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5082,46 +5086,42 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="W41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 234-2023 artfynd.xlsx", "A 234-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 33298-2023 artfynd.xlsx", "A 33298-2023")</f>
         <v/>
       </c>
       <c r="X41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 234-2023 karta.png", "A 234-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 33298-2023 karta.png", "A 33298-2023")</f>
         <v/>
       </c>
       <c r="Y41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 234-2023 georefererad karta.tif", "A 234-2023")</f>
-        <v/>
-      </c>
-      <c r="Z41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/knärot/A 234-2023 karta knärot.png", "A 234-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 33298-2023 georefererad karta.tif", "A 33298-2023")</f>
         <v/>
       </c>
       <c r="AA41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 234-2023 FSC-klagomål.docx", "A 234-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 33298-2023 FSC-klagomål.docx", "A 33298-2023")</f>
         <v/>
       </c>
       <c r="AB41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 234-2023 FSC-klagomål mail.docx", "A 234-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 33298-2023 FSC-klagomål mail.docx", "A 33298-2023")</f>
         <v/>
       </c>
       <c r="AC41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 234-2023 tillsynsbegäran.docx", "A 234-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 33298-2023 tillsynsbegäran.docx", "A 33298-2023")</f>
         <v/>
       </c>
       <c r="AD41">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 234-2023 tillsynsbegäran mail.docx", "A 234-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 33298-2023 tillsynsbegäran mail.docx", "A 33298-2023")</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" t="inlineStr">
         <is>
-          <t>A 28397-2024</t>
+          <t>A 30008-2024</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -5135,10 +5135,10 @@
         </is>
       </c>
       <c r="D42" s="1" t="n">
-        <v>45477</v>
+        <v>45488</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5156,13 +5156,13 @@
         </is>
       </c>
       <c r="I42" t="n">
-        <v>5</v>
+        <v>0.8</v>
       </c>
       <c r="J42" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" t="n">
         <v>1</v>
-      </c>
-      <c r="K42" t="n">
-        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -5196,42 +5196,42 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 28397-2024 artfynd.xlsx", "A 28397-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 30008-2024 artfynd.xlsx", "A 30008-2024")</f>
         <v/>
       </c>
       <c r="X42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 28397-2024 karta.png", "A 28397-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 30008-2024 karta.png", "A 30008-2024")</f>
         <v/>
       </c>
       <c r="Y42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 28397-2024 georefererad karta.tif", "A 28397-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 30008-2024 georefererad karta.tif", "A 30008-2024")</f>
         <v/>
       </c>
       <c r="AA42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 28397-2024 FSC-klagomål.docx", "A 28397-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 30008-2024 FSC-klagomål.docx", "A 30008-2024")</f>
         <v/>
       </c>
       <c r="AB42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 28397-2024 FSC-klagomål mail.docx", "A 28397-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 30008-2024 FSC-klagomål mail.docx", "A 30008-2024")</f>
         <v/>
       </c>
       <c r="AC42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 28397-2024 tillsynsbegäran.docx", "A 28397-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 30008-2024 tillsynsbegäran.docx", "A 30008-2024")</f>
         <v/>
       </c>
       <c r="AD42">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 28397-2024 tillsynsbegäran mail.docx", "A 28397-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 30008-2024 tillsynsbegäran mail.docx", "A 30008-2024")</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" t="inlineStr">
         <is>
-          <t>A 23354-2024</t>
+          <t>A 13745-2023</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -5245,10 +5245,10 @@
         </is>
       </c>
       <c r="D43" s="1" t="n">
-        <v>45453</v>
+        <v>45007</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5262,21 +5262,21 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I43" t="n">
-        <v>2</v>
+        <v>0.5</v>
       </c>
       <c r="J43" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" t="n">
         <v>1</v>
       </c>
-      <c r="K43" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" t="n">
-        <v>0</v>
-      </c>
       <c r="M43" t="n">
         <v>0</v>
       </c>
@@ -5290,7 +5290,7 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R43" t="n">
         <v>0</v>
@@ -5306,42 +5306,42 @@
       </c>
       <c r="V43" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Stiftgelélav</t>
         </is>
       </c>
       <c r="W43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 23354-2024 artfynd.xlsx", "A 23354-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 13745-2023 artfynd.xlsx", "A 13745-2023")</f>
         <v/>
       </c>
       <c r="X43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 23354-2024 karta.png", "A 23354-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 13745-2023 karta.png", "A 13745-2023")</f>
         <v/>
       </c>
       <c r="Y43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 23354-2024 georefererad karta.tif", "A 23354-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 13745-2023 georefererad karta.tif", "A 13745-2023")</f>
         <v/>
       </c>
       <c r="AA43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 23354-2024 FSC-klagomål.docx", "A 23354-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 13745-2023 FSC-klagomål.docx", "A 13745-2023")</f>
         <v/>
       </c>
       <c r="AB43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 23354-2024 FSC-klagomål mail.docx", "A 23354-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 13745-2023 FSC-klagomål mail.docx", "A 13745-2023")</f>
         <v/>
       </c>
       <c r="AC43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 23354-2024 tillsynsbegäran.docx", "A 23354-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 13745-2023 tillsynsbegäran.docx", "A 13745-2023")</f>
         <v/>
       </c>
       <c r="AD43">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 23354-2024 tillsynsbegäran mail.docx", "A 23354-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 13745-2023 tillsynsbegäran mail.docx", "A 13745-2023")</f>
         <v/>
       </c>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" t="inlineStr">
         <is>
-          <t>A 30008-2024</t>
+          <t>A 48063-2024</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -5355,10 +5355,10 @@
         </is>
       </c>
       <c r="D44" s="1" t="n">
-        <v>45488</v>
+        <v>45589</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5370,16 +5370,11 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I44" t="n">
-        <v>0.8</v>
+        <v>3.9</v>
       </c>
       <c r="J44" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K44" t="n">
         <v>1</v>
@@ -5412,46 +5407,46 @@
         <v>1</v>
       </c>
       <c r="U44" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V44" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="W44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 30008-2024 artfynd.xlsx", "A 30008-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 48063-2024 artfynd.xlsx", "A 48063-2024")</f>
         <v/>
       </c>
       <c r="X44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 30008-2024 karta.png", "A 30008-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 48063-2024 karta.png", "A 48063-2024")</f>
         <v/>
       </c>
       <c r="Y44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 30008-2024 georefererad karta.tif", "A 30008-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 48063-2024 georefererad karta.tif", "A 48063-2024")</f>
         <v/>
       </c>
       <c r="AA44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 30008-2024 FSC-klagomål.docx", "A 30008-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 48063-2024 FSC-klagomål.docx", "A 48063-2024")</f>
         <v/>
       </c>
       <c r="AB44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 30008-2024 FSC-klagomål mail.docx", "A 30008-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 48063-2024 FSC-klagomål mail.docx", "A 48063-2024")</f>
         <v/>
       </c>
       <c r="AC44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 30008-2024 tillsynsbegäran.docx", "A 30008-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 48063-2024 tillsynsbegäran.docx", "A 48063-2024")</f>
         <v/>
       </c>
       <c r="AD44">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 30008-2024 tillsynsbegäran mail.docx", "A 30008-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 48063-2024 tillsynsbegäran mail.docx", "A 48063-2024")</f>
         <v/>
       </c>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" t="inlineStr">
         <is>
-          <t>A 49815-2024</t>
+          <t>A 23354-2024</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -5465,10 +5460,10 @@
         </is>
       </c>
       <c r="D45" s="1" t="n">
-        <v>45597</v>
+        <v>45453</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5480,17 +5475,22 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I45" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
@@ -5505,7 +5505,7 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
         <v>0</v>
@@ -5517,46 +5517,46 @@
         <v>1</v>
       </c>
       <c r="U45" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V45" s="2" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 49815-2024 artfynd.xlsx", "A 49815-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 23354-2024 artfynd.xlsx", "A 23354-2024")</f>
         <v/>
       </c>
       <c r="X45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 49815-2024 karta.png", "A 49815-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 23354-2024 karta.png", "A 23354-2024")</f>
         <v/>
       </c>
       <c r="Y45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 49815-2024 georefererad karta.tif", "A 49815-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 23354-2024 georefererad karta.tif", "A 23354-2024")</f>
         <v/>
       </c>
       <c r="AA45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 49815-2024 FSC-klagomål.docx", "A 49815-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 23354-2024 FSC-klagomål.docx", "A 23354-2024")</f>
         <v/>
       </c>
       <c r="AB45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 49815-2024 FSC-klagomål mail.docx", "A 49815-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 23354-2024 FSC-klagomål mail.docx", "A 23354-2024")</f>
         <v/>
       </c>
       <c r="AC45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 49815-2024 tillsynsbegäran.docx", "A 49815-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 23354-2024 tillsynsbegäran.docx", "A 23354-2024")</f>
         <v/>
       </c>
       <c r="AD45">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 49815-2024 tillsynsbegäran mail.docx", "A 49815-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 23354-2024 tillsynsbegäran mail.docx", "A 23354-2024")</f>
         <v/>
       </c>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" t="inlineStr">
         <is>
-          <t>A 35514-2024</t>
+          <t>A 28397-2024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -5570,10 +5570,10 @@
         </is>
       </c>
       <c r="D46" s="1" t="n">
-        <v>45531</v>
+        <v>45477</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5591,7 +5591,7 @@
         </is>
       </c>
       <c r="I46" t="n">
-        <v>6.5</v>
+        <v>5</v>
       </c>
       <c r="J46" t="n">
         <v>1</v>
@@ -5600,7 +5600,7 @@
         <v>0</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M46" t="n">
         <v>0</v>
@@ -5615,7 +5615,7 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
         <v>0</v>
@@ -5627,50 +5627,46 @@
         <v>1</v>
       </c>
       <c r="U46" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V46" s="2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 35514-2024 artfynd.xlsx", "A 35514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 28397-2024 artfynd.xlsx", "A 28397-2024")</f>
         <v/>
       </c>
       <c r="X46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 35514-2024 karta.png", "A 35514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 28397-2024 karta.png", "A 28397-2024")</f>
         <v/>
       </c>
       <c r="Y46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 35514-2024 georefererad karta.tif", "A 35514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 28397-2024 georefererad karta.tif", "A 28397-2024")</f>
         <v/>
       </c>
       <c r="AA46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 35514-2024 FSC-klagomål.docx", "A 35514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 28397-2024 FSC-klagomål.docx", "A 28397-2024")</f>
         <v/>
       </c>
       <c r="AB46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 35514-2024 FSC-klagomål mail.docx", "A 35514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 28397-2024 FSC-klagomål mail.docx", "A 28397-2024")</f>
         <v/>
       </c>
       <c r="AC46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 35514-2024 tillsynsbegäran.docx", "A 35514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 28397-2024 tillsynsbegäran.docx", "A 28397-2024")</f>
         <v/>
       </c>
       <c r="AD46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 35514-2024 tillsynsbegäran mail.docx", "A 35514-2024")</f>
-        <v/>
-      </c>
-      <c r="AE46">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/fåglar/A 35514-2024 prioriterade fågelarter.docx", "A 35514-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 28397-2024 tillsynsbegäran mail.docx", "A 28397-2024")</f>
         <v/>
       </c>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" t="inlineStr">
         <is>
-          <t>A 10587-2022</t>
+          <t>A 44694-2025</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -5684,10 +5680,10 @@
         </is>
       </c>
       <c r="D47" s="1" t="n">
-        <v>44624</v>
+        <v>45917</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5699,18 +5695,23 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I47" t="n">
-        <v>5</v>
+        <v>12.1</v>
       </c>
       <c r="J47" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" t="n">
         <v>1</v>
       </c>
-      <c r="K47" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" t="n">
-        <v>0</v>
-      </c>
       <c r="M47" t="n">
         <v>0</v>
       </c>
@@ -5724,7 +5725,7 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R47" t="n">
         <v>0</v>
@@ -5733,49 +5734,49 @@
         <v>1</v>
       </c>
       <c r="T47" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="U47" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V47" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="W47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 10587-2022 artfynd.xlsx", "A 10587-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 44694-2025 artfynd.xlsx", "A 44694-2025")</f>
         <v/>
       </c>
       <c r="X47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 10587-2022 karta.png", "A 10587-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 44694-2025 karta.png", "A 44694-2025")</f>
         <v/>
       </c>
       <c r="Y47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 10587-2022 georefererad karta.tif", "A 10587-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 44694-2025 georefererad karta.tif", "A 44694-2025")</f>
         <v/>
       </c>
       <c r="AA47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 10587-2022 FSC-klagomål.docx", "A 10587-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 44694-2025 FSC-klagomål.docx", "A 44694-2025")</f>
         <v/>
       </c>
       <c r="AB47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 10587-2022 FSC-klagomål mail.docx", "A 10587-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 44694-2025 FSC-klagomål mail.docx", "A 44694-2025")</f>
         <v/>
       </c>
       <c r="AC47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 10587-2022 tillsynsbegäran.docx", "A 10587-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 44694-2025 tillsynsbegäran.docx", "A 44694-2025")</f>
         <v/>
       </c>
       <c r="AD47">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 10587-2022 tillsynsbegäran mail.docx", "A 10587-2022")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 44694-2025 tillsynsbegäran mail.docx", "A 44694-2025")</f>
         <v/>
       </c>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" t="inlineStr">
         <is>
-          <t>A 44694-2025</t>
+          <t>A 35521-2024</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -5789,10 +5790,10 @@
         </is>
       </c>
       <c r="D48" s="1" t="n">
-        <v>45917</v>
+        <v>45531</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5810,16 +5811,16 @@
         </is>
       </c>
       <c r="I48" t="n">
-        <v>12.1</v>
+        <v>1.3</v>
       </c>
       <c r="J48" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
         <v>0</v>
       </c>
       <c r="L48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" t="n">
         <v>0</v>
@@ -5834,7 +5835,7 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
         <v>0</v>
@@ -5850,42 +5851,42 @@
       </c>
       <c r="V48" s="2" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 44694-2025 artfynd.xlsx", "A 44694-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 35521-2024 artfynd.xlsx", "A 35521-2024")</f>
         <v/>
       </c>
       <c r="X48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 44694-2025 karta.png", "A 44694-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 35521-2024 karta.png", "A 35521-2024")</f>
         <v/>
       </c>
       <c r="Y48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 44694-2025 georefererad karta.tif", "A 44694-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 35521-2024 georefererad karta.tif", "A 35521-2024")</f>
         <v/>
       </c>
       <c r="AA48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 44694-2025 FSC-klagomål.docx", "A 44694-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 35521-2024 FSC-klagomål.docx", "A 35521-2024")</f>
         <v/>
       </c>
       <c r="AB48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 44694-2025 FSC-klagomål mail.docx", "A 44694-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 35521-2024 FSC-klagomål mail.docx", "A 35521-2024")</f>
         <v/>
       </c>
       <c r="AC48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 44694-2025 tillsynsbegäran.docx", "A 44694-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 35521-2024 tillsynsbegäran.docx", "A 35521-2024")</f>
         <v/>
       </c>
       <c r="AD48">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 44694-2025 tillsynsbegäran mail.docx", "A 44694-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 35521-2024 tillsynsbegäran mail.docx", "A 35521-2024")</f>
         <v/>
       </c>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" t="inlineStr">
         <is>
-          <t>A 48063-2024</t>
+          <t>A 49815-2024</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -5899,10 +5900,10 @@
         </is>
       </c>
       <c r="D49" s="1" t="n">
-        <v>45589</v>
+        <v>45597</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -5915,31 +5916,31 @@
         </is>
       </c>
       <c r="I49" t="n">
-        <v>3.9</v>
+        <v>0.9</v>
       </c>
       <c r="J49" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" t="n">
         <v>1</v>
       </c>
-      <c r="K49" t="n">
+      <c r="M49" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" t="n">
+        <v>0</v>
+      </c>
+      <c r="P49" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="n">
         <v>1</v>
-      </c>
-      <c r="L49" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" t="n">
-        <v>0</v>
-      </c>
-      <c r="P49" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q49" t="n">
-        <v>0</v>
       </c>
       <c r="R49" t="n">
         <v>0</v>
@@ -5955,42 +5956,42 @@
       </c>
       <c r="V49" s="2" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Brunklöver</t>
         </is>
       </c>
       <c r="W49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 48063-2024 artfynd.xlsx", "A 48063-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 49815-2024 artfynd.xlsx", "A 49815-2024")</f>
         <v/>
       </c>
       <c r="X49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 48063-2024 karta.png", "A 48063-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 49815-2024 karta.png", "A 49815-2024")</f>
         <v/>
       </c>
       <c r="Y49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 48063-2024 georefererad karta.tif", "A 48063-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 49815-2024 georefererad karta.tif", "A 49815-2024")</f>
         <v/>
       </c>
       <c r="AA49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 48063-2024 FSC-klagomål.docx", "A 48063-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 49815-2024 FSC-klagomål.docx", "A 49815-2024")</f>
         <v/>
       </c>
       <c r="AB49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 48063-2024 FSC-klagomål mail.docx", "A 48063-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 49815-2024 FSC-klagomål mail.docx", "A 49815-2024")</f>
         <v/>
       </c>
       <c r="AC49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 48063-2024 tillsynsbegäran.docx", "A 48063-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 49815-2024 tillsynsbegäran.docx", "A 49815-2024")</f>
         <v/>
       </c>
       <c r="AD49">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 48063-2024 tillsynsbegäran mail.docx", "A 48063-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 49815-2024 tillsynsbegäran mail.docx", "A 49815-2024")</f>
         <v/>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" t="inlineStr">
         <is>
-          <t>A 26513-2026</t>
+          <t>A 10587-2022</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -6004,10 +6005,10 @@
         </is>
       </c>
       <c r="D50" s="1" t="n">
-        <v>46183</v>
+        <v>44624</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6019,19 +6020,14 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I50" t="n">
-        <v>6.9</v>
+        <v>5</v>
       </c>
       <c r="J50" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K50" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L50" t="n">
         <v>0</v>
@@ -6058,49 +6054,49 @@
         <v>1</v>
       </c>
       <c r="T50" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V50" s="2" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 26513-2026 artfynd.xlsx", "A 26513-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 10587-2022 artfynd.xlsx", "A 10587-2022")</f>
         <v/>
       </c>
       <c r="X50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 26513-2026 karta.png", "A 26513-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 10587-2022 karta.png", "A 10587-2022")</f>
         <v/>
       </c>
       <c r="Y50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 26513-2026 georefererad karta.tif", "A 26513-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 10587-2022 georefererad karta.tif", "A 10587-2022")</f>
         <v/>
       </c>
       <c r="AA50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 26513-2026 FSC-klagomål.docx", "A 26513-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 10587-2022 FSC-klagomål.docx", "A 10587-2022")</f>
         <v/>
       </c>
       <c r="AB50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 26513-2026 FSC-klagomål mail.docx", "A 26513-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 10587-2022 FSC-klagomål mail.docx", "A 10587-2022")</f>
         <v/>
       </c>
       <c r="AC50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 26513-2026 tillsynsbegäran.docx", "A 26513-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 10587-2022 tillsynsbegäran.docx", "A 10587-2022")</f>
         <v/>
       </c>
       <c r="AD50">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 26513-2026 tillsynsbegäran mail.docx", "A 26513-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 10587-2022 tillsynsbegäran mail.docx", "A 10587-2022")</f>
         <v/>
       </c>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" t="inlineStr">
         <is>
-          <t>A 13745-2023</t>
+          <t>A 26513-2026</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -6114,10 +6110,10 @@
         </is>
       </c>
       <c r="D51" s="1" t="n">
-        <v>45007</v>
+        <v>46183</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6131,20 +6127,20 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.5</v>
+        <v>6.9</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M51" t="n">
         <v>0</v>
@@ -6159,7 +6155,7 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
@@ -6171,39 +6167,39 @@
         <v>1</v>
       </c>
       <c r="U51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V51" s="2" t="inlineStr">
         <is>
-          <t>Stiftgelélav</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="W51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 13745-2023 artfynd.xlsx", "A 13745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 26513-2026 artfynd.xlsx", "A 26513-2026")</f>
         <v/>
       </c>
       <c r="X51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 13745-2023 karta.png", "A 13745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 26513-2026 karta.png", "A 26513-2026")</f>
         <v/>
       </c>
       <c r="Y51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 13745-2023 georefererad karta.tif", "A 13745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 26513-2026 georefererad karta.tif", "A 26513-2026")</f>
         <v/>
       </c>
       <c r="AA51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 13745-2023 FSC-klagomål.docx", "A 13745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 26513-2026 FSC-klagomål.docx", "A 26513-2026")</f>
         <v/>
       </c>
       <c r="AB51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 13745-2023 FSC-klagomål mail.docx", "A 13745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 26513-2026 FSC-klagomål mail.docx", "A 26513-2026")</f>
         <v/>
       </c>
       <c r="AC51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 13745-2023 tillsynsbegäran.docx", "A 13745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 26513-2026 tillsynsbegäran.docx", "A 26513-2026")</f>
         <v/>
       </c>
       <c r="AD51">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 13745-2023 tillsynsbegäran mail.docx", "A 13745-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 26513-2026 tillsynsbegäran mail.docx", "A 26513-2026")</f>
         <v/>
       </c>
     </row>
@@ -6227,7 +6223,7 @@
         <v>45924</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6337,7 +6333,7 @@
         <v>46091</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6429,7 +6425,7 @@
     <row r="54" ht="15" customHeight="1">
       <c r="A54" t="inlineStr">
         <is>
-          <t>A 33298-2023</t>
+          <t>A 28392-2024</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -6443,10 +6439,10 @@
         </is>
       </c>
       <c r="D54" s="1" t="n">
-        <v>45127</v>
+        <v>45477</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6464,13 +6460,13 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>5.6</v>
+        <v>0.5</v>
       </c>
       <c r="J54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L54" t="n">
         <v>0</v>
@@ -6497,42 +6493,42 @@
         <v>1</v>
       </c>
       <c r="T54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="U54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="V54" s="2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 33298-2023 artfynd.xlsx", "A 33298-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 28392-2024 artfynd.xlsx", "A 28392-2024")</f>
         <v/>
       </c>
       <c r="X54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 33298-2023 karta.png", "A 33298-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 28392-2024 karta.png", "A 28392-2024")</f>
         <v/>
       </c>
       <c r="Y54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 33298-2023 georefererad karta.tif", "A 33298-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 28392-2024 georefererad karta.tif", "A 28392-2024")</f>
         <v/>
       </c>
       <c r="AA54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 33298-2023 FSC-klagomål.docx", "A 33298-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 28392-2024 FSC-klagomål.docx", "A 28392-2024")</f>
         <v/>
       </c>
       <c r="AB54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 33298-2023 FSC-klagomål mail.docx", "A 33298-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 28392-2024 FSC-klagomål mail.docx", "A 28392-2024")</f>
         <v/>
       </c>
       <c r="AC54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 33298-2023 tillsynsbegäran.docx", "A 33298-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 28392-2024 tillsynsbegäran.docx", "A 28392-2024")</f>
         <v/>
       </c>
       <c r="AD54">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 33298-2023 tillsynsbegäran mail.docx", "A 33298-2023")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 28392-2024 tillsynsbegäran mail.docx", "A 28392-2024")</f>
         <v/>
       </c>
     </row>
@@ -6556,7 +6552,7 @@
         <v>46196</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6649,7 +6645,7 @@
     <row r="56" ht="15" customHeight="1">
       <c r="A56" t="inlineStr">
         <is>
-          <t>A 31185-2026</t>
+          <t>A 234-2023</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -6663,10 +6659,10 @@
         </is>
       </c>
       <c r="D56" s="1" t="n">
-        <v>46217</v>
+        <v>44928</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6684,7 +6680,7 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>6.8</v>
+        <v>5.1</v>
       </c>
       <c r="J56" t="n">
         <v>1</v>
@@ -6696,7 +6692,7 @@
         <v>0</v>
       </c>
       <c r="M56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
@@ -6708,10 +6704,10 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S56" t="n">
         <v>1</v>
@@ -6720,39 +6716,43 @@
         <v>1</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V56" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="W56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 31185-2026 artfynd.xlsx", "A 31185-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 234-2023 artfynd.xlsx", "A 234-2023")</f>
         <v/>
       </c>
       <c r="X56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 31185-2026 karta.png", "A 31185-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 234-2023 karta.png", "A 234-2023")</f>
         <v/>
       </c>
       <c r="Y56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 31185-2026 georefererad karta.tif", "A 31185-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 234-2023 georefererad karta.tif", "A 234-2023")</f>
+        <v/>
+      </c>
+      <c r="Z56">
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/knärot/A 234-2023 karta knärot.png", "A 234-2023")</f>
         <v/>
       </c>
       <c r="AA56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 31185-2026 FSC-klagomål.docx", "A 31185-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 234-2023 FSC-klagomål.docx", "A 234-2023")</f>
         <v/>
       </c>
       <c r="AB56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 31185-2026 FSC-klagomål mail.docx", "A 31185-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 234-2023 FSC-klagomål mail.docx", "A 234-2023")</f>
         <v/>
       </c>
       <c r="AC56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 31185-2026 tillsynsbegäran.docx", "A 31185-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 234-2023 tillsynsbegäran.docx", "A 234-2023")</f>
         <v/>
       </c>
       <c r="AD56">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 31185-2026 tillsynsbegäran mail.docx", "A 31185-2026")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 234-2023 tillsynsbegäran mail.docx", "A 234-2023")</f>
         <v/>
       </c>
     </row>
@@ -6776,7 +6776,7 @@
         <v>46217</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6869,7 +6869,7 @@
     <row r="58" ht="15" customHeight="1">
       <c r="A58" t="inlineStr">
         <is>
-          <t>A 35521-2024</t>
+          <t>A 31185-2026</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -6883,10 +6883,10 @@
         </is>
       </c>
       <c r="D58" s="1" t="n">
-        <v>45531</v>
+        <v>46217</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -6904,7 +6904,7 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>1.3</v>
+        <v>6.8</v>
       </c>
       <c r="J58" t="n">
         <v>1</v>
@@ -6944,35 +6944,35 @@
       </c>
       <c r="V58" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 35521-2024 artfynd.xlsx", "A 35521-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 31185-2026 artfynd.xlsx", "A 31185-2026")</f>
         <v/>
       </c>
       <c r="X58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 35521-2024 karta.png", "A 35521-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 31185-2026 karta.png", "A 31185-2026")</f>
         <v/>
       </c>
       <c r="Y58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 35521-2024 georefererad karta.tif", "A 35521-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 31185-2026 georefererad karta.tif", "A 31185-2026")</f>
         <v/>
       </c>
       <c r="AA58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 35521-2024 FSC-klagomål.docx", "A 35521-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 31185-2026 FSC-klagomål.docx", "A 31185-2026")</f>
         <v/>
       </c>
       <c r="AB58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 35521-2024 FSC-klagomål mail.docx", "A 35521-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 31185-2026 FSC-klagomål mail.docx", "A 31185-2026")</f>
         <v/>
       </c>
       <c r="AC58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 35521-2024 tillsynsbegäran.docx", "A 35521-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 31185-2026 tillsynsbegäran.docx", "A 31185-2026")</f>
         <v/>
       </c>
       <c r="AD58">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 35521-2024 tillsynsbegäran mail.docx", "A 35521-2024")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 31185-2026 tillsynsbegäran mail.docx", "A 31185-2026")</f>
         <v/>
       </c>
     </row>
@@ -6996,7 +6996,7 @@
         <v>46252</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7110,7 +7110,7 @@
         <v>46262</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
     <row r="61" ht="15" customHeight="1">
       <c r="A61" t="inlineStr">
         <is>
-          <t>A 27431-2025</t>
+          <t>A 27438-2025</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -7220,7 +7220,7 @@
         <v>45813</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>3.4</v>
+        <v>0.9</v>
       </c>
       <c r="J61" t="n">
         <v>1</v>
@@ -7250,7 +7250,7 @@
         <v>0</v>
       </c>
       <c r="M61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
@@ -7262,58 +7262,58 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>1</v>
       </c>
       <c r="T61" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="U61" t="n">
         <v>0</v>
       </c>
       <c r="V61" s="2" t="inlineStr">
         <is>
-          <t>Väddnätfjäril</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 27431-2025 artfynd.xlsx", "A 27431-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 27438-2025 artfynd.xlsx", "A 27438-2025")</f>
         <v/>
       </c>
       <c r="X61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 27431-2025 karta.png", "A 27431-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 27438-2025 karta.png", "A 27438-2025")</f>
         <v/>
       </c>
       <c r="Y61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 27431-2025 georefererad karta.tif", "A 27431-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 27438-2025 georefererad karta.tif", "A 27438-2025")</f>
         <v/>
       </c>
       <c r="AA61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 27431-2025 FSC-klagomål.docx", "A 27431-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 27438-2025 FSC-klagomål.docx", "A 27438-2025")</f>
         <v/>
       </c>
       <c r="AB61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 27431-2025 FSC-klagomål mail.docx", "A 27431-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 27438-2025 FSC-klagomål mail.docx", "A 27438-2025")</f>
         <v/>
       </c>
       <c r="AC61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 27431-2025 tillsynsbegäran.docx", "A 27431-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 27438-2025 tillsynsbegäran.docx", "A 27438-2025")</f>
         <v/>
       </c>
       <c r="AD61">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 27431-2025 tillsynsbegäran mail.docx", "A 27431-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 27438-2025 tillsynsbegäran mail.docx", "A 27438-2025")</f>
         <v/>
       </c>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" t="inlineStr">
         <is>
-          <t>A 27438-2025</t>
+          <t>A 27432-2025</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -7330,7 +7330,7 @@
         <v>45813</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7348,7 +7348,7 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.9</v>
+        <v>3.6</v>
       </c>
       <c r="J62" t="n">
         <v>1</v>
@@ -7381,49 +7381,49 @@
         <v>1</v>
       </c>
       <c r="T62" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="U62" t="n">
         <v>0</v>
       </c>
       <c r="V62" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="W62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 27438-2025 artfynd.xlsx", "A 27438-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 27432-2025 artfynd.xlsx", "A 27432-2025")</f>
         <v/>
       </c>
       <c r="X62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 27438-2025 karta.png", "A 27438-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 27432-2025 karta.png", "A 27432-2025")</f>
         <v/>
       </c>
       <c r="Y62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 27438-2025 georefererad karta.tif", "A 27438-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 27432-2025 georefererad karta.tif", "A 27432-2025")</f>
         <v/>
       </c>
       <c r="AA62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 27438-2025 FSC-klagomål.docx", "A 27438-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 27432-2025 FSC-klagomål.docx", "A 27432-2025")</f>
         <v/>
       </c>
       <c r="AB62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 27438-2025 FSC-klagomål mail.docx", "A 27438-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 27432-2025 FSC-klagomål mail.docx", "A 27432-2025")</f>
         <v/>
       </c>
       <c r="AC62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 27438-2025 tillsynsbegäran.docx", "A 27438-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 27432-2025 tillsynsbegäran.docx", "A 27432-2025")</f>
         <v/>
       </c>
       <c r="AD62">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 27438-2025 tillsynsbegäran mail.docx", "A 27438-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 27432-2025 tillsynsbegäran mail.docx", "A 27432-2025")</f>
         <v/>
       </c>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" t="inlineStr">
         <is>
-          <t>A 27432-2025</t>
+          <t>A 27441-2025</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -7440,7 +7440,7 @@
         <v>45813</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7458,7 +7458,7 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>3.6</v>
+        <v>1.2</v>
       </c>
       <c r="J63" t="n">
         <v>1</v>
@@ -7498,42 +7498,42 @@
       </c>
       <c r="V63" s="2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="W63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 27432-2025 artfynd.xlsx", "A 27432-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 27441-2025 artfynd.xlsx", "A 27441-2025")</f>
         <v/>
       </c>
       <c r="X63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 27432-2025 karta.png", "A 27432-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 27441-2025 karta.png", "A 27441-2025")</f>
         <v/>
       </c>
       <c r="Y63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 27432-2025 georefererad karta.tif", "A 27432-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 27441-2025 georefererad karta.tif", "A 27441-2025")</f>
         <v/>
       </c>
       <c r="AA63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 27432-2025 FSC-klagomål.docx", "A 27432-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 27441-2025 FSC-klagomål.docx", "A 27441-2025")</f>
         <v/>
       </c>
       <c r="AB63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 27432-2025 FSC-klagomål mail.docx", "A 27432-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 27441-2025 FSC-klagomål mail.docx", "A 27441-2025")</f>
         <v/>
       </c>
       <c r="AC63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 27432-2025 tillsynsbegäran.docx", "A 27432-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 27441-2025 tillsynsbegäran.docx", "A 27441-2025")</f>
         <v/>
       </c>
       <c r="AD63">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 27432-2025 tillsynsbegäran mail.docx", "A 27432-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 27441-2025 tillsynsbegäran mail.docx", "A 27441-2025")</f>
         <v/>
       </c>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" t="inlineStr">
         <is>
-          <t>A 27441-2025</t>
+          <t>A 27431-2025</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -7550,7 +7550,7 @@
         <v>45813</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>1.2</v>
+        <v>3.4</v>
       </c>
       <c r="J64" t="n">
         <v>1</v>
@@ -7580,7 +7580,7 @@
         <v>0</v>
       </c>
       <c r="M64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
@@ -7592,51 +7592,51 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S64" t="n">
         <v>1</v>
       </c>
       <c r="T64" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="U64" t="n">
         <v>0</v>
       </c>
       <c r="V64" s="2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Väddnätfjäril</t>
         </is>
       </c>
       <c r="W64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 27441-2025 artfynd.xlsx", "A 27441-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/artfynd/A 27431-2025 artfynd.xlsx", "A 27431-2025")</f>
         <v/>
       </c>
       <c r="X64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 27441-2025 karta.png", "A 27441-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor/A 27431-2025 karta.png", "A 27431-2025")</f>
         <v/>
       </c>
       <c r="Y64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 27441-2025 georefererad karta.tif", "A 27441-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/kartor_geotiff/A 27431-2025 georefererad karta.tif", "A 27431-2025")</f>
         <v/>
       </c>
       <c r="AA64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 27441-2025 FSC-klagomål.docx", "A 27441-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomål/A 27431-2025 FSC-klagomål.docx", "A 27431-2025")</f>
         <v/>
       </c>
       <c r="AB64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 27441-2025 FSC-klagomål mail.docx", "A 27441-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/klagomålsmail/A 27431-2025 FSC-klagomål mail.docx", "A 27431-2025")</f>
         <v/>
       </c>
       <c r="AC64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 27441-2025 tillsynsbegäran.docx", "A 27441-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsyn/A 27431-2025 tillsynsbegäran.docx", "A 27431-2025")</f>
         <v/>
       </c>
       <c r="AD64">
-        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 27441-2025 tillsynsbegäran mail.docx", "A 27441-2025")</f>
+        <f>HYPERLINK("https://klasma.github.io/Logging_2104/tillsynsmail/A 27431-2025 tillsynsbegäran mail.docx", "A 27431-2025")</f>
         <v/>
       </c>
     </row>
@@ -7660,7 +7660,7 @@
         <v>45348</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>45860</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7875,7 +7875,7 @@
         <v>45870</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7985,7 +7985,7 @@
         <v>45874</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>45881</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>45701</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>45727</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45706</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44868</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44582</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>44501</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>44512</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>44873</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44868</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>44692</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9043,7 +9043,7 @@
     <row r="80" ht="15" customHeight="1">
       <c r="A80" t="inlineStr">
         <is>
-          <t>A 17179-2025</t>
+          <t>A 35505-2024</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -9057,10 +9057,10 @@
         </is>
       </c>
       <c r="D80" s="1" t="n">
-        <v>45755</v>
+        <v>45531</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9074,11 +9074,11 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I80" t="n">
-        <v>1.3</v>
+        <v>1</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -9121,7 +9121,7 @@
     <row r="81" ht="15" customHeight="1">
       <c r="A81" t="inlineStr">
         <is>
-          <t>A 35498-2024</t>
+          <t>A 13473-2024</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -9135,10 +9135,10 @@
         </is>
       </c>
       <c r="D81" s="1" t="n">
-        <v>45531</v>
+        <v>45387</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9150,13 +9150,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I81" t="n">
-        <v>2.7</v>
+        <v>1.8</v>
       </c>
       <c r="J81" t="n">
         <v>0</v>
@@ -9199,7 +9194,7 @@
     <row r="82" ht="15" customHeight="1">
       <c r="A82" t="inlineStr">
         <is>
-          <t>A 6929-2023</t>
+          <t>A 22226-2024</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -9213,10 +9208,10 @@
         </is>
       </c>
       <c r="D82" s="1" t="n">
-        <v>44967</v>
+        <v>45446</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9229,7 +9224,7 @@
         </is>
       </c>
       <c r="I82" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J82" t="n">
         <v>0</v>
@@ -9272,7 +9267,7 @@
     <row r="83" ht="15" customHeight="1">
       <c r="A83" t="inlineStr">
         <is>
-          <t>A 33978-2024</t>
+          <t>A 23376-2024</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -9286,10 +9281,10 @@
         </is>
       </c>
       <c r="D83" s="1" t="n">
-        <v>45523</v>
+        <v>45453</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9301,8 +9296,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I83" t="n">
-        <v>0.6</v>
+        <v>10.8</v>
       </c>
       <c r="J83" t="n">
         <v>0</v>
@@ -9345,7 +9345,7 @@
     <row r="84" ht="15" customHeight="1">
       <c r="A84" t="inlineStr">
         <is>
-          <t>A 33984-2024</t>
+          <t>A 37744-2022</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -9359,10 +9359,10 @@
         </is>
       </c>
       <c r="D84" s="1" t="n">
-        <v>45523</v>
+        <v>44810</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9375,7 +9375,7 @@
         </is>
       </c>
       <c r="I84" t="n">
-        <v>0.5</v>
+        <v>1.1</v>
       </c>
       <c r="J84" t="n">
         <v>0</v>
@@ -9418,7 +9418,7 @@
     <row r="85" ht="15" customHeight="1">
       <c r="A85" t="inlineStr">
         <is>
-          <t>A 4032-2025</t>
+          <t>A 30229-2024</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -9428,14 +9428,14 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D85" s="1" t="n">
-        <v>45684</v>
+        <v>45490</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9447,8 +9447,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I85" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="J85" t="n">
         <v>0</v>
@@ -9491,7 +9496,7 @@
     <row r="86" ht="15" customHeight="1">
       <c r="A86" t="inlineStr">
         <is>
-          <t>A 28391-2024</t>
+          <t>A 62596-2023</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -9505,10 +9510,10 @@
         </is>
       </c>
       <c r="D86" s="1" t="n">
-        <v>45477</v>
+        <v>45271</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9520,13 +9525,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I86" t="n">
-        <v>2.7</v>
+        <v>3.6</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -9569,7 +9569,7 @@
     <row r="87" ht="15" customHeight="1">
       <c r="A87" t="inlineStr">
         <is>
-          <t>A 33296-2023</t>
+          <t>A 41020-2023</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -9583,10 +9583,10 @@
         </is>
       </c>
       <c r="D87" s="1" t="n">
-        <v>45127</v>
+        <v>45173</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9604,7 +9604,7 @@
         </is>
       </c>
       <c r="I87" t="n">
-        <v>6.4</v>
+        <v>1.5</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -9647,7 +9647,7 @@
     <row r="88" ht="15" customHeight="1">
       <c r="A88" t="inlineStr">
         <is>
-          <t>A 51337-2023</t>
+          <t>A 30007-2024</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -9661,10 +9661,10 @@
         </is>
       </c>
       <c r="D88" s="1" t="n">
-        <v>45219</v>
+        <v>45488</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9676,8 +9676,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>11.5</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -9720,7 +9725,7 @@
     <row r="89" ht="15" customHeight="1">
       <c r="A89" t="inlineStr">
         <is>
-          <t>A 54149-2023</t>
+          <t>A 30009-2024</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -9734,10 +9739,10 @@
         </is>
       </c>
       <c r="D89" s="1" t="n">
-        <v>45232</v>
+        <v>45488</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9749,8 +9754,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I89" t="n">
-        <v>4.6</v>
+        <v>0.6</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -9793,7 +9803,7 @@
     <row r="90" ht="15" customHeight="1">
       <c r="A90" t="inlineStr">
         <is>
-          <t>A 37743-2022</t>
+          <t>A 13471-2024</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -9807,10 +9817,10 @@
         </is>
       </c>
       <c r="D90" s="1" t="n">
-        <v>44810</v>
+        <v>45387</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9823,7 +9833,7 @@
         </is>
       </c>
       <c r="I90" t="n">
-        <v>1.6</v>
+        <v>2.9</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -9866,7 +9876,7 @@
     <row r="91" ht="15" customHeight="1">
       <c r="A91" t="inlineStr">
         <is>
-          <t>A 58240-2021</t>
+          <t>A 58787-2021</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -9880,10 +9890,10 @@
         </is>
       </c>
       <c r="D91" s="1" t="n">
-        <v>44487</v>
+        <v>44489</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9939,7 +9949,7 @@
     <row r="92" ht="15" customHeight="1">
       <c r="A92" t="inlineStr">
         <is>
-          <t>A 13471-2024</t>
+          <t>A 6963-2024</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -9953,10 +9963,10 @@
         </is>
       </c>
       <c r="D92" s="1" t="n">
-        <v>45387</v>
+        <v>45343</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -9969,7 +9979,7 @@
         </is>
       </c>
       <c r="I92" t="n">
-        <v>2.9</v>
+        <v>2.4</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -10012,7 +10022,7 @@
     <row r="93" ht="15" customHeight="1">
       <c r="A93" t="inlineStr">
         <is>
-          <t>A 11953-2025</t>
+          <t>A 31645-2024</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -10026,10 +10036,10 @@
         </is>
       </c>
       <c r="D93" s="1" t="n">
-        <v>45728</v>
+        <v>45506</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10047,7 +10057,7 @@
         </is>
       </c>
       <c r="I93" t="n">
-        <v>34.8</v>
+        <v>11.1</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -10090,7 +10100,7 @@
     <row r="94" ht="15" customHeight="1">
       <c r="A94" t="inlineStr">
         <is>
-          <t>A 37680-2022</t>
+          <t>A 54149-2023</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -10104,10 +10114,10 @@
         </is>
       </c>
       <c r="D94" s="1" t="n">
-        <v>44810</v>
+        <v>45232</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10120,7 +10130,7 @@
         </is>
       </c>
       <c r="I94" t="n">
-        <v>6.6</v>
+        <v>4.6</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -10163,7 +10173,7 @@
     <row r="95" ht="15" customHeight="1">
       <c r="A95" t="inlineStr">
         <is>
-          <t>A 27738-2024</t>
+          <t>A 47359-2024</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -10177,10 +10187,10 @@
         </is>
       </c>
       <c r="D95" s="1" t="n">
-        <v>45475</v>
+        <v>45587</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10192,13 +10202,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I95" t="n">
-        <v>2.6</v>
+        <v>1.2</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -10241,7 +10246,7 @@
     <row r="96" ht="15" customHeight="1">
       <c r="A96" t="inlineStr">
         <is>
-          <t>A 58373-2023</t>
+          <t>A 16371-2022</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -10255,10 +10260,10 @@
         </is>
       </c>
       <c r="D96" s="1" t="n">
-        <v>45250</v>
+        <v>44671</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10271,7 +10276,7 @@
         </is>
       </c>
       <c r="I96" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -10314,7 +10319,7 @@
     <row r="97" ht="15" customHeight="1">
       <c r="A97" t="inlineStr">
         <is>
-          <t>A 41020-2023</t>
+          <t>A 23355-2024</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -10328,10 +10333,10 @@
         </is>
       </c>
       <c r="D97" s="1" t="n">
-        <v>45173</v>
+        <v>45453</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10349,7 +10354,7 @@
         </is>
       </c>
       <c r="I97" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -10392,7 +10397,7 @@
     <row r="98" ht="15" customHeight="1">
       <c r="A98" t="inlineStr">
         <is>
-          <t>A 23355-2024</t>
+          <t>A 11607-2023</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -10406,10 +10411,10 @@
         </is>
       </c>
       <c r="D98" s="1" t="n">
-        <v>45453</v>
+        <v>44994</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10423,11 +10428,11 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I98" t="n">
-        <v>1.2</v>
+        <v>1.1</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -10470,7 +10475,7 @@
     <row r="99" ht="15" customHeight="1">
       <c r="A99" t="inlineStr">
         <is>
-          <t>A 44356-2023</t>
+          <t>A 6929-2023</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -10484,10 +10489,10 @@
         </is>
       </c>
       <c r="D99" s="1" t="n">
-        <v>45188</v>
+        <v>44967</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10500,7 +10505,7 @@
         </is>
       </c>
       <c r="I99" t="n">
-        <v>2.1</v>
+        <v>0.9</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -10543,7 +10548,7 @@
     <row r="100" ht="15" customHeight="1">
       <c r="A100" t="inlineStr">
         <is>
-          <t>A 13744-2023</t>
+          <t>A 25474-2024</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -10557,10 +10562,10 @@
         </is>
       </c>
       <c r="D100" s="1" t="n">
-        <v>45007</v>
+        <v>45463</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10574,11 +10579,11 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I100" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -10621,7 +10626,7 @@
     <row r="101" ht="15" customHeight="1">
       <c r="A101" t="inlineStr">
         <is>
-          <t>A 8510-2023</t>
+          <t>A 38741-2025</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -10635,10 +10640,10 @@
         </is>
       </c>
       <c r="D101" s="1" t="n">
-        <v>44977</v>
+        <v>45887</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10650,8 +10655,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I101" t="n">
-        <v>0.4</v>
+        <v>2.5</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -10694,7 +10704,7 @@
     <row r="102" ht="15" customHeight="1">
       <c r="A102" t="inlineStr">
         <is>
-          <t>A 47495-2024</t>
+          <t>A 11813-2024</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -10708,10 +10718,10 @@
         </is>
       </c>
       <c r="D102" s="1" t="n">
-        <v>45587</v>
+        <v>45376</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10723,13 +10733,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I102" t="n">
-        <v>5.2</v>
+        <v>2.3</v>
       </c>
       <c r="J102" t="n">
         <v>0</v>
@@ -10772,7 +10777,7 @@
     <row r="103" ht="15" customHeight="1">
       <c r="A103" t="inlineStr">
         <is>
-          <t>A 30007-2024</t>
+          <t>A 16888-2026</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -10786,10 +10791,10 @@
         </is>
       </c>
       <c r="D103" s="1" t="n">
-        <v>45488</v>
+        <v>46113</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10801,13 +10806,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I103" t="n">
-        <v>11.5</v>
+        <v>2</v>
       </c>
       <c r="J103" t="n">
         <v>0</v>
@@ -10850,7 +10850,7 @@
     <row r="104" ht="15" customHeight="1">
       <c r="A104" t="inlineStr">
         <is>
-          <t>A 30009-2024</t>
+          <t>A 11953-2025</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -10864,10 +10864,10 @@
         </is>
       </c>
       <c r="D104" s="1" t="n">
-        <v>45488</v>
+        <v>45728</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10885,7 +10885,7 @@
         </is>
       </c>
       <c r="I104" t="n">
-        <v>0.6</v>
+        <v>34.8</v>
       </c>
       <c r="J104" t="n">
         <v>0</v>
@@ -10928,7 +10928,7 @@
     <row r="105" ht="15" customHeight="1">
       <c r="A105" t="inlineStr">
         <is>
-          <t>A 38741-2025</t>
+          <t>A 40407-2025</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -10938,14 +10938,14 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D105" s="1" t="n">
-        <v>45887</v>
+        <v>45895</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         </is>
       </c>
       <c r="I105" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -11006,7 +11006,7 @@
     <row r="106" ht="15" customHeight="1">
       <c r="A106" t="inlineStr">
         <is>
-          <t>A 38486-2025</t>
+          <t>A 37743-2022</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -11020,10 +11020,10 @@
         </is>
       </c>
       <c r="D106" s="1" t="n">
-        <v>45884</v>
+        <v>44810</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11036,7 +11036,7 @@
         </is>
       </c>
       <c r="I106" t="n">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="J106" t="n">
         <v>0</v>
@@ -11079,7 +11079,7 @@
     <row r="107" ht="15" customHeight="1">
       <c r="A107" t="inlineStr">
         <is>
-          <t>A 37763-2023</t>
+          <t>A 38486-2025</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -11093,10 +11093,10 @@
         </is>
       </c>
       <c r="D107" s="1" t="n">
-        <v>45156</v>
+        <v>45884</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11109,7 +11109,7 @@
         </is>
       </c>
       <c r="I107" t="n">
-        <v>2.9</v>
+        <v>1.9</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -11152,7 +11152,7 @@
     <row r="108" ht="15" customHeight="1">
       <c r="A108" t="inlineStr">
         <is>
-          <t>A 43885-2025</t>
+          <t>A 51337-2023</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -11166,10 +11166,10 @@
         </is>
       </c>
       <c r="D108" s="1" t="n">
-        <v>45912</v>
+        <v>45219</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11181,13 +11181,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I108" t="n">
-        <v>1.6</v>
+        <v>1</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -11230,7 +11225,7 @@
     <row r="109" ht="15" customHeight="1">
       <c r="A109" t="inlineStr">
         <is>
-          <t>A 35505-2024</t>
+          <t>A 17185-2025</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -11244,10 +11239,10 @@
         </is>
       </c>
       <c r="D109" s="1" t="n">
-        <v>45531</v>
+        <v>45755</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11261,11 +11256,11 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog väst AB</t>
         </is>
       </c>
       <c r="I109" t="n">
-        <v>1</v>
+        <v>10.3</v>
       </c>
       <c r="J109" t="n">
         <v>0</v>
@@ -11308,7 +11303,7 @@
     <row r="110" ht="15" customHeight="1">
       <c r="A110" t="inlineStr">
         <is>
-          <t>A 30229-2024</t>
+          <t>A 37680-2022</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -11322,10 +11317,10 @@
         </is>
       </c>
       <c r="D110" s="1" t="n">
-        <v>45490</v>
+        <v>44810</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11337,13 +11332,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I110" t="n">
-        <v>3.3</v>
+        <v>6.6</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -11386,7 +11376,7 @@
     <row r="111" ht="15" customHeight="1">
       <c r="A111" t="inlineStr">
         <is>
-          <t>A 11277-2026</t>
+          <t>A 44692-2025</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -11400,10 +11390,10 @@
         </is>
       </c>
       <c r="D111" s="1" t="n">
-        <v>46080</v>
+        <v>45917</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11421,7 +11411,7 @@
         </is>
       </c>
       <c r="I111" t="n">
-        <v>2.1</v>
+        <v>5.4</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -11464,7 +11454,7 @@
     <row r="112" ht="15" customHeight="1">
       <c r="A112" t="inlineStr">
         <is>
-          <t>A 2612-2025</t>
+          <t>A 22129-2023</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -11478,10 +11468,10 @@
         </is>
       </c>
       <c r="D112" s="1" t="n">
-        <v>45674</v>
+        <v>45069</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11493,8 +11483,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I112" t="n">
-        <v>3.8</v>
+        <v>0.7</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -11537,7 +11532,7 @@
     <row r="113" ht="15" customHeight="1">
       <c r="A113" t="inlineStr">
         <is>
-          <t>A 40407-2025</t>
+          <t>A 47249-2025</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -11547,14 +11542,14 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D113" s="1" t="n">
-        <v>45895</v>
+        <v>45930</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11566,13 +11561,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I113" t="n">
-        <v>2.2</v>
+        <v>1.6</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -11615,7 +11605,7 @@
     <row r="114" ht="15" customHeight="1">
       <c r="A114" t="inlineStr">
         <is>
-          <t>A 25474-2024</t>
+          <t>A 12922-2026</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -11629,10 +11619,10 @@
         </is>
       </c>
       <c r="D114" s="1" t="n">
-        <v>45463</v>
+        <v>46092</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11650,7 +11640,7 @@
         </is>
       </c>
       <c r="I114" t="n">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -11693,7 +11683,7 @@
     <row r="115" ht="15" customHeight="1">
       <c r="A115" t="inlineStr">
         <is>
-          <t>A 23376-2024</t>
+          <t>A 47091-2025</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -11707,10 +11697,10 @@
         </is>
       </c>
       <c r="D115" s="1" t="n">
-        <v>45453</v>
+        <v>45929</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11722,13 +11712,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I115" t="n">
-        <v>10.8</v>
+        <v>3.7</v>
       </c>
       <c r="J115" t="n">
         <v>0</v>
@@ -11771,7 +11756,7 @@
     <row r="116" ht="15" customHeight="1">
       <c r="A116" t="inlineStr">
         <is>
-          <t>A 11813-2024</t>
+          <t>A 28133-2024</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -11785,10 +11770,10 @@
         </is>
       </c>
       <c r="D116" s="1" t="n">
-        <v>45376</v>
+        <v>45476</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11801,7 +11786,7 @@
         </is>
       </c>
       <c r="I116" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="J116" t="n">
         <v>0</v>
@@ -11844,7 +11829,7 @@
     <row r="117" ht="15" customHeight="1">
       <c r="A117" t="inlineStr">
         <is>
-          <t>A 58955-2023</t>
+          <t>A 33978-2024</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -11858,10 +11843,10 @@
         </is>
       </c>
       <c r="D117" s="1" t="n">
-        <v>45252</v>
+        <v>45523</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11874,7 +11859,7 @@
         </is>
       </c>
       <c r="I117" t="n">
-        <v>1.4</v>
+        <v>0.6</v>
       </c>
       <c r="J117" t="n">
         <v>0</v>
@@ -11917,7 +11902,7 @@
     <row r="118" ht="15" customHeight="1">
       <c r="A118" t="inlineStr">
         <is>
-          <t>A 15217-2026</t>
+          <t>A 33984-2024</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -11931,10 +11916,10 @@
         </is>
       </c>
       <c r="D118" s="1" t="n">
-        <v>46105</v>
+        <v>45523</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -11946,13 +11931,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H118" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I118" t="n">
-        <v>1.3</v>
+        <v>0.5</v>
       </c>
       <c r="J118" t="n">
         <v>0</v>
@@ -11995,7 +11975,7 @@
     <row r="119" ht="15" customHeight="1">
       <c r="A119" t="inlineStr">
         <is>
-          <t>A 12922-2026</t>
+          <t>A 48232-2025</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -12009,10 +11989,10 @@
         </is>
       </c>
       <c r="D119" s="1" t="n">
-        <v>46092</v>
+        <v>45933</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12030,7 +12010,7 @@
         </is>
       </c>
       <c r="I119" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J119" t="n">
         <v>0</v>
@@ -12090,7 +12070,7 @@
         <v>45629</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12146,7 +12126,7 @@
     <row r="121" ht="15" customHeight="1">
       <c r="A121" t="inlineStr">
         <is>
-          <t>A 11871-2026</t>
+          <t>A 48612-2025</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -12160,10 +12140,10 @@
         </is>
       </c>
       <c r="D121" s="1" t="n">
-        <v>46085</v>
+        <v>45935</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12175,8 +12155,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I121" t="n">
-        <v>1.3</v>
+        <v>5.3</v>
       </c>
       <c r="J121" t="n">
         <v>0</v>
@@ -12219,7 +12204,7 @@
     <row r="122" ht="15" customHeight="1">
       <c r="A122" t="inlineStr">
         <is>
-          <t>A 16888-2026</t>
+          <t>A 48231-2025</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -12233,10 +12218,10 @@
         </is>
       </c>
       <c r="D122" s="1" t="n">
-        <v>46113</v>
+        <v>45933</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12248,8 +12233,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I122" t="n">
-        <v>2</v>
+        <v>2.7</v>
       </c>
       <c r="J122" t="n">
         <v>0</v>
@@ -12292,7 +12282,7 @@
     <row r="123" ht="15" customHeight="1">
       <c r="A123" t="inlineStr">
         <is>
-          <t>A 6963-2024</t>
+          <t>A 27959-2025</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -12306,10 +12296,10 @@
         </is>
       </c>
       <c r="D123" s="1" t="n">
-        <v>45343</v>
+        <v>45816</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12321,8 +12311,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I123" t="n">
-        <v>2.4</v>
+        <v>45.6</v>
       </c>
       <c r="J123" t="n">
         <v>0</v>
@@ -12365,7 +12360,7 @@
     <row r="124" ht="15" customHeight="1">
       <c r="A124" t="inlineStr">
         <is>
-          <t>A 22129-2023</t>
+          <t>A 48240-2025</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -12375,14 +12370,14 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D124" s="1" t="n">
-        <v>45069</v>
+        <v>45933</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12400,7 +12395,7 @@
         </is>
       </c>
       <c r="I124" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="J124" t="n">
         <v>0</v>
@@ -12443,7 +12438,7 @@
     <row r="125" ht="15" customHeight="1">
       <c r="A125" t="inlineStr">
         <is>
-          <t>A 44692-2025</t>
+          <t>A 48241-2025</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -12457,10 +12452,10 @@
         </is>
       </c>
       <c r="D125" s="1" t="n">
-        <v>45917</v>
+        <v>45933</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12478,7 +12473,7 @@
         </is>
       </c>
       <c r="I125" t="n">
-        <v>5.4</v>
+        <v>1.1</v>
       </c>
       <c r="J125" t="n">
         <v>0</v>
@@ -12538,7 +12533,7 @@
         <v>45538</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12594,7 +12589,7 @@
     <row r="127" ht="15" customHeight="1">
       <c r="A127" t="inlineStr">
         <is>
-          <t>A 47091-2025</t>
+          <t>A 51225-2025</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -12608,10 +12603,10 @@
         </is>
       </c>
       <c r="D127" s="1" t="n">
-        <v>45929</v>
+        <v>45947</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12623,8 +12618,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I127" t="n">
-        <v>3.7</v>
+        <v>2.1</v>
       </c>
       <c r="J127" t="n">
         <v>0</v>
@@ -12667,7 +12667,7 @@
     <row r="128" ht="15" customHeight="1">
       <c r="A128" t="inlineStr">
         <is>
-          <t>A 21027-2024</t>
+          <t>A 10161-2023</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -12681,10 +12681,10 @@
         </is>
       </c>
       <c r="D128" s="1" t="n">
-        <v>45439</v>
+        <v>44986</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12698,11 +12698,11 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I128" t="n">
-        <v>1.9</v>
+        <v>0.6</v>
       </c>
       <c r="J128" t="n">
         <v>0</v>
@@ -12745,7 +12745,7 @@
     <row r="129" ht="15" customHeight="1">
       <c r="A129" t="inlineStr">
         <is>
-          <t>A 21028-2024</t>
+          <t>A 52693-2025</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -12759,10 +12759,10 @@
         </is>
       </c>
       <c r="D129" s="1" t="n">
-        <v>45439</v>
+        <v>45956</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12774,13 +12774,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I129" t="n">
-        <v>1.6</v>
+        <v>1.4</v>
       </c>
       <c r="J129" t="n">
         <v>0</v>
@@ -12823,7 +12818,7 @@
     <row r="130" ht="15" customHeight="1">
       <c r="A130" t="inlineStr">
         <is>
-          <t>A 16371-2022</t>
+          <t>A 3614-2026</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -12837,10 +12832,10 @@
         </is>
       </c>
       <c r="D130" s="1" t="n">
-        <v>44671</v>
+        <v>46042</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12853,7 +12848,7 @@
         </is>
       </c>
       <c r="I130" t="n">
-        <v>0.8</v>
+        <v>2.2</v>
       </c>
       <c r="J130" t="n">
         <v>0</v>
@@ -12896,7 +12891,7 @@
     <row r="131" ht="15" customHeight="1">
       <c r="A131" t="inlineStr">
         <is>
-          <t>A 47249-2025</t>
+          <t>A 3391-2026</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -12910,10 +12905,10 @@
         </is>
       </c>
       <c r="D131" s="1" t="n">
-        <v>45930</v>
+        <v>46042</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12926,7 +12921,7 @@
         </is>
       </c>
       <c r="I131" t="n">
-        <v>1.6</v>
+        <v>0.7</v>
       </c>
       <c r="J131" t="n">
         <v>0</v>
@@ -12969,7 +12964,7 @@
     <row r="132" ht="15" customHeight="1">
       <c r="A132" t="inlineStr">
         <is>
-          <t>A 48232-2025</t>
+          <t>A 23545-2025</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -12979,14 +12974,14 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D132" s="1" t="n">
-        <v>45933</v>
+        <v>45792</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -12998,13 +12993,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I132" t="n">
-        <v>1</v>
+        <v>3.5</v>
       </c>
       <c r="J132" t="n">
         <v>0</v>
@@ -13047,7 +13037,7 @@
     <row r="133" ht="15" customHeight="1">
       <c r="A133" t="inlineStr">
         <is>
-          <t>A 27959-2025</t>
+          <t>A 54827-2025</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -13061,10 +13051,10 @@
         </is>
       </c>
       <c r="D133" s="1" t="n">
-        <v>45816</v>
+        <v>45966</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13076,13 +13066,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I133" t="n">
-        <v>45.6</v>
+        <v>2.3</v>
       </c>
       <c r="J133" t="n">
         <v>0</v>
@@ -13125,7 +13110,7 @@
     <row r="134" ht="15" customHeight="1">
       <c r="A134" t="inlineStr">
         <is>
-          <t>A 48240-2025</t>
+          <t>A 31611-2023</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -13135,14 +13120,14 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D134" s="1" t="n">
-        <v>45933</v>
+        <v>45117</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13154,13 +13139,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I134" t="n">
-        <v>1.3</v>
+        <v>4.4</v>
       </c>
       <c r="J134" t="n">
         <v>0</v>
@@ -13203,7 +13183,7 @@
     <row r="135" ht="15" customHeight="1">
       <c r="A135" t="inlineStr">
         <is>
-          <t>A 48241-2025</t>
+          <t>A 55287-2025</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -13217,10 +13197,10 @@
         </is>
       </c>
       <c r="D135" s="1" t="n">
-        <v>45933</v>
+        <v>45969</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13232,13 +13212,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H135" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I135" t="n">
-        <v>1.1</v>
+        <v>2.7</v>
       </c>
       <c r="J135" t="n">
         <v>0</v>
@@ -13281,7 +13256,7 @@
     <row r="136" ht="15" customHeight="1">
       <c r="A136" t="inlineStr">
         <is>
-          <t>A 48231-2025</t>
+          <t>A 55288-2025</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -13295,10 +13270,10 @@
         </is>
       </c>
       <c r="D136" s="1" t="n">
-        <v>45933</v>
+        <v>45969</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13310,13 +13285,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I136" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="J136" t="n">
         <v>0</v>
@@ -13359,7 +13329,7 @@
     <row r="137" ht="15" customHeight="1">
       <c r="A137" t="inlineStr">
         <is>
-          <t>A 48612-2025</t>
+          <t>A 23326-2026</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -13373,10 +13343,10 @@
         </is>
       </c>
       <c r="D137" s="1" t="n">
-        <v>45935</v>
+        <v>46162</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13390,11 +13360,11 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I137" t="n">
-        <v>5.3</v>
+        <v>1.4</v>
       </c>
       <c r="J137" t="n">
         <v>0</v>
@@ -13437,7 +13407,7 @@
     <row r="138" ht="15" customHeight="1">
       <c r="A138" t="inlineStr">
         <is>
-          <t>A 57751-2024</t>
+          <t>A 57593-2025</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -13451,10 +13421,10 @@
         </is>
       </c>
       <c r="D138" s="1" t="n">
-        <v>45630</v>
+        <v>45980</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13510,7 +13480,7 @@
     <row r="139" ht="15" customHeight="1">
       <c r="A139" t="inlineStr">
         <is>
-          <t>A 51225-2025</t>
+          <t>A 57595-2025</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -13524,10 +13494,10 @@
         </is>
       </c>
       <c r="D139" s="1" t="n">
-        <v>45947</v>
+        <v>45980</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13539,13 +13509,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I139" t="n">
-        <v>2.1</v>
+        <v>1.6</v>
       </c>
       <c r="J139" t="n">
         <v>0</v>
@@ -13588,7 +13553,7 @@
     <row r="140" ht="15" customHeight="1">
       <c r="A140" t="inlineStr">
         <is>
-          <t>A 3391-2026</t>
+          <t>A 57596-2025</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -13602,10 +13567,10 @@
         </is>
       </c>
       <c r="D140" s="1" t="n">
-        <v>46042</v>
+        <v>45980</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13618,7 +13583,7 @@
         </is>
       </c>
       <c r="I140" t="n">
-        <v>0.7</v>
+        <v>1.9</v>
       </c>
       <c r="J140" t="n">
         <v>0</v>
@@ -13661,7 +13626,7 @@
     <row r="141" ht="15" customHeight="1">
       <c r="A141" t="inlineStr">
         <is>
-          <t>A 2915-2025</t>
+          <t>A 23334-2026</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -13675,10 +13640,10 @@
         </is>
       </c>
       <c r="D141" s="1" t="n">
-        <v>45677</v>
+        <v>46162</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13690,8 +13655,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I141" t="n">
-        <v>1.9</v>
+        <v>0.5</v>
       </c>
       <c r="J141" t="n">
         <v>0</v>
@@ -13734,7 +13704,7 @@
     <row r="142" ht="15" customHeight="1">
       <c r="A142" t="inlineStr">
         <is>
-          <t>A 32980-2023</t>
+          <t>A 57594-2025</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -13748,10 +13718,10 @@
         </is>
       </c>
       <c r="D142" s="1" t="n">
-        <v>45125</v>
+        <v>45980</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13764,7 +13734,7 @@
         </is>
       </c>
       <c r="I142" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="J142" t="n">
         <v>0</v>
@@ -13807,7 +13777,7 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" t="inlineStr">
         <is>
-          <t>A 23545-2025</t>
+          <t>A 58633-2025</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -13817,14 +13787,14 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D143" s="1" t="n">
-        <v>45792</v>
+        <v>45986</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13837,7 +13807,7 @@
         </is>
       </c>
       <c r="I143" t="n">
-        <v>3.5</v>
+        <v>1.3</v>
       </c>
       <c r="J143" t="n">
         <v>0</v>
@@ -13880,7 +13850,7 @@
     <row r="144" ht="15" customHeight="1">
       <c r="A144" t="inlineStr">
         <is>
-          <t>A 3614-2026</t>
+          <t>A 8510-2023</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -13894,10 +13864,10 @@
         </is>
       </c>
       <c r="D144" s="1" t="n">
-        <v>46042</v>
+        <v>44977</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13910,7 +13880,7 @@
         </is>
       </c>
       <c r="I144" t="n">
-        <v>2.2</v>
+        <v>0.4</v>
       </c>
       <c r="J144" t="n">
         <v>0</v>
@@ -13953,7 +13923,7 @@
     <row r="145" ht="15" customHeight="1">
       <c r="A145" t="inlineStr">
         <is>
-          <t>A 62596-2023</t>
+          <t>A 27738-2024</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -13967,10 +13937,10 @@
         </is>
       </c>
       <c r="D145" s="1" t="n">
-        <v>45271</v>
+        <v>45475</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -13982,8 +13952,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I145" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="J145" t="n">
         <v>0</v>
@@ -14026,7 +14001,7 @@
     <row r="146" ht="15" customHeight="1">
       <c r="A146" t="inlineStr">
         <is>
-          <t>A 52693-2025</t>
+          <t>A 58805-2025</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -14040,10 +14015,10 @@
         </is>
       </c>
       <c r="D146" s="1" t="n">
-        <v>45956</v>
+        <v>45986</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14056,7 +14031,7 @@
         </is>
       </c>
       <c r="I146" t="n">
-        <v>1.4</v>
+        <v>1.3</v>
       </c>
       <c r="J146" t="n">
         <v>0</v>
@@ -14099,7 +14074,7 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" t="inlineStr">
         <is>
-          <t>A 8448-2025</t>
+          <t>A 31607-2023</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -14109,14 +14084,14 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D147" s="1" t="n">
-        <v>45709</v>
+        <v>45117</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14129,7 +14104,7 @@
         </is>
       </c>
       <c r="I147" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="J147" t="n">
         <v>0</v>
@@ -14172,7 +14147,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" t="inlineStr">
         <is>
-          <t>A 47493-2024</t>
+          <t>A 13744-2023</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -14186,10 +14161,10 @@
         </is>
       </c>
       <c r="D148" s="1" t="n">
-        <v>45587</v>
+        <v>45007</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14203,11 +14178,11 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Övriga statliga verk och myndigheter</t>
         </is>
       </c>
       <c r="I148" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="J148" t="n">
         <v>0</v>
@@ -14250,7 +14225,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" t="inlineStr">
         <is>
-          <t>A 54827-2025</t>
+          <t>A 24988-2023</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -14264,10 +14239,10 @@
         </is>
       </c>
       <c r="D149" s="1" t="n">
-        <v>45966</v>
+        <v>45085</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14279,8 +14254,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I149" t="n">
-        <v>2.3</v>
+        <v>1.9</v>
       </c>
       <c r="J149" t="n">
         <v>0</v>
@@ -14323,7 +14303,7 @@
     <row r="150" ht="15" customHeight="1">
       <c r="A150" t="inlineStr">
         <is>
-          <t>A 55288-2025</t>
+          <t>A 61186-2025</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -14337,10 +14317,10 @@
         </is>
       </c>
       <c r="D150" s="1" t="n">
-        <v>45969</v>
+        <v>46000</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14353,7 +14333,7 @@
         </is>
       </c>
       <c r="I150" t="n">
-        <v>2.6</v>
+        <v>4.2</v>
       </c>
       <c r="J150" t="n">
         <v>0</v>
@@ -14396,7 +14376,7 @@
     <row r="151" ht="15" customHeight="1">
       <c r="A151" t="inlineStr">
         <is>
-          <t>A 55287-2025</t>
+          <t>A 23833-2026</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -14410,10 +14390,10 @@
         </is>
       </c>
       <c r="D151" s="1" t="n">
-        <v>45969</v>
+        <v>46167</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14425,8 +14405,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I151" t="n">
-        <v>2.7</v>
+        <v>1</v>
       </c>
       <c r="J151" t="n">
         <v>0</v>
@@ -14469,7 +14454,7 @@
     <row r="152" ht="15" customHeight="1">
       <c r="A152" t="inlineStr">
         <is>
-          <t>A 23334-2026</t>
+          <t>A 61642-2025</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -14483,10 +14468,10 @@
         </is>
       </c>
       <c r="D152" s="1" t="n">
-        <v>46162</v>
+        <v>46002</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14498,13 +14483,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I152" t="n">
-        <v>0.5</v>
+        <v>3.4</v>
       </c>
       <c r="J152" t="n">
         <v>0</v>
@@ -14547,7 +14527,7 @@
     <row r="153" ht="15" customHeight="1">
       <c r="A153" t="inlineStr">
         <is>
-          <t>A 10161-2023</t>
+          <t>A 35136-2023</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -14561,10 +14541,10 @@
         </is>
       </c>
       <c r="D153" s="1" t="n">
-        <v>44986</v>
+        <v>45145</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14576,13 +14556,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I153" t="n">
-        <v>0.6</v>
+        <v>2</v>
       </c>
       <c r="J153" t="n">
         <v>0</v>
@@ -14625,7 +14600,7 @@
     <row r="154" ht="15" customHeight="1">
       <c r="A154" t="inlineStr">
         <is>
-          <t>A 57596-2025</t>
+          <t>A 24342-2026</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -14635,14 +14610,14 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D154" s="1" t="n">
-        <v>45980</v>
+        <v>46169</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14654,8 +14629,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I154" t="n">
-        <v>1.9</v>
+        <v>1.5</v>
       </c>
       <c r="J154" t="n">
         <v>0</v>
@@ -14698,7 +14678,7 @@
     <row r="155" ht="15" customHeight="1">
       <c r="A155" t="inlineStr">
         <is>
-          <t>A 57593-2025</t>
+          <t>A 692-2026</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -14712,10 +14692,10 @@
         </is>
       </c>
       <c r="D155" s="1" t="n">
-        <v>45980</v>
+        <v>46029</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14728,7 +14708,7 @@
         </is>
       </c>
       <c r="I155" t="n">
-        <v>1.8</v>
+        <v>0.5</v>
       </c>
       <c r="J155" t="n">
         <v>0</v>
@@ -14771,7 +14751,7 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" t="inlineStr">
         <is>
-          <t>A 57595-2025</t>
+          <t>A 892-2026</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -14785,10 +14765,10 @@
         </is>
       </c>
       <c r="D156" s="1" t="n">
-        <v>45980</v>
+        <v>46030</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14801,7 +14781,7 @@
         </is>
       </c>
       <c r="I156" t="n">
-        <v>1.6</v>
+        <v>3.6</v>
       </c>
       <c r="J156" t="n">
         <v>0</v>
@@ -14844,7 +14824,7 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" t="inlineStr">
         <is>
-          <t>A 23326-2026</t>
+          <t>A 659-2026</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -14858,10 +14838,10 @@
         </is>
       </c>
       <c r="D157" s="1" t="n">
-        <v>46162</v>
+        <v>46029</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14873,13 +14853,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I157" t="n">
-        <v>1.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J157" t="n">
         <v>0</v>
@@ -14922,7 +14897,7 @@
     <row r="158" ht="15" customHeight="1">
       <c r="A158" t="inlineStr">
         <is>
-          <t>A 57594-2025</t>
+          <t>A 2220-2026</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -14936,10 +14911,10 @@
         </is>
       </c>
       <c r="D158" s="1" t="n">
-        <v>45980</v>
+        <v>46036</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14952,7 +14927,7 @@
         </is>
       </c>
       <c r="I158" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="J158" t="n">
         <v>0</v>
@@ -14995,7 +14970,7 @@
     <row r="159" ht="15" customHeight="1">
       <c r="A159" t="inlineStr">
         <is>
-          <t>A 23833-2026</t>
+          <t>A 2546-2026</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -15009,10 +14984,10 @@
         </is>
       </c>
       <c r="D159" s="1" t="n">
-        <v>46167</v>
+        <v>46037</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15024,13 +14999,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I159" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J159" t="n">
         <v>0</v>
@@ -15073,7 +15043,7 @@
     <row r="160" ht="15" customHeight="1">
       <c r="A160" t="inlineStr">
         <is>
-          <t>A 58633-2025</t>
+          <t>A 37693-2023</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -15087,10 +15057,10 @@
         </is>
       </c>
       <c r="D160" s="1" t="n">
-        <v>45986</v>
+        <v>45159</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15103,7 +15073,7 @@
         </is>
       </c>
       <c r="I160" t="n">
-        <v>1.3</v>
+        <v>0.6</v>
       </c>
       <c r="J160" t="n">
         <v>0</v>
@@ -15146,7 +15116,7 @@
     <row r="161" ht="15" customHeight="1">
       <c r="A161" t="inlineStr">
         <is>
-          <t>A 58805-2025</t>
+          <t>A 37763-2023</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -15160,10 +15130,10 @@
         </is>
       </c>
       <c r="D161" s="1" t="n">
-        <v>45986</v>
+        <v>45156</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15176,7 +15146,7 @@
         </is>
       </c>
       <c r="I161" t="n">
-        <v>1.3</v>
+        <v>2.9</v>
       </c>
       <c r="J161" t="n">
         <v>0</v>
@@ -15219,7 +15189,7 @@
     <row r="162" ht="15" customHeight="1">
       <c r="A162" t="inlineStr">
         <is>
-          <t>A 34232-2023</t>
+          <t>A 3615-2026</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -15233,10 +15203,10 @@
         </is>
       </c>
       <c r="D162" s="1" t="n">
-        <v>45127</v>
+        <v>46042</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15248,13 +15218,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I162" t="n">
-        <v>5.8</v>
+        <v>2.4</v>
       </c>
       <c r="J162" t="n">
         <v>0</v>
@@ -15297,7 +15262,7 @@
     <row r="163" ht="15" customHeight="1">
       <c r="A163" t="inlineStr">
         <is>
-          <t>A 24342-2026</t>
+          <t>A 5549-2026</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -15307,14 +15272,14 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D163" s="1" t="n">
-        <v>46169</v>
+        <v>46050</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15326,13 +15291,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I163" t="n">
-        <v>1.5</v>
+        <v>2.4</v>
       </c>
       <c r="J163" t="n">
         <v>0</v>
@@ -15375,7 +15335,7 @@
     <row r="164" ht="15" customHeight="1">
       <c r="A164" t="inlineStr">
         <is>
-          <t>A 61186-2025</t>
+          <t>A 7580-2026</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -15389,10 +15349,10 @@
         </is>
       </c>
       <c r="D164" s="1" t="n">
-        <v>46000</v>
+        <v>46061</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15405,7 +15365,7 @@
         </is>
       </c>
       <c r="I164" t="n">
-        <v>4.2</v>
+        <v>1.5</v>
       </c>
       <c r="J164" t="n">
         <v>0</v>
@@ -15448,7 +15408,7 @@
     <row r="165" ht="15" customHeight="1">
       <c r="A165" t="inlineStr">
         <is>
-          <t>A 61642-2025</t>
+          <t>A 35498-2024</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -15462,10 +15422,10 @@
         </is>
       </c>
       <c r="D165" s="1" t="n">
-        <v>46002</v>
+        <v>45531</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15477,8 +15437,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I165" t="n">
-        <v>3.4</v>
+        <v>2.7</v>
       </c>
       <c r="J165" t="n">
         <v>0</v>
@@ -15521,7 +15486,7 @@
     <row r="166" ht="15" customHeight="1">
       <c r="A166" t="inlineStr">
         <is>
-          <t>A 22226-2024</t>
+          <t>A 8448-2025</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -15535,10 +15500,10 @@
         </is>
       </c>
       <c r="D166" s="1" t="n">
-        <v>45446</v>
+        <v>45709</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15551,7 +15516,7 @@
         </is>
       </c>
       <c r="I166" t="n">
-        <v>0.6</v>
+        <v>1.7</v>
       </c>
       <c r="J166" t="n">
         <v>0</v>
@@ -15594,7 +15559,7 @@
     <row r="167" ht="15" customHeight="1">
       <c r="A167" t="inlineStr">
         <is>
-          <t>A 37693-2023</t>
+          <t>A 4566-2026</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -15608,10 +15573,10 @@
         </is>
       </c>
       <c r="D167" s="1" t="n">
-        <v>45159</v>
+        <v>46047</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15624,7 +15589,7 @@
         </is>
       </c>
       <c r="I167" t="n">
-        <v>0.6</v>
+        <v>1.1</v>
       </c>
       <c r="J167" t="n">
         <v>0</v>
@@ -15667,7 +15632,7 @@
     <row r="168" ht="15" customHeight="1">
       <c r="A168" t="inlineStr">
         <is>
-          <t>A 659-2026</t>
+          <t>A 26516-2026</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -15677,14 +15642,14 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D168" s="1" t="n">
-        <v>46029</v>
+        <v>46183</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15696,8 +15661,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I168" t="n">
-        <v>9.199999999999999</v>
+        <v>1.8</v>
       </c>
       <c r="J168" t="n">
         <v>0</v>
@@ -15740,7 +15710,7 @@
     <row r="169" ht="15" customHeight="1">
       <c r="A169" t="inlineStr">
         <is>
-          <t>A 692-2026</t>
+          <t>A 17762-2022</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -15750,14 +15720,14 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D169" s="1" t="n">
-        <v>46029</v>
+        <v>44680</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15770,7 +15740,7 @@
         </is>
       </c>
       <c r="I169" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="J169" t="n">
         <v>0</v>
@@ -15813,7 +15783,7 @@
     <row r="170" ht="15" customHeight="1">
       <c r="A170" t="inlineStr">
         <is>
-          <t>A 892-2026</t>
+          <t>A 26515-2026</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -15823,14 +15793,14 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D170" s="1" t="n">
-        <v>46030</v>
+        <v>46183</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15842,8 +15812,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I170" t="n">
-        <v>3.6</v>
+        <v>1.4</v>
       </c>
       <c r="J170" t="n">
         <v>0</v>
@@ -15886,7 +15861,7 @@
     <row r="171" ht="15" customHeight="1">
       <c r="A171" t="inlineStr">
         <is>
-          <t>A 2546-2026</t>
+          <t>A 33296-2023</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -15900,10 +15875,10 @@
         </is>
       </c>
       <c r="D171" s="1" t="n">
-        <v>46037</v>
+        <v>45127</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15915,8 +15890,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I171" t="n">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="J171" t="n">
         <v>0</v>
@@ -15959,7 +15939,7 @@
     <row r="172" ht="15" customHeight="1">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A 2220-2026</t>
+          <t>A 11462-2026</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -15973,10 +15953,10 @@
         </is>
       </c>
       <c r="D172" s="1" t="n">
-        <v>46036</v>
+        <v>46083</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -15989,7 +15969,7 @@
         </is>
       </c>
       <c r="I172" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="J172" t="n">
         <v>0</v>
@@ -16032,7 +16012,7 @@
     <row r="173" ht="15" customHeight="1">
       <c r="A173" t="inlineStr">
         <is>
-          <t>A 3615-2026</t>
+          <t>A 12803-2026</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -16046,10 +16026,10 @@
         </is>
       </c>
       <c r="D173" s="1" t="n">
-        <v>46042</v>
+        <v>46092</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16061,8 +16041,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I173" t="n">
-        <v>2.4</v>
+        <v>7.4</v>
       </c>
       <c r="J173" t="n">
         <v>0</v>
@@ -16105,7 +16090,7 @@
     <row r="174" ht="15" customHeight="1">
       <c r="A174" t="inlineStr">
         <is>
-          <t>A 17762-2022</t>
+          <t>A 17179-2025</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -16115,14 +16100,14 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D174" s="1" t="n">
-        <v>44680</v>
+        <v>45755</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16134,8 +16119,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I174" t="n">
-        <v>1</v>
+        <v>1.3</v>
       </c>
       <c r="J174" t="n">
         <v>0</v>
@@ -16178,7 +16168,7 @@
     <row r="175" ht="15" customHeight="1">
       <c r="A175" t="inlineStr">
         <is>
-          <t>A 5549-2026</t>
+          <t>A 58955-2023</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -16192,10 +16182,10 @@
         </is>
       </c>
       <c r="D175" s="1" t="n">
-        <v>46050</v>
+        <v>45252</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16208,7 +16198,7 @@
         </is>
       </c>
       <c r="I175" t="n">
-        <v>2.4</v>
+        <v>1.4</v>
       </c>
       <c r="J175" t="n">
         <v>0</v>
@@ -16251,7 +16241,7 @@
     <row r="176" ht="15" customHeight="1">
       <c r="A176" t="inlineStr">
         <is>
-          <t>A 26515-2026</t>
+          <t>A 64359-2023</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -16261,14 +16251,14 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D176" s="1" t="n">
-        <v>46183</v>
+        <v>45280</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16280,13 +16270,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I176" t="n">
-        <v>1.4</v>
+        <v>4.7</v>
       </c>
       <c r="J176" t="n">
         <v>0</v>
@@ -16329,7 +16314,7 @@
     <row r="177" ht="15" customHeight="1">
       <c r="A177" t="inlineStr">
         <is>
-          <t>A 7580-2026</t>
+          <t>A 28330-2026</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -16343,10 +16328,10 @@
         </is>
       </c>
       <c r="D177" s="1" t="n">
-        <v>46061</v>
+        <v>46196</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16358,8 +16343,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I177" t="n">
-        <v>1.5</v>
+        <v>1.1</v>
       </c>
       <c r="J177" t="n">
         <v>0</v>
@@ -16402,7 +16392,7 @@
     <row r="178" ht="15" customHeight="1">
       <c r="A178" t="inlineStr">
         <is>
-          <t>A 26516-2026</t>
+          <t>A 58373-2023</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -16412,14 +16402,14 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D178" s="1" t="n">
-        <v>46183</v>
+        <v>45250</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16431,13 +16421,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H178" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I178" t="n">
-        <v>1.8</v>
+        <v>0.6</v>
       </c>
       <c r="J178" t="n">
         <v>0</v>
@@ -16480,7 +16465,7 @@
     <row r="179" ht="15" customHeight="1">
       <c r="A179" t="inlineStr">
         <is>
-          <t>A 4566-2026</t>
+          <t>A 15810-2026</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -16494,10 +16479,10 @@
         </is>
       </c>
       <c r="D179" s="1" t="n">
-        <v>46047</v>
+        <v>46107</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16509,8 +16494,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I179" t="n">
-        <v>1.1</v>
+        <v>0.7</v>
       </c>
       <c r="J179" t="n">
         <v>0</v>
@@ -16553,7 +16543,7 @@
     <row r="180" ht="15" customHeight="1">
       <c r="A180" t="inlineStr">
         <is>
-          <t>A 11462-2026</t>
+          <t>A 38251-2022</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -16567,10 +16557,10 @@
         </is>
       </c>
       <c r="D180" s="1" t="n">
-        <v>46083</v>
+        <v>44812</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16583,7 +16573,7 @@
         </is>
       </c>
       <c r="I180" t="n">
-        <v>0.8</v>
+        <v>3.5</v>
       </c>
       <c r="J180" t="n">
         <v>0</v>
@@ -16626,7 +16616,7 @@
     <row r="181" ht="15" customHeight="1">
       <c r="A181" t="inlineStr">
         <is>
-          <t>A 47459-2023</t>
+          <t>A 28329-2026</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -16640,10 +16630,10 @@
         </is>
       </c>
       <c r="D181" s="1" t="n">
-        <v>45202</v>
+        <v>46196</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16655,8 +16645,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I181" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="J181" t="n">
         <v>0</v>
@@ -16699,7 +16694,7 @@
     <row r="182" ht="15" customHeight="1">
       <c r="A182" t="inlineStr">
         <is>
-          <t>A 12803-2026</t>
+          <t>A 17170-2026</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -16713,10 +16708,10 @@
         </is>
       </c>
       <c r="D182" s="1" t="n">
-        <v>46092</v>
+        <v>46115</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16728,13 +16723,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I182" t="n">
-        <v>7.4</v>
+        <v>2.7</v>
       </c>
       <c r="J182" t="n">
         <v>0</v>
@@ -16777,7 +16767,7 @@
     <row r="183" ht="15" customHeight="1">
       <c r="A183" t="inlineStr">
         <is>
-          <t>A 28330-2026</t>
+          <t>A 29060-2026</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -16791,10 +16781,10 @@
         </is>
       </c>
       <c r="D183" s="1" t="n">
-        <v>46196</v>
+        <v>46199</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16812,7 +16802,7 @@
         </is>
       </c>
       <c r="I183" t="n">
-        <v>1.1</v>
+        <v>3.1</v>
       </c>
       <c r="J183" t="n">
         <v>0</v>
@@ -16855,7 +16845,7 @@
     <row r="184" ht="15" customHeight="1">
       <c r="A184" t="inlineStr">
         <is>
-          <t>A 28329-2026</t>
+          <t>A 11873-2026</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -16869,10 +16859,10 @@
         </is>
       </c>
       <c r="D184" s="1" t="n">
-        <v>46196</v>
+        <v>46085</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16884,13 +16874,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I184" t="n">
-        <v>3.1</v>
+        <v>0.5</v>
       </c>
       <c r="J184" t="n">
         <v>0</v>
@@ -16933,7 +16918,7 @@
     <row r="185" ht="15" customHeight="1">
       <c r="A185" t="inlineStr">
         <is>
-          <t>A 35136-2023</t>
+          <t>A 12705-2026</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -16947,10 +16932,10 @@
         </is>
       </c>
       <c r="D185" s="1" t="n">
-        <v>45145</v>
+        <v>46091</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -16962,8 +16947,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I185" t="n">
-        <v>2</v>
+        <v>1.3</v>
       </c>
       <c r="J185" t="n">
         <v>0</v>
@@ -17006,7 +16996,7 @@
     <row r="186" ht="15" customHeight="1">
       <c r="A186" t="inlineStr">
         <is>
-          <t>A 38251-2022</t>
+          <t>A 47459-2023</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -17020,10 +17010,10 @@
         </is>
       </c>
       <c r="D186" s="1" t="n">
-        <v>44812</v>
+        <v>45202</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17036,7 +17026,7 @@
         </is>
       </c>
       <c r="I186" t="n">
-        <v>3.5</v>
+        <v>6</v>
       </c>
       <c r="J186" t="n">
         <v>0</v>
@@ -17079,7 +17069,7 @@
     <row r="187" ht="15" customHeight="1">
       <c r="A187" t="inlineStr">
         <is>
-          <t>A 15810-2026</t>
+          <t>A 68079-2021</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -17093,10 +17083,10 @@
         </is>
       </c>
       <c r="D187" s="1" t="n">
-        <v>46107</v>
+        <v>44526</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17108,13 +17098,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I187" t="n">
-        <v>0.7</v>
+        <v>2.3</v>
       </c>
       <c r="J187" t="n">
         <v>0</v>
@@ -17157,7 +17142,7 @@
     <row r="188" ht="15" customHeight="1">
       <c r="A188" t="inlineStr">
         <is>
-          <t>A 17170-2026</t>
+          <t>A 11871-2026</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -17171,10 +17156,10 @@
         </is>
       </c>
       <c r="D188" s="1" t="n">
-        <v>46115</v>
+        <v>46085</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17187,7 +17172,7 @@
         </is>
       </c>
       <c r="I188" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
       </c>
       <c r="J188" t="n">
         <v>0</v>
@@ -17230,7 +17215,7 @@
     <row r="189" ht="15" customHeight="1">
       <c r="A189" t="inlineStr">
         <is>
-          <t>A 31607-2023</t>
+          <t>A 11277-2026</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -17240,14 +17225,14 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D189" s="1" t="n">
-        <v>45117</v>
+        <v>46080</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17259,8 +17244,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I189" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="J189" t="n">
         <v>0</v>
@@ -17303,7 +17293,7 @@
     <row r="190" ht="15" customHeight="1">
       <c r="A190" t="inlineStr">
         <is>
-          <t>A 31611-2023</t>
+          <t>A 43885-2025</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -17313,14 +17303,14 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D190" s="1" t="n">
-        <v>45117</v>
+        <v>45912</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17332,8 +17322,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I190" t="n">
-        <v>4.4</v>
+        <v>1.6</v>
       </c>
       <c r="J190" t="n">
         <v>0</v>
@@ -17376,7 +17371,7 @@
     <row r="191" ht="15" customHeight="1">
       <c r="A191" t="inlineStr">
         <is>
-          <t>A 29060-2026</t>
+          <t>A 15217-2026</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -17390,10 +17385,10 @@
         </is>
       </c>
       <c r="D191" s="1" t="n">
-        <v>46199</v>
+        <v>46105</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17411,7 +17406,7 @@
         </is>
       </c>
       <c r="I191" t="n">
-        <v>3.1</v>
+        <v>1.3</v>
       </c>
       <c r="J191" t="n">
         <v>0</v>
@@ -17454,7 +17449,7 @@
     <row r="192" ht="15" customHeight="1">
       <c r="A192" t="inlineStr">
         <is>
-          <t>A 11873-2026</t>
+          <t>A 44356-2023</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -17468,10 +17463,10 @@
         </is>
       </c>
       <c r="D192" s="1" t="n">
-        <v>46085</v>
+        <v>45188</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17484,7 +17479,7 @@
         </is>
       </c>
       <c r="I192" t="n">
-        <v>0.5</v>
+        <v>2.1</v>
       </c>
       <c r="J192" t="n">
         <v>0</v>
@@ -17527,7 +17522,7 @@
     <row r="193" ht="15" customHeight="1">
       <c r="A193" t="inlineStr">
         <is>
-          <t>A 12705-2026</t>
+          <t>A 47495-2024</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -17541,10 +17536,10 @@
         </is>
       </c>
       <c r="D193" s="1" t="n">
-        <v>46091</v>
+        <v>45587</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17558,11 +17553,11 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Bergvik skog öst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I193" t="n">
-        <v>1.3</v>
+        <v>5.2</v>
       </c>
       <c r="J193" t="n">
         <v>0</v>
@@ -17605,7 +17600,7 @@
     <row r="194" ht="15" customHeight="1">
       <c r="A194" t="inlineStr">
         <is>
-          <t>A 47359-2024</t>
+          <t>A 30638-2026</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -17619,10 +17614,10 @@
         </is>
       </c>
       <c r="D194" s="1" t="n">
-        <v>45587</v>
+        <v>46211</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17635,7 +17630,7 @@
         </is>
       </c>
       <c r="I194" t="n">
-        <v>1.2</v>
+        <v>8</v>
       </c>
       <c r="J194" t="n">
         <v>0</v>
@@ -17678,7 +17673,7 @@
     <row r="195" ht="15" customHeight="1">
       <c r="A195" t="inlineStr">
         <is>
-          <t>A 31645-2024</t>
+          <t>A 10602-2022</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -17692,10 +17687,10 @@
         </is>
       </c>
       <c r="D195" s="1" t="n">
-        <v>45506</v>
+        <v>44624</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17707,13 +17702,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I195" t="n">
-        <v>11.1</v>
+        <v>7</v>
       </c>
       <c r="J195" t="n">
         <v>0</v>
@@ -17756,7 +17746,7 @@
     <row r="196" ht="15" customHeight="1">
       <c r="A196" t="inlineStr">
         <is>
-          <t>A 64359-2023</t>
+          <t>A 31088-2026</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -17770,10 +17760,10 @@
         </is>
       </c>
       <c r="D196" s="1" t="n">
-        <v>45280</v>
+        <v>46216</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17785,8 +17775,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Kommuner</t>
+        </is>
+      </c>
       <c r="I196" t="n">
-        <v>4.7</v>
+        <v>1.3</v>
       </c>
       <c r="J196" t="n">
         <v>0</v>
@@ -17829,7 +17824,7 @@
     <row r="197" ht="15" customHeight="1">
       <c r="A197" t="inlineStr">
         <is>
-          <t>A 58787-2021</t>
+          <t>A 31315-2026</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -17843,10 +17838,10 @@
         </is>
       </c>
       <c r="D197" s="1" t="n">
-        <v>44489</v>
+        <v>46219</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17859,7 +17854,7 @@
         </is>
       </c>
       <c r="I197" t="n">
-        <v>1.1</v>
+        <v>0.9</v>
       </c>
       <c r="J197" t="n">
         <v>0</v>
@@ -17902,7 +17897,7 @@
     <row r="198" ht="15" customHeight="1">
       <c r="A198" t="inlineStr">
         <is>
-          <t>A 24988-2023</t>
+          <t>A 37148-2026</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -17916,10 +17911,10 @@
         </is>
       </c>
       <c r="D198" s="1" t="n">
-        <v>45085</v>
+        <v>46274</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17931,13 +17926,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H198" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I198" t="n">
-        <v>1.9</v>
+        <v>0.4</v>
       </c>
       <c r="J198" t="n">
         <v>0</v>
@@ -17980,7 +17970,7 @@
     <row r="199" ht="15" customHeight="1">
       <c r="A199" t="inlineStr">
         <is>
-          <t>A 30638-2026</t>
+          <t>A 31613-2023</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -17990,14 +17980,14 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för att bevara och utveckla /försöksver</t>
         </is>
       </c>
       <c r="D199" s="1" t="n">
-        <v>46211</v>
+        <v>45117</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18010,7 +18000,7 @@
         </is>
       </c>
       <c r="I199" t="n">
-        <v>8</v>
+        <v>1.2</v>
       </c>
       <c r="J199" t="n">
         <v>0</v>
@@ -18053,7 +18043,7 @@
     <row r="200" ht="15" customHeight="1">
       <c r="A200" t="inlineStr">
         <is>
-          <t>A 31088-2026</t>
+          <t>A 37182-2026</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -18067,10 +18057,10 @@
         </is>
       </c>
       <c r="D200" s="1" t="n">
-        <v>46216</v>
+        <v>46274</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18082,13 +18072,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H200" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I200" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="J200" t="n">
         <v>0</v>
@@ -18131,7 +18116,7 @@
     <row r="201" ht="15" customHeight="1">
       <c r="A201" t="inlineStr">
         <is>
-          <t>A 31315-2026</t>
+          <t>A 6958-2024</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -18145,10 +18130,10 @@
         </is>
       </c>
       <c r="D201" s="1" t="n">
-        <v>46219</v>
+        <v>45343</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18161,7 +18146,7 @@
         </is>
       </c>
       <c r="I201" t="n">
-        <v>0.9</v>
+        <v>3.4</v>
       </c>
       <c r="J201" t="n">
         <v>0</v>
@@ -18204,7 +18189,7 @@
     <row r="202" ht="15" customHeight="1">
       <c r="A202" t="inlineStr">
         <is>
-          <t>A 36707-2026</t>
+          <t>A 47493-2024</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -18218,10 +18203,10 @@
         </is>
       </c>
       <c r="D202" s="1" t="n">
-        <v>46272</v>
+        <v>45587</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18233,8 +18218,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I202" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="J202" t="n">
         <v>0</v>
@@ -18277,7 +18267,7 @@
     <row r="203" ht="15" customHeight="1">
       <c r="A203" t="inlineStr">
         <is>
-          <t>A 13473-2024</t>
+          <t>A 34232-2023</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -18291,10 +18281,10 @@
         </is>
       </c>
       <c r="D203" s="1" t="n">
-        <v>45387</v>
+        <v>45127</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18306,8 +18296,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I203" t="n">
-        <v>1.8</v>
+        <v>5.8</v>
       </c>
       <c r="J203" t="n">
         <v>0</v>
@@ -18350,7 +18345,7 @@
     <row r="204" ht="15" customHeight="1">
       <c r="A204" t="inlineStr">
         <is>
-          <t>A 36808-2026</t>
+          <t>A 21027-2024</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -18364,10 +18359,10 @@
         </is>
       </c>
       <c r="D204" s="1" t="n">
-        <v>46272</v>
+        <v>45439</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18379,8 +18374,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I204" t="n">
-        <v>3.1</v>
+        <v>1.9</v>
       </c>
       <c r="J204" t="n">
         <v>0</v>
@@ -18423,7 +18423,7 @@
     <row r="205" ht="15" customHeight="1">
       <c r="A205" t="inlineStr">
         <is>
-          <t>A 37148-2026</t>
+          <t>A 21028-2024</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -18437,10 +18437,10 @@
         </is>
       </c>
       <c r="D205" s="1" t="n">
-        <v>46274</v>
+        <v>45439</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18452,8 +18452,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I205" t="n">
-        <v>0.4</v>
+        <v>1.6</v>
       </c>
       <c r="J205" t="n">
         <v>0</v>
@@ -18496,7 +18501,7 @@
     <row r="206" ht="15" customHeight="1">
       <c r="A206" t="inlineStr">
         <is>
-          <t>A 28133-2024</t>
+          <t>A 2612-2025</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -18506,14 +18511,14 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D206" s="1" t="n">
-        <v>45476</v>
+        <v>45674</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18569,7 +18574,7 @@
     <row r="207" ht="15" customHeight="1">
       <c r="A207" t="inlineStr">
         <is>
-          <t>A 37182-2026</t>
+          <t>A 32980-2023</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -18583,10 +18588,10 @@
         </is>
       </c>
       <c r="D207" s="1" t="n">
-        <v>46274</v>
+        <v>45125</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18599,7 +18604,7 @@
         </is>
       </c>
       <c r="I207" t="n">
-        <v>4</v>
+        <v>0.7</v>
       </c>
       <c r="J207" t="n">
         <v>0</v>
@@ -18642,7 +18647,7 @@
     <row r="208" ht="15" customHeight="1">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A 37744-2022</t>
+          <t>A 39529-2026</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -18656,10 +18661,10 @@
         </is>
       </c>
       <c r="D208" s="1" t="n">
-        <v>44810</v>
+        <v>46289</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18672,7 +18677,7 @@
         </is>
       </c>
       <c r="I208" t="n">
-        <v>1.1</v>
+        <v>3.3</v>
       </c>
       <c r="J208" t="n">
         <v>0</v>
@@ -18715,7 +18720,7 @@
     <row r="209" ht="15" customHeight="1">
       <c r="A209" t="inlineStr">
         <is>
-          <t>A 10602-2022</t>
+          <t>A 64036-2025</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -18729,10 +18734,10 @@
         </is>
       </c>
       <c r="D209" s="1" t="n">
-        <v>44624</v>
+        <v>46021</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18745,7 +18750,7 @@
         </is>
       </c>
       <c r="I209" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="J209" t="n">
         <v>0</v>
@@ -18788,7 +18793,7 @@
     <row r="210" ht="15" customHeight="1">
       <c r="A210" t="inlineStr">
         <is>
-          <t>A 11607-2023</t>
+          <t>A 31087-2026</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -18802,10 +18807,10 @@
         </is>
       </c>
       <c r="D210" s="1" t="n">
-        <v>44994</v>
+        <v>46216</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18819,11 +18824,11 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Övriga statliga verk och myndigheter</t>
+          <t>Kommuner</t>
         </is>
       </c>
       <c r="I210" t="n">
-        <v>1.1</v>
+        <v>1.5</v>
       </c>
       <c r="J210" t="n">
         <v>0</v>
@@ -18866,7 +18871,7 @@
     <row r="211" ht="15" customHeight="1">
       <c r="A211" t="inlineStr">
         <is>
-          <t>A 35504-2024</t>
+          <t>A 57751-2024</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -18880,10 +18885,10 @@
         </is>
       </c>
       <c r="D211" s="1" t="n">
-        <v>45531</v>
+        <v>45630</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18893,11 +18898,6 @@
       <c r="G211" t="inlineStr">
         <is>
           <t>HOFORS</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I211" t="n">
@@ -18944,7 +18944,7 @@
     <row r="212" ht="15" customHeight="1">
       <c r="A212" t="inlineStr">
         <is>
-          <t>A 68079-2021</t>
+          <t>A 35504-2024</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -18958,10 +18958,10 @@
         </is>
       </c>
       <c r="D212" s="1" t="n">
-        <v>44526</v>
+        <v>45531</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -18973,8 +18973,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I212" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="J212" t="n">
         <v>0</v>
@@ -19017,7 +19022,7 @@
     <row r="213" ht="15" customHeight="1">
       <c r="A213" t="inlineStr">
         <is>
-          <t>A 6958-2024</t>
+          <t>A 2915-2025</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -19031,10 +19036,10 @@
         </is>
       </c>
       <c r="D213" s="1" t="n">
-        <v>45343</v>
+        <v>45677</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19047,7 +19052,7 @@
         </is>
       </c>
       <c r="I213" t="n">
-        <v>3.4</v>
+        <v>1.9</v>
       </c>
       <c r="J213" t="n">
         <v>0</v>
@@ -19090,7 +19095,7 @@
     <row r="214" ht="15" customHeight="1">
       <c r="A214" t="inlineStr">
         <is>
-          <t>A 39529-2026</t>
+          <t>A 4032-2025</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -19100,14 +19105,14 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D214" s="1" t="n">
-        <v>46289</v>
+        <v>45684</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19120,7 +19125,7 @@
         </is>
       </c>
       <c r="I214" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="J214" t="n">
         <v>0</v>
@@ -19163,7 +19168,7 @@
     <row r="215" ht="15" customHeight="1">
       <c r="A215" t="inlineStr">
         <is>
-          <t>A 17185-2025</t>
+          <t>A 28391-2024</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -19177,10 +19182,10 @@
         </is>
       </c>
       <c r="D215" s="1" t="n">
-        <v>45755</v>
+        <v>45477</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19194,11 +19199,11 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Bergvik skog väst AB</t>
+          <t>Sveaskog</t>
         </is>
       </c>
       <c r="I215" t="n">
-        <v>10.3</v>
+        <v>2.7</v>
       </c>
       <c r="J215" t="n">
         <v>0</v>
@@ -19241,7 +19246,7 @@
     <row r="216" ht="15" customHeight="1">
       <c r="A216" t="inlineStr">
         <is>
-          <t>A 64036-2025</t>
+          <t>A 8321-2026</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -19255,10 +19260,10 @@
         </is>
       </c>
       <c r="D216" s="1" t="n">
-        <v>46021</v>
+        <v>46064</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19271,7 +19276,7 @@
         </is>
       </c>
       <c r="I216" t="n">
-        <v>2</v>
+        <v>0.9</v>
       </c>
       <c r="J216" t="n">
         <v>0</v>
@@ -19314,7 +19319,7 @@
     <row r="217" ht="15" customHeight="1">
       <c r="A217" t="inlineStr">
         <is>
-          <t>A 31087-2026</t>
+          <t>A 41210-2026</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -19328,10 +19333,10 @@
         </is>
       </c>
       <c r="D217" s="1" t="n">
-        <v>46216</v>
+        <v>46300</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19343,13 +19348,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>Kommuner</t>
-        </is>
-      </c>
       <c r="I217" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="J217" t="n">
         <v>0</v>
@@ -19392,7 +19392,7 @@
     <row r="218" ht="15" customHeight="1">
       <c r="A218" t="inlineStr">
         <is>
-          <t>A 31613-2023</t>
+          <t>A 21340-2025</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -19402,14 +19402,14 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Avverkning för att bevara och utveckla /försöksver</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D218" s="1" t="n">
-        <v>45117</v>
+        <v>45782</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="I218" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="J218" t="n">
         <v>0</v>
@@ -19465,7 +19465,7 @@
     <row r="219" ht="15" customHeight="1">
       <c r="A219" t="inlineStr">
         <is>
-          <t>A 54874-2025</t>
+          <t>A 19401-2026</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -19479,10 +19479,10 @@
         </is>
       </c>
       <c r="D219" s="1" t="n">
-        <v>45967</v>
+        <v>46133</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19494,8 +19494,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H219" t="inlineStr">
+        <is>
+          <t>Bergvik skog öst AB</t>
+        </is>
+      </c>
       <c r="I219" t="n">
-        <v>5.3</v>
+        <v>3.1</v>
       </c>
       <c r="J219" t="n">
         <v>0</v>
@@ -19538,7 +19543,7 @@
     <row r="220" ht="15" customHeight="1">
       <c r="A220" t="inlineStr">
         <is>
-          <t>A 8321-2026</t>
+          <t>A 1144-2024</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -19552,10 +19557,10 @@
         </is>
       </c>
       <c r="D220" s="1" t="n">
-        <v>46064</v>
+        <v>45302</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19611,7 +19616,7 @@
     <row r="221" ht="15" customHeight="1">
       <c r="A221" t="inlineStr">
         <is>
-          <t>A 54876-2025</t>
+          <t>A 41181-2026</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -19625,10 +19630,10 @@
         </is>
       </c>
       <c r="D221" s="1" t="n">
-        <v>45967</v>
+        <v>46300</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19641,7 +19646,7 @@
         </is>
       </c>
       <c r="I221" t="n">
-        <v>0.6</v>
+        <v>3.6</v>
       </c>
       <c r="J221" t="n">
         <v>0</v>
@@ -19684,7 +19689,7 @@
     <row r="222" ht="15" customHeight="1">
       <c r="A222" t="inlineStr">
         <is>
-          <t>A 54877-2025</t>
+          <t>A 54874-2025</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -19701,7 +19706,7 @@
         <v>45967</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19714,7 +19719,7 @@
         </is>
       </c>
       <c r="I222" t="n">
-        <v>0.9</v>
+        <v>5.3</v>
       </c>
       <c r="J222" t="n">
         <v>0</v>
@@ -19757,7 +19762,7 @@
     <row r="223" ht="15" customHeight="1">
       <c r="A223" t="inlineStr">
         <is>
-          <t>A 41181-2026</t>
+          <t>A 54876-2025</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -19771,10 +19776,10 @@
         </is>
       </c>
       <c r="D223" s="1" t="n">
-        <v>46300</v>
+        <v>45967</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19787,7 +19792,7 @@
         </is>
       </c>
       <c r="I223" t="n">
-        <v>3.6</v>
+        <v>0.6</v>
       </c>
       <c r="J223" t="n">
         <v>0</v>
@@ -19830,7 +19835,7 @@
     <row r="224" ht="15" customHeight="1">
       <c r="A224" t="inlineStr">
         <is>
-          <t>A 41210-2026</t>
+          <t>A 54877-2025</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -19844,10 +19849,10 @@
         </is>
       </c>
       <c r="D224" s="1" t="n">
-        <v>46300</v>
+        <v>45967</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19860,7 +19865,7 @@
         </is>
       </c>
       <c r="I224" t="n">
-        <v>2.2</v>
+        <v>0.9</v>
       </c>
       <c r="J224" t="n">
         <v>0</v>
@@ -19903,7 +19908,7 @@
     <row r="225" ht="15" customHeight="1">
       <c r="A225" t="inlineStr">
         <is>
-          <t>A 19401-2026</t>
+          <t>A 5554-2024</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -19917,10 +19922,10 @@
         </is>
       </c>
       <c r="D225" s="1" t="n">
-        <v>46133</v>
+        <v>45334</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -19932,13 +19937,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
       <c r="I225" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="J225" t="n">
         <v>0</v>
@@ -19981,7 +19981,7 @@
     <row r="226" ht="15" customHeight="1">
       <c r="A226" t="inlineStr">
         <is>
-          <t>A 1144-2024</t>
+          <t>A 34993-2026</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -19995,10 +19995,10 @@
         </is>
       </c>
       <c r="D226" s="1" t="n">
-        <v>45302</v>
+        <v>46259</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20010,8 +20010,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H226" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I226" t="n">
-        <v>0.9</v>
+        <v>6.7</v>
       </c>
       <c r="J226" t="n">
         <v>0</v>
@@ -20054,7 +20059,7 @@
     <row r="227" ht="15" customHeight="1">
       <c r="A227" t="inlineStr">
         <is>
-          <t>A 21340-2025</t>
+          <t>A 23666-2025</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -20068,10 +20073,10 @@
         </is>
       </c>
       <c r="D227" s="1" t="n">
-        <v>45782</v>
+        <v>45792</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20084,7 +20089,7 @@
         </is>
       </c>
       <c r="I227" t="n">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="J227" t="n">
         <v>0</v>
@@ -20127,7 +20132,7 @@
     <row r="228" ht="15" customHeight="1">
       <c r="A228" t="inlineStr">
         <is>
-          <t>A 5554-2024</t>
+          <t>A 53517-2024</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -20141,10 +20146,10 @@
         </is>
       </c>
       <c r="D228" s="1" t="n">
-        <v>45334</v>
+        <v>45614</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20200,7 +20205,7 @@
     <row r="229" ht="15" customHeight="1">
       <c r="A229" t="inlineStr">
         <is>
-          <t>A 34993-2026</t>
+          <t>A 33981-2024</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -20214,10 +20219,10 @@
         </is>
       </c>
       <c r="D229" s="1" t="n">
-        <v>46259</v>
+        <v>45523</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20229,13 +20234,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>Sveaskog</t>
-        </is>
-      </c>
       <c r="I229" t="n">
-        <v>6.7</v>
+        <v>2.3</v>
       </c>
       <c r="J229" t="n">
         <v>0</v>
@@ -20295,7 +20295,7 @@
         <v>46260</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20356,7 +20356,7 @@
     <row r="231" ht="15" customHeight="1">
       <c r="A231" t="inlineStr">
         <is>
-          <t>A 34980-2026</t>
+          <t>A 24258-2026</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -20370,10 +20370,10 @@
         </is>
       </c>
       <c r="D231" s="1" t="n">
-        <v>46259</v>
+        <v>46169</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20385,13 +20385,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H231" t="inlineStr">
-        <is>
-          <t>Övriga statliga verk och myndigheter</t>
-        </is>
-      </c>
       <c r="I231" t="n">
-        <v>1.7</v>
+        <v>2.9</v>
       </c>
       <c r="J231" t="n">
         <v>0</v>
@@ -20434,7 +20429,7 @@
     <row r="232" ht="15" customHeight="1">
       <c r="A232" t="inlineStr">
         <is>
-          <t>A 23666-2025</t>
+          <t>A 26302-2025</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -20444,14 +20439,14 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Avverkning för annat ändamål</t>
         </is>
       </c>
       <c r="D232" s="1" t="n">
-        <v>45792</v>
+        <v>45805</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20464,7 +20459,7 @@
         </is>
       </c>
       <c r="I232" t="n">
-        <v>0.4</v>
+        <v>5.3</v>
       </c>
       <c r="J232" t="n">
         <v>0</v>
@@ -20507,7 +20502,7 @@
     <row r="233" ht="15" customHeight="1">
       <c r="A233" t="inlineStr">
         <is>
-          <t>A 24258-2026</t>
+          <t>A 31471-2025</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -20521,10 +20516,10 @@
         </is>
       </c>
       <c r="D233" s="1" t="n">
-        <v>46169</v>
+        <v>45833</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20537,7 +20532,7 @@
         </is>
       </c>
       <c r="I233" t="n">
-        <v>2.9</v>
+        <v>1.6</v>
       </c>
       <c r="J233" t="n">
         <v>0</v>
@@ -20580,7 +20575,7 @@
     <row r="234" ht="15" customHeight="1">
       <c r="A234" t="inlineStr">
         <is>
-          <t>A 33981-2024</t>
+          <t>A 32299-2025</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -20594,10 +20589,10 @@
         </is>
       </c>
       <c r="D234" s="1" t="n">
-        <v>45523</v>
+        <v>45835</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20609,8 +20604,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H234" t="inlineStr">
+        <is>
+          <t>Bergvik skog väst AB</t>
+        </is>
+      </c>
       <c r="I234" t="n">
-        <v>2.3</v>
+        <v>12.8</v>
       </c>
       <c r="J234" t="n">
         <v>0</v>
@@ -20653,7 +20653,7 @@
     <row r="235" ht="15" customHeight="1">
       <c r="A235" t="inlineStr">
         <is>
-          <t>A 53517-2024</t>
+          <t>A 36278-2026</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -20667,10 +20667,10 @@
         </is>
       </c>
       <c r="D235" s="1" t="n">
-        <v>45614</v>
+        <v>46268</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20683,7 +20683,7 @@
         </is>
       </c>
       <c r="I235" t="n">
-        <v>1</v>
+        <v>2.8</v>
       </c>
       <c r="J235" t="n">
         <v>0</v>
@@ -20726,7 +20726,7 @@
     <row r="236" ht="15" customHeight="1">
       <c r="A236" t="inlineStr">
         <is>
-          <t>A 26302-2025</t>
+          <t>A 36707-2026</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -20736,14 +20736,14 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Avverkning för annat ändamål</t>
+          <t>Föryngringsavverkning</t>
         </is>
       </c>
       <c r="D236" s="1" t="n">
-        <v>45805</v>
+        <v>46272</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20756,7 +20756,7 @@
         </is>
       </c>
       <c r="I236" t="n">
-        <v>5.3</v>
+        <v>3.3</v>
       </c>
       <c r="J236" t="n">
         <v>0</v>
@@ -20799,7 +20799,7 @@
     <row r="237" ht="15" customHeight="1">
       <c r="A237" t="inlineStr">
         <is>
-          <t>A 36278-2026</t>
+          <t>A 34980-2026</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -20813,10 +20813,10 @@
         </is>
       </c>
       <c r="D237" s="1" t="n">
-        <v>46268</v>
+        <v>46259</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20828,8 +20828,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>Övriga statliga verk och myndigheter</t>
+        </is>
+      </c>
       <c r="I237" t="n">
-        <v>2.8</v>
+        <v>1.7</v>
       </c>
       <c r="J237" t="n">
         <v>0</v>
@@ -20872,7 +20877,7 @@
     <row r="238" ht="15" customHeight="1">
       <c r="A238" t="inlineStr">
         <is>
-          <t>A 31471-2025</t>
+          <t>A 36808-2026</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -20886,10 +20891,10 @@
         </is>
       </c>
       <c r="D238" s="1" t="n">
-        <v>45833</v>
+        <v>46272</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20902,7 +20907,7 @@
         </is>
       </c>
       <c r="I238" t="n">
-        <v>1.6</v>
+        <v>3.1</v>
       </c>
       <c r="J238" t="n">
         <v>0</v>
@@ -20945,7 +20950,7 @@
     <row r="239" ht="15" customHeight="1">
       <c r="A239" t="inlineStr">
         <is>
-          <t>A 32299-2025</t>
+          <t>A 36349-2025</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -20959,10 +20964,10 @@
         </is>
       </c>
       <c r="D239" s="1" t="n">
-        <v>45835</v>
+        <v>45868</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -20974,13 +20979,8 @@
           <t>HOFORS</t>
         </is>
       </c>
-      <c r="H239" t="inlineStr">
-        <is>
-          <t>Bergvik skog väst AB</t>
-        </is>
-      </c>
       <c r="I239" t="n">
-        <v>12.8</v>
+        <v>2.7</v>
       </c>
       <c r="J239" t="n">
         <v>0</v>
@@ -21023,7 +21023,7 @@
     <row r="240" ht="15" customHeight="1">
       <c r="A240" t="inlineStr">
         <is>
-          <t>A 36349-2025</t>
+          <t>A 37444-2025</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -21037,10 +21037,10 @@
         </is>
       </c>
       <c r="D240" s="1" t="n">
-        <v>45868</v>
+        <v>45877</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21052,8 +21052,13 @@
           <t>HOFORS</t>
         </is>
       </c>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>Sveaskog</t>
+        </is>
+      </c>
       <c r="I240" t="n">
-        <v>2.7</v>
+        <v>4.8</v>
       </c>
       <c r="J240" t="n">
         <v>0</v>
@@ -21096,24 +21101,24 @@
     <row r="241" ht="15" customHeight="1">
       <c r="A241" t="inlineStr">
         <is>
-          <t>A 37444-2025</t>
+          <t>S 430-2025</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>avverkningsanmälan</t>
+          <t>samrådsanmälan</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Föryngringsavverkning</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D241" s="1" t="n">
-        <v>45877</v>
+        <v>45700</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21131,7 +21136,7 @@
         </is>
       </c>
       <c r="I241" t="n">
-        <v>4.8</v>
+        <v>25.6</v>
       </c>
       <c r="J241" t="n">
         <v>0</v>
@@ -21174,7 +21179,7 @@
     <row r="242" ht="15" customHeight="1">
       <c r="A242" t="inlineStr">
         <is>
-          <t>S 430-2025</t>
+          <t>S 209-2024</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -21188,10 +21193,10 @@
         </is>
       </c>
       <c r="D242" s="1" t="n">
-        <v>45700</v>
+        <v>45316</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21209,7 +21214,7 @@
         </is>
       </c>
       <c r="I242" t="n">
-        <v>25.6</v>
+        <v>59.8</v>
       </c>
       <c r="J242" t="n">
         <v>0</v>
@@ -21252,7 +21257,7 @@
     <row r="243" ht="15" customHeight="1">
       <c r="A243" t="inlineStr">
         <is>
-          <t>S 209-2024</t>
+          <t>S 239-2024</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -21266,10 +21271,10 @@
         </is>
       </c>
       <c r="D243" s="1" t="n">
-        <v>45316</v>
+        <v>45319</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21287,7 +21292,7 @@
         </is>
       </c>
       <c r="I243" t="n">
-        <v>59.8</v>
+        <v>42.3</v>
       </c>
       <c r="J243" t="n">
         <v>0</v>
@@ -21330,7 +21335,7 @@
     <row r="244" ht="15" customHeight="1">
       <c r="A244" t="inlineStr">
         <is>
-          <t>S 239-2024</t>
+          <t>S 1334-2025</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -21340,14 +21345,14 @@
       </c>
       <c r="C244" t="inlineStr">
         <is>
-          <t>Skogsgödsling</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D244" s="1" t="n">
-        <v>45319</v>
+        <v>45771</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21365,7 +21370,7 @@
         </is>
       </c>
       <c r="I244" t="n">
-        <v>42.3</v>
+        <v>5.6</v>
       </c>
       <c r="J244" t="n">
         <v>0</v>
@@ -21408,7 +21413,7 @@
     <row r="245" ht="15" customHeight="1">
       <c r="A245" t="inlineStr">
         <is>
-          <t>S 1334-2025</t>
+          <t>S 532-2025</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -21418,14 +21423,14 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Askåterföring</t>
         </is>
       </c>
       <c r="D245" s="1" t="n">
-        <v>45771</v>
+        <v>45707</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21443,7 +21448,7 @@
         </is>
       </c>
       <c r="I245" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="J245" t="n">
         <v>0</v>
@@ -21486,7 +21491,7 @@
     <row r="246" ht="15" customHeight="1">
       <c r="A246" t="inlineStr">
         <is>
-          <t>S 532-2025</t>
+          <t>S 2403-2025</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -21496,14 +21501,14 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Askåterföring</t>
+          <t>Annan skogsbruksåtgärd</t>
         </is>
       </c>
       <c r="D246" s="1" t="n">
-        <v>45707</v>
+        <v>45895</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21521,7 +21526,7 @@
         </is>
       </c>
       <c r="I246" t="n">
-        <v>4.8</v>
+        <v>2.2</v>
       </c>
       <c r="J246" t="n">
         <v>0</v>
@@ -21564,7 +21569,7 @@
     <row r="247" ht="15" customHeight="1">
       <c r="A247" t="inlineStr">
         <is>
-          <t>S 2403-2025</t>
+          <t>S 428-2026</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -21574,14 +21579,14 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Annan skogsbruksåtgärd</t>
+          <t>Skogsgödsling</t>
         </is>
       </c>
       <c r="D247" s="1" t="n">
-        <v>45895</v>
+        <v>46069</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
@@ -21599,7 +21604,7 @@
         </is>
       </c>
       <c r="I247" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="J247" t="n">
         <v>0</v>
@@ -21639,10 +21644,10 @@
       </c>
       <c r="V247" s="2" t="inlineStr"/>
     </row>
-    <row r="248" ht="15" customHeight="1">
+    <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>S 428-2026</t>
+          <t>S 647-2026</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -21656,10 +21661,10 @@
         </is>
       </c>
       <c r="D248" s="1" t="n">
-        <v>46069</v>
+        <v>46089</v>
       </c>
       <c r="E248" s="1" t="n">
-        <v>46314</v>
+        <v>46315</v>
       </c>
       <c r="F248" t="inlineStr">
         <is>
@@ -21673,11 +21678,11 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>Sveaskog</t>
+          <t>Bergvik skog öst AB</t>
         </is>
       </c>
       <c r="I248" t="n">
-        <v>2.7</v>
+        <v>12.4</v>
       </c>
       <c r="J248" t="n">
         <v>0</v>
@@ -21716,84 +21721,6 @@
         <v>0</v>
       </c>
       <c r="V248" s="2" t="inlineStr"/>
-    </row>
-    <row r="249">
-      <c r="A249" t="inlineStr">
-        <is>
-          <t>S 647-2026</t>
-        </is>
-      </c>
-      <c r="B249" t="inlineStr">
-        <is>
-          <t>samrådsanmälan</t>
-        </is>
-      </c>
-      <c r="C249" t="inlineStr">
-        <is>
-          <t>Skogsgödsling</t>
-        </is>
-      </c>
-      <c r="D249" s="1" t="n">
-        <v>46089</v>
-      </c>
-      <c r="E249" s="1" t="n">
-        <v>46314</v>
-      </c>
-      <c r="F249" t="inlineStr">
-        <is>
-          <t>GÄVLEBORGS LÄN</t>
-        </is>
-      </c>
-      <c r="G249" t="inlineStr">
-        <is>
-          <t>HOFORS</t>
-        </is>
-      </c>
-      <c r="H249" t="inlineStr">
-        <is>
-          <t>Bergvik skog öst AB</t>
-        </is>
-      </c>
-      <c r="I249" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="J249" t="n">
-        <v>0</v>
-      </c>
-      <c r="K249" t="n">
-        <v>0</v>
-      </c>
-      <c r="L249" t="n">
-        <v>0</v>
-      </c>
-      <c r="M249" t="n">
-        <v>0</v>
-      </c>
-      <c r="N249" t="n">
-        <v>0</v>
-      </c>
-      <c r="O249" t="n">
-        <v>0</v>
-      </c>
-      <c r="P249" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q249" t="n">
-        <v>0</v>
-      </c>
-      <c r="R249" t="n">
-        <v>0</v>
-      </c>
-      <c r="S249" t="n">
-        <v>0</v>
-      </c>
-      <c r="T249" t="n">
-        <v>0</v>
-      </c>
-      <c r="U249" t="n">
-        <v>0</v>
-      </c>
-      <c r="V249" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt HOFORS.xlsx
+++ b/Översikt HOFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46064</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>45784</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>46164</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45299</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>46079</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>46163</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>46085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>46266</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45316</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45163</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45813</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>44623</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>45860</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>46199</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44816</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45935</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>45895</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>45895</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>46177</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>46025</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>46043</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45813</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>46199</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>46095</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>45874</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>46154</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44102</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44169</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>44585</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>45317</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45701</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>45895</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45895</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>46142</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>46125</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>44649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>44559</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>44928</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>45531</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>45917</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>46183</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>46196</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>45127</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>46217</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>46217</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>45813</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>45813</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>45813</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>45813</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         <v>46252</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>45924</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>46091</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>45860</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>45870</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>45874</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>46262</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         <v>45881</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>45488</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>45007</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>45348</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>45589</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>45453</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45477</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45531</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>45597</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>44624</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>45477</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>45701</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>45727</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45706</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44868</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44582</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>44501</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>44512</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>44873</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44692</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>44868</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>45887</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>45188</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>45376</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>45387</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>45587</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>45895</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>45884</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45531</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>44624</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>46162</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>46162</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>45917</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>46167</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>45117</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>46169</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>45930</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>45929</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>45343</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>45933</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>45935</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
         <v>45933</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>45816</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>45933</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>45933</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>45453</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>45446</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>45587</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>45127</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>44810</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>45947</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45439</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>45439</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>45674</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>46183</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>46183</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>45125</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>45956</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>45966</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>45969</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>45969</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>46196</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>46196</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>46199</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>45980</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>45980</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>45980</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>45630</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>45980</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>45531</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>45986</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>45490</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>45677</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>45986</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>46211</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>45684</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>46216</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>46000</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>45477</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>46219</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>46002</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>45782</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>45302</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>45334</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>46029</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>46030</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         <v>46029</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         <v>46036</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>45271</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>46037</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>45792</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>46042</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>45614</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>45523</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>46050</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>46289</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>46061</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>46021</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>46216</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>46047</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>45805</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>46083</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>46064</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>46300</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>45833</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>46133</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>45835</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>46300</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>45967</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>45967</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>45967</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>46092</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>46107</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45173</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>46259</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>46115</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>45868</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>46085</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>46091</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>46260</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>45877</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         <v>46169</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
         <v>45488</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>45488</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>45387</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>45343</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16935,7 +16935,7 @@
         <v>46085</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>45506</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>46080</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>45912</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>46268</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>46259</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>46105</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>45463</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>46113</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>45232</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>46272</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>46272</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>45069</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>46274</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>46092</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>44671</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>45629</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         <v>46274</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         <v>45587</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18362,7 +18362,7 @@
         <v>45453</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>46042</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>46042</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>45792</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>44967</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>44994</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>45728</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>44810</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>45219</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>45755</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>44810</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>45476</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>45523</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>45523</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>45538</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>44986</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>45117</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44977</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>45475</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>45117</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>45007</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>45085</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>45145</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>45159</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>45156</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>45531</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>45709</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>44680</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>45127</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>45755</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
         <v>45252</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20680,7 +20680,7 @@
         <v>45280</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>45250</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20826,7 +20826,7 @@
         <v>44812</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>45202</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>44526</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         <v>45700</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>45316</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45319</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>45771</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45707</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>45895</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>46069</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21591,7 +21591,7 @@
         <v>46089</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46319</v>
+        <v>46320</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>

--- a/Översikt HOFORS.xlsx
+++ b/Översikt HOFORS.xlsx
@@ -601,7 +601,7 @@
         <v>46064</v>
       </c>
       <c r="E2" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -738,7 +738,7 @@
         <v>45784</v>
       </c>
       <c r="E3" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -868,7 +868,7 @@
         <v>46164</v>
       </c>
       <c r="E4" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
         <v>45299</v>
       </c>
       <c r="E5" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
         <v>46079</v>
       </c>
       <c r="E6" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -1220,7 +1220,7 @@
         <v>46163</v>
       </c>
       <c r="E7" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>46085</v>
       </c>
       <c r="E8" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -1453,7 +1453,7 @@
         <v>46266</v>
       </c>
       <c r="E9" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -1569,7 +1569,7 @@
         <v>45316</v>
       </c>
       <c r="E10" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -1684,7 +1684,7 @@
         <v>45163</v>
       </c>
       <c r="E11" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -1802,7 +1802,7 @@
         <v>45813</v>
       </c>
       <c r="E12" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>44623</v>
       </c>
       <c r="E13" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -2031,7 +2031,7 @@
         <v>45860</v>
       </c>
       <c r="E14" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -2147,7 +2147,7 @@
         <v>46199</v>
       </c>
       <c r="E15" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -2263,7 +2263,7 @@
         <v>44816</v>
       </c>
       <c r="E16" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>45935</v>
       </c>
       <c r="E17" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         <v>45895</v>
       </c>
       <c r="E18" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -2595,7 +2595,7 @@
         <v>45895</v>
       </c>
       <c r="E19" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -2706,7 +2706,7 @@
         <v>46177</v>
       </c>
       <c r="E20" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>46025</v>
       </c>
       <c r="E21" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -2927,7 +2927,7 @@
         <v>46043</v>
       </c>
       <c r="E22" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -3038,7 +3038,7 @@
         <v>45813</v>
       </c>
       <c r="E23" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -3149,7 +3149,7 @@
         <v>46199</v>
       </c>
       <c r="E24" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -3264,7 +3264,7 @@
         <v>46095</v>
       </c>
       <c r="E25" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
@@ -3370,7 +3370,7 @@
         <v>45874</v>
       </c>
       <c r="E26" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>46154</v>
       </c>
       <c r="E27" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -3595,7 +3595,7 @@
         <v>44102</v>
       </c>
       <c r="E28" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
         <v>44169</v>
       </c>
       <c r="E29" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>44585</v>
       </c>
       <c r="E30" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
@@ -3928,7 +3928,7 @@
         <v>45317</v>
       </c>
       <c r="E31" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
@@ -4039,7 +4039,7 @@
         <v>45701</v>
       </c>
       <c r="E32" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
@@ -4150,7 +4150,7 @@
         <v>45895</v>
       </c>
       <c r="E33" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -4261,7 +4261,7 @@
         <v>45895</v>
       </c>
       <c r="E34" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -4372,7 +4372,7 @@
         <v>46142</v>
       </c>
       <c r="E35" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -4483,7 +4483,7 @@
         <v>46125</v>
       </c>
       <c r="E36" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -4594,7 +4594,7 @@
         <v>44649</v>
       </c>
       <c r="E37" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
@@ -4699,7 +4699,7 @@
         <v>44511</v>
       </c>
       <c r="E38" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>44559</v>
       </c>
       <c r="E39" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>44928</v>
       </c>
       <c r="E40" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
@@ -5028,7 +5028,7 @@
         <v>45531</v>
       </c>
       <c r="E41" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -5142,7 +5142,7 @@
         <v>45917</v>
       </c>
       <c r="E42" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -5252,7 +5252,7 @@
         <v>46183</v>
       </c>
       <c r="E43" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -5362,7 +5362,7 @@
         <v>46196</v>
       </c>
       <c r="E44" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -5472,7 +5472,7 @@
         <v>45127</v>
       </c>
       <c r="E45" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -5582,7 +5582,7 @@
         <v>46217</v>
       </c>
       <c r="E46" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -5692,7 +5692,7 @@
         <v>46217</v>
       </c>
       <c r="E47" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
@@ -5802,7 +5802,7 @@
         <v>45813</v>
       </c>
       <c r="E48" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
@@ -5912,7 +5912,7 @@
         <v>45813</v>
       </c>
       <c r="E49" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
@@ -6022,7 +6022,7 @@
         <v>45813</v>
       </c>
       <c r="E50" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
@@ -6132,7 +6132,7 @@
         <v>45813</v>
       </c>
       <c r="E51" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -6242,7 +6242,7 @@
         <v>46252</v>
       </c>
       <c r="E52" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
@@ -6356,7 +6356,7 @@
         <v>45924</v>
       </c>
       <c r="E53" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
@@ -6466,7 +6466,7 @@
         <v>46091</v>
       </c>
       <c r="E54" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>45860</v>
       </c>
       <c r="E55" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>45870</v>
       </c>
       <c r="E56" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>45874</v>
       </c>
       <c r="E57" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -6905,7 +6905,7 @@
         <v>46262</v>
       </c>
       <c r="E58" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         <v>45881</v>
       </c>
       <c r="E59" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
@@ -7125,7 +7125,7 @@
         <v>45488</v>
       </c>
       <c r="E60" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -7235,7 +7235,7 @@
         <v>45007</v>
       </c>
       <c r="E61" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
@@ -7345,7 +7345,7 @@
         <v>45348</v>
       </c>
       <c r="E62" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
@@ -7450,7 +7450,7 @@
         <v>45589</v>
       </c>
       <c r="E63" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
@@ -7555,7 +7555,7 @@
         <v>45453</v>
       </c>
       <c r="E64" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
@@ -7665,7 +7665,7 @@
         <v>45477</v>
       </c>
       <c r="E65" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -7775,7 +7775,7 @@
         <v>45531</v>
       </c>
       <c r="E66" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -7885,7 +7885,7 @@
         <v>45597</v>
       </c>
       <c r="E67" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -7990,7 +7990,7 @@
         <v>44624</v>
       </c>
       <c r="E68" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -8095,7 +8095,7 @@
         <v>45477</v>
       </c>
       <c r="E69" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         <v>45701</v>
       </c>
       <c r="E70" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
@@ -8315,7 +8315,7 @@
         <v>45727</v>
       </c>
       <c r="E71" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
@@ -8429,7 +8429,7 @@
         <v>45706</v>
       </c>
       <c r="E72" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
@@ -8539,7 +8539,7 @@
         <v>44868</v>
       </c>
       <c r="E73" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         <v>44582</v>
       </c>
       <c r="E74" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
         <v>44501</v>
       </c>
       <c r="E75" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -8763,7 +8763,7 @@
         <v>44512</v>
       </c>
       <c r="E76" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>44873</v>
       </c>
       <c r="E77" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
@@ -8909,7 +8909,7 @@
         <v>44692</v>
       </c>
       <c r="E78" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
@@ -8982,7 +8982,7 @@
         <v>44868</v>
       </c>
       <c r="E79" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -9060,7 +9060,7 @@
         <v>45887</v>
       </c>
       <c r="E80" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
@@ -9138,7 +9138,7 @@
         <v>45188</v>
       </c>
       <c r="E81" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -9211,7 +9211,7 @@
         <v>45376</v>
       </c>
       <c r="E82" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -9284,7 +9284,7 @@
         <v>45387</v>
       </c>
       <c r="E83" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -9357,7 +9357,7 @@
         <v>45587</v>
       </c>
       <c r="E84" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -9435,7 +9435,7 @@
         <v>45895</v>
       </c>
       <c r="E85" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>45884</v>
       </c>
       <c r="E86" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
         <v>45531</v>
       </c>
       <c r="E87" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>44624</v>
       </c>
       <c r="E88" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
@@ -9737,7 +9737,7 @@
         <v>46162</v>
       </c>
       <c r="E89" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>46162</v>
       </c>
       <c r="E90" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -9893,7 +9893,7 @@
         <v>45917</v>
       </c>
       <c r="E91" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -9971,7 +9971,7 @@
         <v>46167</v>
       </c>
       <c r="E92" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
@@ -10049,7 +10049,7 @@
         <v>45117</v>
       </c>
       <c r="E93" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
@@ -10122,7 +10122,7 @@
         <v>46169</v>
       </c>
       <c r="E94" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
@@ -10200,7 +10200,7 @@
         <v>45930</v>
       </c>
       <c r="E95" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
@@ -10273,7 +10273,7 @@
         <v>45929</v>
       </c>
       <c r="E96" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
@@ -10346,7 +10346,7 @@
         <v>45343</v>
       </c>
       <c r="E97" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -10419,7 +10419,7 @@
         <v>45933</v>
       </c>
       <c r="E98" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>45935</v>
       </c>
       <c r="E99" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
@@ -10575,7 +10575,7 @@
         <v>45933</v>
       </c>
       <c r="E100" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
@@ -10653,7 +10653,7 @@
         <v>45816</v>
       </c>
       <c r="E101" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
@@ -10731,7 +10731,7 @@
         <v>45933</v>
       </c>
       <c r="E102" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -10809,7 +10809,7 @@
         <v>45933</v>
       </c>
       <c r="E103" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -10887,7 +10887,7 @@
         <v>45453</v>
       </c>
       <c r="E104" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
@@ -10965,7 +10965,7 @@
         <v>45446</v>
       </c>
       <c r="E105" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -11038,7 +11038,7 @@
         <v>45587</v>
       </c>
       <c r="E106" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -11116,7 +11116,7 @@
         <v>45127</v>
       </c>
       <c r="E107" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>44810</v>
       </c>
       <c r="E108" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>45947</v>
       </c>
       <c r="E109" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -11345,7 +11345,7 @@
         <v>45439</v>
       </c>
       <c r="E110" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -11423,7 +11423,7 @@
         <v>45439</v>
       </c>
       <c r="E111" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>45674</v>
       </c>
       <c r="E112" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -11574,7 +11574,7 @@
         <v>46183</v>
       </c>
       <c r="E113" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -11652,7 +11652,7 @@
         <v>46183</v>
       </c>
       <c r="E114" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -11730,7 +11730,7 @@
         <v>45125</v>
       </c>
       <c r="E115" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -11803,7 +11803,7 @@
         <v>45956</v>
       </c>
       <c r="E116" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -11876,7 +11876,7 @@
         <v>45966</v>
       </c>
       <c r="E117" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>45969</v>
       </c>
       <c r="E118" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -12022,7 +12022,7 @@
         <v>45969</v>
       </c>
       <c r="E119" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>46196</v>
       </c>
       <c r="E120" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
@@ -12173,7 +12173,7 @@
         <v>46196</v>
       </c>
       <c r="E121" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -12251,7 +12251,7 @@
         <v>46199</v>
       </c>
       <c r="E122" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
@@ -12329,7 +12329,7 @@
         <v>45980</v>
       </c>
       <c r="E123" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
@@ -12402,7 +12402,7 @@
         <v>45980</v>
       </c>
       <c r="E124" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
@@ -12475,7 +12475,7 @@
         <v>45980</v>
       </c>
       <c r="E125" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
@@ -12548,7 +12548,7 @@
         <v>45630</v>
       </c>
       <c r="E126" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>45980</v>
       </c>
       <c r="E127" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
@@ -12694,7 +12694,7 @@
         <v>45531</v>
       </c>
       <c r="E128" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>45986</v>
       </c>
       <c r="E129" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
@@ -12845,7 +12845,7 @@
         <v>45490</v>
       </c>
       <c r="E130" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
         <v>45677</v>
       </c>
       <c r="E131" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
@@ -12996,7 +12996,7 @@
         <v>45986</v>
       </c>
       <c r="E132" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
@@ -13069,7 +13069,7 @@
         <v>46211</v>
       </c>
       <c r="E133" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
@@ -13142,7 +13142,7 @@
         <v>45684</v>
       </c>
       <c r="E134" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
@@ -13215,7 +13215,7 @@
         <v>46216</v>
       </c>
       <c r="E135" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
@@ -13293,7 +13293,7 @@
         <v>46000</v>
       </c>
       <c r="E136" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
@@ -13366,7 +13366,7 @@
         <v>45477</v>
       </c>
       <c r="E137" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>46219</v>
       </c>
       <c r="E138" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -13517,7 +13517,7 @@
         <v>46002</v>
       </c>
       <c r="E139" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
@@ -13590,7 +13590,7 @@
         <v>45782</v>
       </c>
       <c r="E140" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
@@ -13663,7 +13663,7 @@
         <v>45302</v>
       </c>
       <c r="E141" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
@@ -13736,7 +13736,7 @@
         <v>45334</v>
       </c>
       <c r="E142" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -13809,7 +13809,7 @@
         <v>46029</v>
       </c>
       <c r="E143" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -13882,7 +13882,7 @@
         <v>46030</v>
       </c>
       <c r="E144" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
@@ -13955,7 +13955,7 @@
         <v>46029</v>
       </c>
       <c r="E145" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -14028,7 +14028,7 @@
         <v>46036</v>
       </c>
       <c r="E146" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>45271</v>
       </c>
       <c r="E147" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -14174,7 +14174,7 @@
         <v>46037</v>
       </c>
       <c r="E148" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>45792</v>
       </c>
       <c r="E149" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
@@ -14320,7 +14320,7 @@
         <v>46042</v>
       </c>
       <c r="E150" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
@@ -14393,7 +14393,7 @@
         <v>45614</v>
       </c>
       <c r="E151" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
@@ -14466,7 +14466,7 @@
         <v>45523</v>
       </c>
       <c r="E152" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
         <v>46050</v>
       </c>
       <c r="E153" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
@@ -14612,7 +14612,7 @@
         <v>46289</v>
       </c>
       <c r="E154" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
@@ -14685,7 +14685,7 @@
         <v>46061</v>
       </c>
       <c r="E155" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
@@ -14758,7 +14758,7 @@
         <v>46021</v>
       </c>
       <c r="E156" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
@@ -14831,7 +14831,7 @@
         <v>46216</v>
       </c>
       <c r="E157" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
@@ -14909,7 +14909,7 @@
         <v>46047</v>
       </c>
       <c r="E158" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
@@ -14982,7 +14982,7 @@
         <v>45805</v>
       </c>
       <c r="E159" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>46083</v>
       </c>
       <c r="E160" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
@@ -15128,7 +15128,7 @@
         <v>46064</v>
       </c>
       <c r="E161" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
@@ -15201,7 +15201,7 @@
         <v>46300</v>
       </c>
       <c r="E162" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>45833</v>
       </c>
       <c r="E163" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
@@ -15347,7 +15347,7 @@
         <v>46133</v>
       </c>
       <c r="E164" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
@@ -15425,7 +15425,7 @@
         <v>45835</v>
       </c>
       <c r="E165" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -15503,7 +15503,7 @@
         <v>46300</v>
       </c>
       <c r="E166" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -15576,7 +15576,7 @@
         <v>45967</v>
       </c>
       <c r="E167" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -15649,7 +15649,7 @@
         <v>45967</v>
       </c>
       <c r="E168" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>45967</v>
       </c>
       <c r="E169" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -15795,7 +15795,7 @@
         <v>46092</v>
       </c>
       <c r="E170" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>46107</v>
       </c>
       <c r="E171" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -15951,7 +15951,7 @@
         <v>45173</v>
       </c>
       <c r="E172" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -16029,7 +16029,7 @@
         <v>46259</v>
       </c>
       <c r="E173" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -16107,7 +16107,7 @@
         <v>46115</v>
       </c>
       <c r="E174" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -16180,7 +16180,7 @@
         <v>45868</v>
       </c>
       <c r="E175" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -16253,7 +16253,7 @@
         <v>46085</v>
       </c>
       <c r="E176" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -16326,7 +16326,7 @@
         <v>46091</v>
       </c>
       <c r="E177" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -16404,7 +16404,7 @@
         <v>46260</v>
       </c>
       <c r="E178" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>45877</v>
       </c>
       <c r="E179" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F179" t="inlineStr">
         <is>
@@ -16560,7 +16560,7 @@
         <v>46169</v>
       </c>
       <c r="E180" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -16633,7 +16633,7 @@
         <v>45488</v>
       </c>
       <c r="E181" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F181" t="inlineStr">
         <is>
@@ -16711,7 +16711,7 @@
         <v>45488</v>
       </c>
       <c r="E182" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
@@ -16789,7 +16789,7 @@
         <v>45387</v>
       </c>
       <c r="E183" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F183" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>45343</v>
       </c>
       <c r="E184" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F184" t="inlineStr">
         <is>
@@ -16935,7 +16935,7 @@
         <v>46085</v>
       </c>
       <c r="E185" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
@@ -17008,7 +17008,7 @@
         <v>45506</v>
       </c>
       <c r="E186" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
@@ -17086,7 +17086,7 @@
         <v>46080</v>
       </c>
       <c r="E187" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
@@ -17164,7 +17164,7 @@
         <v>45912</v>
       </c>
       <c r="E188" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F188" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>46268</v>
       </c>
       <c r="E189" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F189" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>46259</v>
       </c>
       <c r="E190" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F190" t="inlineStr">
         <is>
@@ -17393,7 +17393,7 @@
         <v>46105</v>
       </c>
       <c r="E191" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F191" t="inlineStr">
         <is>
@@ -17471,7 +17471,7 @@
         <v>45463</v>
       </c>
       <c r="E192" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F192" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>46113</v>
       </c>
       <c r="E193" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F193" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>45232</v>
       </c>
       <c r="E194" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F194" t="inlineStr">
         <is>
@@ -17695,7 +17695,7 @@
         <v>46272</v>
       </c>
       <c r="E195" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F195" t="inlineStr">
         <is>
@@ -17768,7 +17768,7 @@
         <v>46272</v>
       </c>
       <c r="E196" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F196" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>45069</v>
       </c>
       <c r="E197" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F197" t="inlineStr">
         <is>
@@ -17919,7 +17919,7 @@
         <v>46274</v>
       </c>
       <c r="E198" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F198" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>46092</v>
       </c>
       <c r="E199" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
@@ -18070,7 +18070,7 @@
         <v>44671</v>
       </c>
       <c r="E200" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
@@ -18143,7 +18143,7 @@
         <v>45629</v>
       </c>
       <c r="E201" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -18216,7 +18216,7 @@
         <v>46274</v>
       </c>
       <c r="E202" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -18289,7 +18289,7 @@
         <v>45587</v>
       </c>
       <c r="E203" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -18362,7 +18362,7 @@
         <v>45453</v>
       </c>
       <c r="E204" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -18440,7 +18440,7 @@
         <v>46042</v>
       </c>
       <c r="E205" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -18513,7 +18513,7 @@
         <v>46042</v>
       </c>
       <c r="E206" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F206" t="inlineStr">
         <is>
@@ -18586,7 +18586,7 @@
         <v>45792</v>
       </c>
       <c r="E207" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F207" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>44967</v>
       </c>
       <c r="E208" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F208" t="inlineStr">
         <is>
@@ -18732,7 +18732,7 @@
         <v>44994</v>
       </c>
       <c r="E209" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F209" t="inlineStr">
         <is>
@@ -18810,7 +18810,7 @@
         <v>45728</v>
       </c>
       <c r="E210" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F210" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>44810</v>
       </c>
       <c r="E211" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F211" t="inlineStr">
         <is>
@@ -18961,7 +18961,7 @@
         <v>45219</v>
       </c>
       <c r="E212" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
@@ -19034,7 +19034,7 @@
         <v>45755</v>
       </c>
       <c r="E213" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
@@ -19112,7 +19112,7 @@
         <v>44810</v>
       </c>
       <c r="E214" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -19185,7 +19185,7 @@
         <v>45476</v>
       </c>
       <c r="E215" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -19258,7 +19258,7 @@
         <v>45523</v>
       </c>
       <c r="E216" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>45523</v>
       </c>
       <c r="E217" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F217" t="inlineStr">
         <is>
@@ -19404,7 +19404,7 @@
         <v>45538</v>
       </c>
       <c r="E218" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F218" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>44986</v>
       </c>
       <c r="E219" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F219" t="inlineStr">
         <is>
@@ -19555,7 +19555,7 @@
         <v>45117</v>
       </c>
       <c r="E220" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F220" t="inlineStr">
         <is>
@@ -19628,7 +19628,7 @@
         <v>44977</v>
       </c>
       <c r="E221" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F221" t="inlineStr">
         <is>
@@ -19701,7 +19701,7 @@
         <v>45475</v>
       </c>
       <c r="E222" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F222" t="inlineStr">
         <is>
@@ -19779,7 +19779,7 @@
         <v>45117</v>
       </c>
       <c r="E223" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F223" t="inlineStr">
         <is>
@@ -19852,7 +19852,7 @@
         <v>45007</v>
       </c>
       <c r="E224" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F224" t="inlineStr">
         <is>
@@ -19930,7 +19930,7 @@
         <v>45085</v>
       </c>
       <c r="E225" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F225" t="inlineStr">
         <is>
@@ -20008,7 +20008,7 @@
         <v>45145</v>
       </c>
       <c r="E226" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F226" t="inlineStr">
         <is>
@@ -20081,7 +20081,7 @@
         <v>45159</v>
       </c>
       <c r="E227" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F227" t="inlineStr">
         <is>
@@ -20154,7 +20154,7 @@
         <v>45156</v>
       </c>
       <c r="E228" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F228" t="inlineStr">
         <is>
@@ -20227,7 +20227,7 @@
         <v>45531</v>
       </c>
       <c r="E229" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F229" t="inlineStr">
         <is>
@@ -20305,7 +20305,7 @@
         <v>45709</v>
       </c>
       <c r="E230" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F230" t="inlineStr">
         <is>
@@ -20378,7 +20378,7 @@
         <v>44680</v>
       </c>
       <c r="E231" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F231" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>45127</v>
       </c>
       <c r="E232" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F232" t="inlineStr">
         <is>
@@ -20529,7 +20529,7 @@
         <v>45755</v>
       </c>
       <c r="E233" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F233" t="inlineStr">
         <is>
@@ -20607,7 +20607,7 @@
         <v>45252</v>
       </c>
       <c r="E234" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F234" t="inlineStr">
         <is>
@@ -20680,7 +20680,7 @@
         <v>45280</v>
       </c>
       <c r="E235" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F235" t="inlineStr">
         <is>
@@ -20753,7 +20753,7 @@
         <v>45250</v>
       </c>
       <c r="E236" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F236" t="inlineStr">
         <is>
@@ -20826,7 +20826,7 @@
         <v>44812</v>
       </c>
       <c r="E237" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F237" t="inlineStr">
         <is>
@@ -20899,7 +20899,7 @@
         <v>45202</v>
       </c>
       <c r="E238" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F238" t="inlineStr">
         <is>
@@ -20972,7 +20972,7 @@
         <v>44526</v>
       </c>
       <c r="E239" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F239" t="inlineStr">
         <is>
@@ -21045,7 +21045,7 @@
         <v>45700</v>
       </c>
       <c r="E240" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F240" t="inlineStr">
         <is>
@@ -21123,7 +21123,7 @@
         <v>45316</v>
       </c>
       <c r="E241" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F241" t="inlineStr">
         <is>
@@ -21201,7 +21201,7 @@
         <v>45319</v>
       </c>
       <c r="E242" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F242" t="inlineStr">
         <is>
@@ -21279,7 +21279,7 @@
         <v>45771</v>
       </c>
       <c r="E243" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F243" t="inlineStr">
         <is>
@@ -21357,7 +21357,7 @@
         <v>45707</v>
       </c>
       <c r="E244" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F244" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>45895</v>
       </c>
       <c r="E245" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F245" t="inlineStr">
         <is>
@@ -21513,7 +21513,7 @@
         <v>46069</v>
       </c>
       <c r="E246" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F246" t="inlineStr">
         <is>
@@ -21591,7 +21591,7 @@
         <v>46089</v>
       </c>
       <c r="E247" s="1" t="n">
-        <v>46320</v>
+        <v>46321</v>
       </c>
       <c r="F247" t="inlineStr">
         <is>
